--- a/data/exports/validation_study/packets/week-1/packet-3.xlsx
+++ b/data/exports/validation_study/packets/week-1/packet-3.xlsx
@@ -544,7 +544,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2. 'techniques' sheet - the 13 attacks, mechanisms and defenses we recorded from your papers.</t>
+          <t>2. 'techniques' sheet - the 11 attacks, mechanisms and defenses we recorded from your papers.</t>
         </is>
       </c>
     </row>
@@ -2284,11 +2284,11 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Lost in the Middle: An Emergent Property from Information Retrieval Demands in LLMs</t>
+          <t>A Layered Security Framework Against Prompt Injection in RAG-Based Chatbots</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Lost in the Middle - An Emergent Property from Information Retrieval Demands in LLMs.pdf</t>
+          <t>data/papers/A Layered Security Framework Against Prompt Injection in RAG-Based Chatbots.pdf</t>
         </is>
       </c>
       <c r="G2" s="5" t="n"/>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Multi-Agent Framework for Threat Mitigation and Resilience in AI-Based Systems</t>
+          <t>A Reproducible Benchmark for Prompt Injection Vulnerability Assessment in Small-To-Medium Language Models</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t xml:space="preserve"> (ICCIT) 2025 28th International Conference on Computer and Information Technology</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Multi-Agent Framework for Threat Mitigation and Resilience in AI-Based Systems.pdf</t>
+          <t>data/papers/A Reproducible Benchmark for Prompt Injection Vulnerability Assessment in Small-To-Medium Language Models.pdf</t>
         </is>
       </c>
       <c r="G3" s="5" t="n"/>
@@ -2340,23 +2340,23 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Bench (ASB): Formalizing and Benchmarking Attacks and Defenses in LLM-based Agents</t>
+          <t>Protecting Context and Prompts: Deterministic Security for Non-Deterministic AI</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Agent Security Bench (ASB) - Formalizing and Benchmarking Attacks and Defenses in LLM-based Agents.pdf</t>
+          <t>data/papers/Protecting Context and Prompts - Deterministic Security for Non-Deterministic AI.pdf</t>
         </is>
       </c>
       <c r="G4" s="5" t="n"/>
@@ -2368,11 +2368,11 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Rag and Roll: An End-to-End Evaluation of Indirect Prompt Manipulations in LLM-based Application Frameworks</t>
+          <t>RADIANT: Retrieval AugmenteD entIty-context AligNmenT - Introducing RAG-ability and Entity-Context Divergence</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -2380,11 +2380,11 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Rag and Roll - An End-to-End Evaluation of Indirect Prompt Manipulations in LLM-based Application Frameworks.pdf</t>
+          <t>data/papers/RADIANT - Retrieval AugmenteD entIty-context AligNmenT - Introducing RAG-ability and Entity-Context Divergence.pdf</t>
         </is>
       </c>
       <c r="G5" s="5" t="n"/>
@@ -2396,23 +2396,23 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>A Study on Prompt Injection Attack Against LLM-Integrated Mobile Robotic Systems</t>
+          <t>AgentSecBench: Measuring Prompt Injection, Privacy Leakage, and Tool-Use Integrity in LLM Agents</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2024 IEEE 35th International Symposium on Software Reliability Engineering Workshops (ISSREW)</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>data/papers/A Study on Prompt Injection Attack Against LLM-Integrated Mobile Robotic Systems.pdf</t>
+          <t>data/papers/AgentSecBench - Measuring Prompt Injection, Privacy Leakage, and Tool-Use Integrity in LLM Agents.pdf</t>
         </is>
       </c>
       <c r="G6" s="5" t="n"/>
@@ -2424,23 +2424,19 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Unified Security Orchestration Framework for Protecting AI/ML Systems Against Input-Based and Model Supply Chain Attacks</t>
+          <t>The Promptware Kill Chain: How Prompt Injections Gradually Evolved Into a Multistep Malware Delivery Mechanism</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v>2026</v>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>AI and Machine Learning Advances</t>
-        </is>
-      </c>
+      <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Unified Security Orchestration Framework for Protecting AI-ML Systems Against Input-Based and Model Supply Chain Attacks.pdf</t>
+          <t>data/papers/The Promptware Kill Chain - How Prompt Injections Gradually Evolved Into a Multistep Malware Delivery Mechanism.pdf</t>
         </is>
       </c>
       <c r="G7" s="5" t="n"/>
@@ -2452,7 +2448,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Failure-Gated Hierarchical Memory: Preventing Memory Pollution in Long-Horizon LLM Agents via Critic-Guided Write Control</t>
+          <t>Addressing Prompt Injection in Large Language Models via In-Context Learning</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -2460,15 +2456,15 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>ICML</t>
+          <t>Computers, Materials &amp;amp; Continua</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Failure-Gated Hierarchical Memory - Preventing Memory Pollution in Long-Horizon LLM Agents via Critic-Guided Write Control.pdf</t>
+          <t>data/papers/Addressing Prompt Injection in Large Language Models via In-Context Learning.pdf</t>
         </is>
       </c>
       <c r="G8" s="5" t="n"/>
@@ -2480,11 +2476,11 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Fact-Augmented Lookahead Planning for LLM Agents</t>
+          <t>Agentic Permissions Policy Algebra for Taint Confinement in LLM Agents</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="n">
@@ -2492,7 +2488,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Fact-Augmented Lookahead Planning for LLM Agents.pdf</t>
+          <t>data/papers/Agentic Permissions Policy Algebra for Taint Confinement in LLM Agents.pdf</t>
         </is>
       </c>
       <c r="G9" s="5" t="n"/>
@@ -2504,11 +2500,11 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
+          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
@@ -2516,11 +2512,11 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>data/papers/MultiChallenge - A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs.pdf</t>
+          <t>data/papers/Caution for the Environment - Multimodal Agents are Susceptible to Environmental Distractions.pdf</t>
         </is>
       </c>
       <c r="G10" s="5" t="n"/>
@@ -2532,23 +2528,19 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>ReAcTree: Hierarchical LLM Agent Trees with Control Flow for Long-Horizon Task Planning</t>
+          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>International Conference on Autonomous Agents and Multiagent Systems</t>
-        </is>
-      </c>
+        <v>2026</v>
+      </c>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>data/papers/ReAcTree - Hierarchical LLM Agent Trees with Control Flow for Long-Horizon Task Planning.pdf</t>
+          <t>data/papers/Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems.pdf</t>
         </is>
       </c>
       <c r="G11" s="5" t="n"/>
@@ -2560,11 +2552,11 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Oblivion: Self-Adaptive Agentic Memory Control through Decay-Driven Activation</t>
+          <t>Attribute or Abstain: Large Language Models as Long Document Assistants</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
@@ -2572,11 +2564,11 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Oblivion - Self-Adaptive Agentic Memory Control through Decay-Driven Activation.pdf</t>
+          <t>data/papers/Attribute or Abstain - Large Language Models as Long Document Assistants.pdf</t>
         </is>
       </c>
       <c r="G12" s="5" t="n"/>
@@ -2588,11 +2580,11 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>LPS-Bench: Benchmarking Safety Awareness of Computer-Use Agents in Long-Horizon Planning under Benign and Adversarial Scenarios</t>
+          <t>When Refusals Fail: Unstable Safety Mechanisms in Long-Context LLM Agents</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
@@ -2600,11 +2592,11 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>data/papers/LPS-Bench - Benchmarking Safety Awareness of Computer-Use Agents in Long-Horizon Planning under Benign and Adversarial Scenarios.pdf</t>
+          <t>data/papers/When Refusals Fail - Unstable Safety Mechanisms in Long-Context LLM Agents.pdf</t>
         </is>
       </c>
       <c r="G13" s="5" t="n"/>
@@ -2616,23 +2608,23 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>WAB: Overcoming Memory, Network, and Security Walls in Native Agentic Browsers with WebAssembly</t>
+          <t>Knowledge Conflicts for LLMs: A Survey</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>WWW</t>
+          <t>EMNLP</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>data/papers/WAB - Overcoming Memory, Network, and Security Walls in Native Agentic Browsers with WebAssembly.pdf</t>
+          <t>data/papers/Knowledge Conflicts for LLMs - A Survey.pdf</t>
         </is>
       </c>
       <c r="G14" s="5" t="n"/>
@@ -2644,15 +2636,15 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Causal Intervention-Based Memory Selection for Long-Horizon LLM Agents</t>
+          <t>Meticulous Thought Defender: Fine-Grained Chain-of-Thought (CoT) for Detecting Prompt Injection Attacks of Large Language Models</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>IEEE Access</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
@@ -2660,7 +2652,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Causal Intervention-Based Memory Selection for Long-Horizon LLM Agents.pdf</t>
+          <t>data/papers/Meticulous Thought Defender - Fine-Grained Chain-of-Thought (CoT) for Detecting Prompt Injection Attacks of Large Language Models.pdf</t>
         </is>
       </c>
       <c r="G15" s="5" t="n"/>
@@ -2672,7 +2664,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Embedding-Based Detection of Indirect Prompt Injection Attacks in Large Language Models Using Semantic Context Analysis</t>
+          <t>Towards trustworthy agentic AI: a comprehensive survey of safety, robustness, privacy, and system security</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -2680,15 +2672,15 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Algorithms</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Embedding-Based Detection of Indirect Prompt Injection Attacks in Large Language Models Using Semantic Context Analysis.pdf</t>
+          <t>data/papers/Towards trustworthy agentic AI - a comprehensive survey of safety, robustness, privacy, and system security.pdf</t>
         </is>
       </c>
       <c r="G16" s="5" t="n"/>
@@ -2700,15 +2692,15 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>How Easily do Irrelevant Inputs Skew the Responses of Large Language Models?</t>
+          <t>Agentic Memory: Learning Unified Long-Term and Short-Term Memory Management for Large Language Model Agents</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>ACL</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
@@ -2716,7 +2708,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>data/papers/How Easily do Irrelevant Inputs Skew the Responses of Large Language Models.pdf</t>
+          <t>data/papers/Agentic Memory - Learning Unified Long-Term and Short-Term Memory Management for Large Language Model Agents.pdf</t>
         </is>
       </c>
       <c r="G17" s="5" t="n"/>
@@ -2800,7 +2792,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Lost in the Middle: An Emergent Property from Information Retrieval Demands in LLMs</t>
+          <t>A Layered Security Framework Against Prompt Injection in RAG-Based Chatbots</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -2823,7 +2815,7 @@
       <c r="H2" s="5" t="n"/>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>47878fc606ace61368776bf9407466cc19ea7a9b</t>
+          <t>1a062f96584a9f5c14177ae49fe9bb3ae30b67c1</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2825,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Lost in the Middle: An Emergent Property from Information Retrieval Demands in LLMs</t>
+          <t>A Layered Security Framework Against Prompt Injection in RAG-Based Chatbots</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -2848,7 +2840,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>ML/AI</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="F3" s="5" t="n"/>
@@ -2856,7 +2848,7 @@
       <c r="H3" s="5" t="n"/>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>47878fc606ace61368776bf9407466cc19ea7a9b</t>
+          <t>1a062f96584a9f5c14177ae49fe9bb3ae30b67c1</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2858,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Lost in the Middle: An Emergent Property from Information Retrieval Demands in LLMs</t>
+          <t>A Layered Security Framework Against Prompt Injection in RAG-Based Chatbots</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -2889,7 +2881,7 @@
       <c r="H4" s="5" t="n"/>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>47878fc606ace61368776bf9407466cc19ea7a9b</t>
+          <t>1a062f96584a9f5c14177ae49fe9bb3ae30b67c1</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2891,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Lost in the Middle: An Emergent Property from Information Retrieval Demands in LLMs</t>
+          <t>A Layered Security Framework Against Prompt Injection in RAG-Based Chatbots</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -2914,7 +2906,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>attack</t>
+          <t>defense</t>
         </is>
       </c>
       <c r="F5" s="5" t="n"/>
@@ -2922,7 +2914,7 @@
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>47878fc606ace61368776bf9407466cc19ea7a9b</t>
+          <t>1a062f96584a9f5c14177ae49fe9bb3ae30b67c1</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2924,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Lost in the Middle: An Emergent Property from Information Retrieval Demands in LLMs</t>
+          <t>A Layered Security Framework Against Prompt Injection in RAG-Based Chatbots</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -2947,7 +2939,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>RAG</t>
         </is>
       </c>
       <c r="F6" s="5" t="n"/>
@@ -2955,7 +2947,7 @@
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>47878fc606ace61368776bf9407466cc19ea7a9b</t>
+          <t>1a062f96584a9f5c14177ae49fe9bb3ae30b67c1</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2957,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Lost in the Middle: An Emergent Property from Information Retrieval Demands in LLMs</t>
+          <t>A Layered Security Framework Against Prompt Injection in RAG-Based Chatbots</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -2980,7 +2972,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="F7" s="5" t="n"/>
@@ -2988,7 +2980,7 @@
       <c r="H7" s="5" t="n"/>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>47878fc606ace61368776bf9407466cc19ea7a9b</t>
+          <t>1a062f96584a9f5c14177ae49fe9bb3ae30b67c1</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2990,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Lost in the Middle: An Emergent Property from Information Retrieval Demands in LLMs</t>
+          <t>A Layered Security Framework Against Prompt Injection in RAG-Based Chatbots</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -3013,7 +3005,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F8" s="5" t="n"/>
@@ -3021,7 +3013,7 @@
       <c r="H8" s="5" t="n"/>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>47878fc606ace61368776bf9407466cc19ea7a9b</t>
+          <t>1a062f96584a9f5c14177ae49fe9bb3ae30b67c1</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3023,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Lost in the Middle: An Emergent Property from Information Retrieval Demands in LLMs</t>
+          <t>A Layered Security Framework Against Prompt Injection in RAG-Based Chatbots</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -3046,7 +3038,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F9" s="5" t="n"/>
@@ -3054,7 +3046,7 @@
       <c r="H9" s="5" t="n"/>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>47878fc606ace61368776bf9407466cc19ea7a9b</t>
+          <t>1a062f96584a9f5c14177ae49fe9bb3ae30b67c1</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3056,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Lost in the Middle: An Emergent Property from Information Retrieval Demands in LLMs</t>
+          <t>A Layered Security Framework Against Prompt Injection in RAG-Based Chatbots</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -3079,7 +3071,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>ingestion</t>
         </is>
       </c>
       <c r="F10" s="5" t="n"/>
@@ -3087,7 +3079,7 @@
       <c r="H10" s="5" t="n"/>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>47878fc606ace61368776bf9407466cc19ea7a9b</t>
+          <t>1a062f96584a9f5c14177ae49fe9bb3ae30b67c1</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3089,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Lost in the Middle: An Emergent Property from Information Retrieval Demands in LLMs</t>
+          <t>A Layered Security Framework Against Prompt Injection in RAG-Based Chatbots</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -3120,7 +3112,7 @@
       <c r="H11" s="5" t="n"/>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>47878fc606ace61368776bf9407466cc19ea7a9b</t>
+          <t>1a062f96584a9f5c14177ae49fe9bb3ae30b67c1</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3122,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Lost in the Middle: An Emergent Property from Information Retrieval Demands in LLMs</t>
+          <t>A Layered Security Framework Against Prompt Injection in RAG-Based Chatbots</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -3153,7 +3145,7 @@
       <c r="H12" s="5" t="n"/>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>47878fc606ace61368776bf9407466cc19ea7a9b</t>
+          <t>1a062f96584a9f5c14177ae49fe9bb3ae30b67c1</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3155,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Lost in the Middle: An Emergent Property from Information Retrieval Demands in LLMs</t>
+          <t>A Layered Security Framework Against Prompt Injection in RAG-Based Chatbots</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -3178,7 +3170,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>No artifact release is mentioned anywhere in the paper. There is no GitHub link, code release, or trained-checkpoint release statement for the from-scratch-trained GPT-2/Llama/RNN/T5 models or the synthetic memory-task datasets used.</t>
+          <t>The paper states in a 'Data and Code Availability' section that 'the datasets, code, and related resources used in the implementation and experiments of this study are available at: GitHub Repository,' but this is rendered as an anchor-text hyperlink without an extractable plain-text URL in the parsed PDF (a recurring PDF-parsing limitation for icon/anchor-style links noted for several papers this session).</t>
         </is>
       </c>
       <c r="F13" s="5" t="n"/>
@@ -3186,7 +3178,7 @@
       <c r="H13" s="5" t="n"/>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>47878fc606ace61368776bf9407466cc19ea7a9b</t>
+          <t>1a062f96584a9f5c14177ae49fe9bb3ae30b67c1</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3188,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Lost in the Middle: An Emergent Property from Information Retrieval Demands in LLMs</t>
+          <t>A Layered Security Framework Against Prompt Injection in RAG-Based Chatbots</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -3211,7 +3203,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>GPT-2 Small, GPT-2 Large, and Llama-3.2 1B are trained entirely from scratch (not pre-trained checkpoints) on the memory paradigm tasks. For architectural comparison, an RNN-based sequence-to-sequence model (autoregressive) and a T5 encoder-decoder model (bidirectional, non-autoregressive) are also trained from scratch on the same free recall task to isolate the role of autoregressive causal masking versus bidirectional processing in producing the primacy effect.</t>
+          <t>Three target LLMs behind the RAG chatbot under evaluation: GPT-4o, Llama 3 (8B), and Mistral 7B. The framework's own detection components are a fine-tuned semantic anomaly classifier (Layer 1) and a semantic drift check (Layer 3); specific backbone architectures for these classifiers are not named in the extracted text.</t>
         </is>
       </c>
       <c r="F14" s="5" t="n"/>
@@ -3219,7 +3211,7 @@
       <c r="H14" s="5" t="n"/>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>47878fc606ace61368776bf9407466cc19ea7a9b</t>
+          <t>1a062f96584a9f5c14177ae49fe9bb3ae30b67c1</t>
         </is>
       </c>
     </row>
@@ -3229,7 +3221,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Lost in the Middle: An Emergent Property from Information Retrieval Demands in LLMs</t>
+          <t>A Layered Security Framework Against Prompt Injection in RAG-Based Chatbots</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -3244,7 +3236,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>No external/standard benchmark is used; the paper constructs synthetic training tasks from scratch. Three core memory paradigm tasks are defined: Free Recall (FR, output all list items in any order, imposing uniform long-term retrieval demand), Running Span (RS, output the last n items preceding a cue token where n is randomly sampled 1-7, imposing end-weighted short-term retrieval demand), and Combined (FR+RS, joint training on both recall objectives on the same input format). A fourth task, Masked Sequence Completion, is used as a closer analog to LLM next-token-prediction pre-training, with two variants -- masked subsequences drawn from anywhere in the list (long-term-demand analog) versus only from near the end of the list (short-term-demand analog) -- to validate that the memory-paradigm findings generalize beyond explicit recall-style tasks.</t>
+          <t>A custom evaluation set of 5,080 benign and adversarial samples (80/10/10 train/validation/test split, Table 7) built over a RAG knowledge base of 500 documents drawn from publicly available product documentation. Attacks are organized around three attacker objectives -- Instruction Override (IO), Data Exfiltration (DE), and Behavioral Manipulation (BM) -- and both direct injection (via user input) and indirect injection (via poisoned knowledge-base documents) vectors. Metrics: Attack Success Rate (ASR), False Positive Rate (FPR), Detection Rate (DR), and Response Quality Score (RQS, BERTScore F1 against a human reference response on benign queries that pass all layers).</t>
         </is>
       </c>
       <c r="F15" s="5" t="n"/>
@@ -3252,7 +3244,7 @@
       <c r="H15" s="5" t="n"/>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>47878fc606ace61368776bf9407466cc19ea7a9b</t>
+          <t>1a062f96584a9f5c14177ae49fe9bb3ae30b67c1</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3254,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Lost in the Middle: An Emergent Property from Information Retrieval Demands in LLMs</t>
+          <t>A Layered Security Framework Against Prompt Injection in RAG-Based Chatbots</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -3277,7 +3269,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Training GPT-2 and Llama-3.2 1B from scratch on Free Recall alone produces a primacy effect (higher recall accuracy for early list items); training on Running Span alone produces a recency effect (higher accuracy for the most recent items); and joint training on the Combined (FR+RS) task reproduces the canonical U-shaped 'lost-in-the-middle' curve seen in real LLMs, even though the models are trained from scratch on simple synthetic tasks with no natural text or actual pre-training. Llama-3.2 1B (the largest model tested) shows a substantially flatter/reduced U-shaped curve while maintaining near-flawless overall recall performance, consistent with prior findings that increased model complexity/scale reduces lost-in-the-middle severity. Architecture ablation shows the primacy effect emerges in autoregressive architectures (RNN seq2seq, GPT-2) but not in the bidirectional T5 encoder-decoder, which instead shows a flat serial-position curve with roughly equal probability of initiating recall from any list position -- supporting the hypothesis that causal masking (autoregressive processing) is a necessary architectural condition for primacy, not merely the long-term memory task demand alone. An attention-sink disruption ablation (using a thresholded sink-detection metric adapted from prior work, implemented via targeted dropout on attention layers exhibiting sink behavior) shows a selective, functional effect: disrupting attention sinks eliminates the primacy effect and impairs performance specifically on tasks with long-term memory demand (free recall and the combined task), while leaving short-term running-span task performance largely unaffected -- indicating attention sinks play a direct, task-selective mechanistic role in supporting long-range information retrieval rather than being a generic, dormant architectural byproduct. The masked sequence completion replication confirms the same pattern: long-term-demand masking (subsequences drawn from anywhere) induces primacy-like behavior, while short-term/end-weighted masking induces recency-like behavior.</t>
+          <t>Macro-averaged across GPT-4o, Llama 3 (8B), and Mistral 7B (Table 8), the undefended baseline has 71.4% ASR; the full three-layer framework reduces this to 11.3% ASR, a 60.1-percentage-point reduction, while maintaining a 4.8% FPR and RQS of 0.89 (versus 0.91 undefended, showing negligible benign-response-quality degradation). This exceeds the best single-layer baseline (L3/Output Auditing only, 38.6% ASR) by 27.3 percentage points and outperforms NeMo Guardrails (a published open-source guardrail system, 35.1% ASR, 8.4% FPR) by 23.8 percentage points on ASR while also achieving a lower FPR. Ablation across all seven non-empty layer subsets (Table 9) shows L3 alone achieves the largest single-layer ASR reduction (32.8 pp), followed by L1 (27.2 pp) and L2 (19.6 pp); critically, the full framework's combined ASR (11.3%) is lower than the best two-layer combination (L2+L3, 22.4%) by 11.1 pp, demonstrating the three layers are complementary rather than redundant, and the full framework's FPR (4.8%) is counterintuitively lower than both L1+L3 (6.9%) and L2+L3 (7.4%) because Layer 2 filters out injections before they reach Layer 3's more FPR-prone harmful-content classifier and drift check. Layer 1's semantic classifier achieves AUC=0.941 and Layer 3's harmful-content predicate AUC=0.923 in standalone ROC analysis. Per-model breakdown shows GPT-4o, despite being substantially more capable on standard benchmarks, achieves only a modestly lower undefended ASR than Llama 3 (8B) or Mistral 7B, consistent with prior findings that instruction-following capability and instruction-override susceptibility are not independent -- implying model upgrades alone cannot substitute for structural defense. Median latency overhead of the full framework is 61.2 ms (Table 10) on an NVIDIA A100 40GB GPU (LLM inference time excluded), with Layer 1 (pattern matching + semantic classifier) contributing ~20.5 ms, Layer 2 (chunk scanner + context assembly) ~11.5 ms, and Layer 3 (policy rule engine + semantic drift check) the remainder.</t>
         </is>
       </c>
       <c r="F16" s="5" t="n"/>
@@ -3285,7 +3277,7 @@
       <c r="H16" s="5" t="n"/>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>47878fc606ace61368776bf9407466cc19ea7a9b</t>
+          <t>1a062f96584a9f5c14177ae49fe9bb3ae30b67c1</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3287,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Lost in the Middle: An Emergent Property from Information Retrieval Demands in LLMs</t>
+          <t>A Layered Security Framework Against Prompt Injection in RAG-Based Chatbots</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -3310,7 +3302,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>This is a mechanistic/explanatory study rather than a method-vs-baseline comparison paper; the core comparisons are across training conditions (Free Recall alone vs. Running Span alone vs. Combined joint training) and across architectures (autoregressive GPT-2/RNN/Llama vs. bidirectional T5 encoder-decoder), plus an attention-sink-disrupted vs. intact ablation, rather than comparisons against competing prior methods or systems.</t>
+          <t>Five baseline conditions: Undefended (all layers disabled, raw inputs/documents passed directly to the LLM), L1 Only (Input Screening alone), L2 Only (Privilege-Constrained Context Assembly alone), L3 Only (Output Auditing alone), and NeMo Guardrails (an open-source guardrail framework with default prompt-injection protections, serving as a representative state-of-the-art single-layer defense baseline), each compared against the full three-layer framework and against each other via the full seven-subset ablation (Table 9).</t>
         </is>
       </c>
       <c r="F17" s="5" t="n"/>
@@ -3318,7 +3310,7 @@
       <c r="H17" s="5" t="n"/>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>47878fc606ace61368776bf9407466cc19ea7a9b</t>
+          <t>1a062f96584a9f5c14177ae49fe9bb3ae30b67c1</t>
         </is>
       </c>
     </row>
@@ -3328,7 +3320,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Lost in the Middle: An Emergent Property from Information Retrieval Demands in LLMs</t>
+          <t>A Layered Security Framework Against Prompt Injection in RAG-Based Chatbots</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -3343,7 +3335,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>N/A - non-adversarial. This is a mechanistic-interpretability and cognitive-science-inspired capability/behavior study, not a security paper. The incidental failure mode of interest is the 'lost-in-the-middle' phenomenon itself: LLM accuracy dropping for information located near the center of a long context window, historically treated in prior literature as a flaw or information-loss artifact, which this paper reframes as a rational, emergent adaptation to the mixture of short-term and long-term information retrieval demands present in pre-training data, shaped further by autoregressive architectural constraints and attention-sink dynamics.</t>
+          <t>Full formal threat model (Section 3), explicitly aligned with OWASP LLM01 (Prompt Injection). Attacker capability profile (Table 1): black-box access only (no model weights, no fine-tuning/parameter/gradient access), unknown system prompt (inferable only via probing), standard user-facing API access, permitted knowledge-base write access through legitimate content channels (e.g., reviews, support tickets, indexed web pages), and unbounded query budget (automated probing assumed). Two attack vectors are formalized: direct prompt injection, where an adversary embeds malicious instructions in the user-facing input field, further split into three sub-classes -- Role Hijacking (persona reassignment via hypothetical framing), Instruction Override ('ignore all previous instructions'-style attacks exploiting the model's tendency to follow the most recent imperative), and System Prompt Extraction (exfiltrating confidential system-prompt content); and indirect prompt injection, where an adversary embeds a malicious payload in an external document that the RAG retrieval module fetches and injects into the model context, critically not requiring the querying user to be the attacker since the payload may have been placed in the knowledge base well in advance, affecting every subsequent user whose query retrieves the poisoned document. Three attacker objectives are evaluated throughout: instruction override, data exfiltration, and behavioral manipulation. The architectural root cause identified is the absence of an instruction-plane/data-plane separation -- the LLM processes the system prompt, retrieved documents, and user message as a single undifferentiated token stream with no runtime mechanism to distinguish trusted instructions from untrusted content.</t>
         </is>
       </c>
       <c r="F18" s="5" t="n"/>
@@ -3351,7 +3343,7 @@
       <c r="H18" s="5" t="n"/>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>47878fc606ace61368776bf9407466cc19ea7a9b</t>
+          <t>1a062f96584a9f5c14177ae49fe9bb3ae30b67c1</t>
         </is>
       </c>
     </row>
@@ -3361,7 +3353,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Lost in the Middle: An Emergent Property from Information Retrieval Demands in LLMs</t>
+          <t>A Layered Security Framework Against Prompt Injection in RAG-Based Chatbots</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -3376,7 +3368,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>The paper has no section explicitly titled 'Limitations' and no dedicated limitations discussion; the paper's Discussion section (Section 4) and Conclusion (Section 5) synthesize findings without a self-critical caveats subsection. The closest analog is an implicit scope acknowledgment in the Introduction, which notes that 'other combinations of tasks and data distributions may also give rise to the lost-in-the-middle behavior after model training,' framing the paper's free-recall-plus-running-span setup as 'a minimal set of task demands' rather than an exhaustive or uniquely necessary explanation -- implicitly conceding that the paper does not rule out alternative causal task-demand formulations for the same emergent behavior. The Discussion also notes that whether attention sinks are functionally meaningful 'remains debated' in the broader literature, citing conflicting prior claims about sinks being largely dormant versus functionally important, positioning the paper's own selective-ablation finding as one data point in that ongoing debate rather than a fully settled question.</t>
+          <t>The paper contains an explicit Section 6.2 ('Limitations') with six distinct points: (1) static attacker model -- the threat model assumes a black-box attacker with no knowledge of the deployed defense; a white-box adversary aware of the Layer 1 pattern library and classifier thresholds could craft targeted evasion payloads below the semantic anomaly threshold, a standard limitation of detection-based defenses that motivates the continuous audit/retraining loop rather than eliminating the gap; (2) single-turn evaluation -- the experimental protocol evaluates each adversarial sample as an independent single-turn query, and the error analysis identifies multi-turn injection (splitting a payload across conversation turns so no individual turn triggers detection) as the fourth most common residual bypass mechanism (15.6% of bypass cases), which the current framework has no mechanism to detect since Layer 1/Layer 3 apply independently per turn; (3) knowledge base composition -- the evaluation knowledge base contains 500 documents from publicly available, relatively benign product documentation, whereas real deployments may index less-controlled content (user-generated reviews, social media, third-party APIs) presenting a wider poisoning surface, so evaluation on a more adversarially representative knowledge base is needed; (4) threshold sensitivity -- Layer 1/Layer 3 thresholds are calibrated on a held-out validation set from the same distribution as the test set, and production input-distribution shift is the most likely cause of FPR degradation in deployment, requiring sufficient labeled production data volume for the audit loop's recalibration mechanisms to function; (5) latency under concurrent load -- reported latency figures are collected under single-request conditions on dedicated hardware, and contention for the shared encoder model between Layer 1 and Layer 3 under concurrent production load may increase p95 latency beyond the reported 97.4 ms, with batched semantic encoding as an unevaluated mitigation; (6) data exfiltration is noted as the most tractable attacker goal, implying the other two objectives (instruction override, behavioral manipulation) are comparatively harder to fully mitigate. Section 6.3 lists four corresponding future-work directions: multi-turn injection detection, adaptive threshold calibration (online Platt scaling/isotonic regression from streaming audit logs), white-box/adaptive-adversary evaluation (e.g., Carlini-Wagner-style attacks adapted to text), and evaluation on more adversarially representative knowledge bases.</t>
         </is>
       </c>
       <c r="F19" s="5" t="n"/>
@@ -3384,7 +3376,7 @@
       <c r="H19" s="5" t="n"/>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>47878fc606ace61368776bf9407466cc19ea7a9b</t>
+          <t>1a062f96584a9f5c14177ae49fe9bb3ae30b67c1</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3386,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Lost in the Middle: An Emergent Property from Information Retrieval Demands in LLMs</t>
+          <t>A Layered Security Framework Against Prompt Injection in RAG-Based Chatbots</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -3409,7 +3401,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>This paper investigates the mechanistic origin of the 'lost-in-the-middle' phenomenon in LLMs -- degraded recall accuracy for information located near the center of a long context window -- by drawing an analogy to serial position effects (primacy and recency) documented in human memory literature, and testing whether the phenomenon is a rational emergent adaptation to training-data information retrieval demands rather than an architectural flaw or genuine information loss. The core methodology trains small language models (GPT-2 Small/Large, Llama-3.2 1B) entirely from scratch (no pre-training) on two classic cognitive-psychology memory paradigms adapted into synthetic sequence-modeling tasks: a Free Recall task, which requires recalling all list items in any order and thus imposes a uniform long-term memory demand equally across the entire input sequence, and a Running Span task, which requires recalling only the last n items preceding a cue token (n randomly sampled 1-7 per trial), imposing an end-weighted short-term memory demand concentrated near the sequence's end. Training a model on Free Recall alone produces a primacy effect (better recall of early items); training on Running Span alone produces a recency effect (better recall of recent items); and jointly training on both objectives (the Combined task) reproduces the full canonical U-shaped lost-in-the-middle curve, demonstrating that this behavior can be induced purely through task-demand optimization without any natural text pre-training. To explain the more counterintuitive primacy component (why uniform long-term demand produces a beginning-of-sequence bias rather than a flat curve), the paper conducts two mechanistic investigations: an architecture ablation comparing autoregressive models (RNN sequence-to-sequence, GPT-2) against a bidirectional T5 encoder-decoder trained on the identical free recall task, finding primacy emerges only under autoregressive (causally-masked) processing, implicating causal masking's inherent bias toward attending to earlier tokens; and an attention-sink ablation using a thresholded sink-detection metric to identify attention heads exhibiting the well-documented 'attention sink' phenomenon (disproportionate attention weight on initial low-semantic-content tokens), then selectively disrupting these heads via targeted dropout, finding this eliminates the primacy effect and impairs long-term-demand task performance specifically, while leaving short-term running-span performance intact -- establishing attention sinks as a task-selective, functionally important mechanism supporting long-range retrieval rather than an inert architectural byproduct. A final replication using a masked sequence completion task (structurally closer to LLM next-token-prediction pre-training than explicit recall) with long-term-demand and short-term-demand masking variants confirms the same primacy/recency pattern generalizes beyond the original memory-paradigm framing.</t>
+          <t>This paper proposes a model-agnostic, three-layer middleware defense against both direct and indirect prompt injection in RAG-based chatbots, arguing that existing single-stage defenses (input filters, system-prompt hardening, output monitors) are each individually incomplete because input filters cannot inspect retrieved documents, privilege/instruction-hierarchy enforcement cannot catch injections a model chooses to follow anyway, and output monitors cannot prevent a malicious payload from reaching the model in the first place. Layer 1 (Input Screening) combines a rule-based pattern-matching library with a fine-tuned semantic anomaly classifier to screen user input before it enters the pipeline. Layer 2 (Privilege-Constrained Context Assembly) enforces a provenance-based instruction hierarchy during RAG context assembly: retrieved document chunks are scanned and any content resembling an instruction is annotated with a [FLAGGED] tag rather than being allowed to silently override operator-defined policy, preventing retrieved content from acquiring instruction-level authority regardless of its phrasing. Layer 3 (Output Auditing) inspects the model's generated response using a policy rule engine (checking against explicit output predicates, e.g., harmful-content patterns) plus a semantic drift detector that flags responses which deviate from the chatbot's reference persona/policy, intercepting malicious payloads before delivery even if they successfully influenced the model's generation. All three layers feed into a Continuous Audit Loop that aggregates structured logs across the pipeline to support periodic retraining of the Layer 1/Layer 3 classifiers as new attack patterns emerge, and the entire framework deploys as middleware without requiring any modification to the underlying LLM. The empirical contribution centers on demonstrating -- via a full ablation over all seven non-empty layer combinations -- that the three layers are complementary (their combined effect on both ASR and FPR exceeds what any pairwise combination achieves) rather than redundant, with a particularly notable finding that Layer 2's filtering role indirectly reduces the false-positive burden reaching Layer 3's more FPR-prone components, an interaction effect invisible to any single-layer evaluation.</t>
         </is>
       </c>
       <c r="F20" s="5" t="n"/>
@@ -3417,7 +3409,7 @@
       <c r="H20" s="5" t="n"/>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>47878fc606ace61368776bf9407466cc19ea7a9b</t>
+          <t>1a062f96584a9f5c14177ae49fe9bb3ae30b67c1</t>
         </is>
       </c>
     </row>
@@ -3427,7 +3419,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Multi-Agent Framework for Threat Mitigation and Resilience in AI-Based Systems</t>
+          <t>A Reproducible Benchmark for Prompt Injection Vulnerability Assessment in Small-To-Medium Language Models</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -3450,7 +3442,7 @@
       <c r="H21" s="5" t="n"/>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>ad8a3f00e1b77aa19a71a7a166ee6ae533e7e3bc</t>
+          <t>64db5497a9b02734cdb6766268ce8929d98c8c20</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3452,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Multi-Agent Framework for Threat Mitigation and Resilience in AI-Based Systems</t>
+          <t>A Reproducible Benchmark for Prompt Injection Vulnerability Assessment in Small-To-Medium Language Models</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -3483,7 +3475,7 @@
       <c r="H22" s="5" t="n"/>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>ad8a3f00e1b77aa19a71a7a166ee6ae533e7e3bc</t>
+          <t>64db5497a9b02734cdb6766268ce8929d98c8c20</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3485,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Multi-Agent Framework for Threat Mitigation and Resilience in AI-Based Systems</t>
+          <t>A Reproducible Benchmark for Prompt Injection Vulnerability Assessment in Small-To-Medium Language Models</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -3516,7 +3508,7 @@
       <c r="H23" s="5" t="n"/>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>ad8a3f00e1b77aa19a71a7a166ee6ae533e7e3bc</t>
+          <t>64db5497a9b02734cdb6766268ce8929d98c8c20</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3518,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Multi-Agent Framework for Threat Mitigation and Resilience in AI-Based Systems</t>
+          <t>A Reproducible Benchmark for Prompt Injection Vulnerability Assessment in Small-To-Medium Language Models</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -3549,7 +3541,7 @@
       <c r="H24" s="5" t="n"/>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>ad8a3f00e1b77aa19a71a7a166ee6ae533e7e3bc</t>
+          <t>64db5497a9b02734cdb6766268ce8929d98c8c20</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3551,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Multi-Agent Framework for Threat Mitigation and Resilience in AI-Based Systems</t>
+          <t>A Reproducible Benchmark for Prompt Injection Vulnerability Assessment in Small-To-Medium Language Models</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -3574,7 +3566,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>multi-agent</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F25" s="5" t="n"/>
@@ -3582,7 +3574,7 @@
       <c r="H25" s="5" t="n"/>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>ad8a3f00e1b77aa19a71a7a166ee6ae533e7e3bc</t>
+          <t>64db5497a9b02734cdb6766268ce8929d98c8c20</t>
         </is>
       </c>
     </row>
@@ -3592,7 +3584,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Multi-Agent Framework for Threat Mitigation and Resilience in AI-Based Systems</t>
+          <t>A Reproducible Benchmark for Prompt Injection Vulnerability Assessment in Small-To-Medium Language Models</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -3615,7 +3607,7 @@
       <c r="H26" s="5" t="n"/>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>ad8a3f00e1b77aa19a71a7a166ee6ae533e7e3bc</t>
+          <t>64db5497a9b02734cdb6766268ce8929d98c8c20</t>
         </is>
       </c>
     </row>
@@ -3625,7 +3617,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Multi-Agent Framework for Threat Mitigation and Resilience in AI-Based Systems</t>
+          <t>A Reproducible Benchmark for Prompt Injection Vulnerability Assessment in Small-To-Medium Language Models</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -3640,7 +3632,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F27" s="5" t="n"/>
@@ -3648,7 +3640,7 @@
       <c r="H27" s="5" t="n"/>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>ad8a3f00e1b77aa19a71a7a166ee6ae533e7e3bc</t>
+          <t>64db5497a9b02734cdb6766268ce8929d98c8c20</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3650,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Multi-Agent Framework for Threat Mitigation and Resilience in AI-Based Systems</t>
+          <t>A Reproducible Benchmark for Prompt Injection Vulnerability Assessment in Small-To-Medium Language Models</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -3681,7 +3673,7 @@
       <c r="H28" s="5" t="n"/>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>ad8a3f00e1b77aa19a71a7a166ee6ae533e7e3bc</t>
+          <t>64db5497a9b02734cdb6766268ce8929d98c8c20</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3683,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Multi-Agent Framework for Threat Mitigation and Resilience in AI-Based Systems</t>
+          <t>A Reproducible Benchmark for Prompt Injection Vulnerability Assessment in Small-To-Medium Language Models</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -3706,7 +3698,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>execution</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F29" s="5" t="n"/>
@@ -3714,7 +3706,7 @@
       <c r="H29" s="5" t="n"/>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>ad8a3f00e1b77aa19a71a7a166ee6ae533e7e3bc</t>
+          <t>64db5497a9b02734cdb6766268ce8929d98c8c20</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3716,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Multi-Agent Framework for Threat Mitigation and Resilience in AI-Based Systems</t>
+          <t>A Reproducible Benchmark for Prompt Injection Vulnerability Assessment in Small-To-Medium Language Models</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -3747,7 +3739,7 @@
       <c r="H30" s="5" t="n"/>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>ad8a3f00e1b77aa19a71a7a166ee6ae533e7e3bc</t>
+          <t>64db5497a9b02734cdb6766268ce8929d98c8c20</t>
         </is>
       </c>
     </row>
@@ -3757,7 +3749,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Multi-Agent Framework for Threat Mitigation and Resilience in AI-Based Systems</t>
+          <t>A Reproducible Benchmark for Prompt Injection Vulnerability Assessment in Small-To-Medium Language Models</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -3780,7 +3772,7 @@
       <c r="H31" s="5" t="n"/>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>ad8a3f00e1b77aa19a71a7a166ee6ae533e7e3bc</t>
+          <t>64db5497a9b02734cdb6766268ce8929d98c8c20</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3782,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Multi-Agent Framework for Threat Mitigation and Resilience in AI-Based Systems</t>
+          <t>A Reproducible Benchmark for Prompt Injection Vulnerability Assessment in Small-To-Medium Language Models</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3803,17 +3795,13 @@
           <t>secondary</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Explicitly released: dataset and code with 'latest development version available at: https://github.com/foundjem/ThreatAssessment_AI-Agency.git' and archived at 'https://doi.org/10.5281/zenodo.17480025' (Zenodo DOI).</t>
-        </is>
-      </c>
+      <c r="E32" s="2" t="n"/>
       <c r="F32" s="5" t="n"/>
       <c r="G32" s="5" t="n"/>
       <c r="H32" s="5" t="n"/>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>ad8a3f00e1b77aa19a71a7a166ee6ae533e7e3bc</t>
+          <t>64db5497a9b02734cdb6766268ce8929d98c8c20</t>
         </is>
       </c>
     </row>
@@ -3823,7 +3811,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Multi-Agent Framework for Threat Mitigation and Resilience in AI-Based Systems</t>
+          <t>A Reproducible Benchmark for Prompt Injection Vulnerability Assessment in Small-To-Medium Language Models</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3838,7 +3826,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>ChatGPT-4o (temperature 0.4) powers the multi-agent Retrieval-Augmented Generation (RAG) reasoning system used to automatically extract TTPs, vulnerabilities, and lifecycle stages from over 300 scientific articles. This is not a paper evaluating LLMs as subjects of attack, but rather uses an LLM-based multi-agent system as the extraction/analysis tool; a Heterogeneous Graph Neural Network (HGNN) is separately trained for severity prediction and evidence-path interpretability (via GNNExplainer).</t>
+          <t>Ten Ollama-hosted small-to-medium language models, with TinyLlama identified as the most vulnerable at 97.3% ASR against a low extreme of 0.44%. A phi-3 model serves as the fallback judge in the dual-judge evaluation pipeline.</t>
         </is>
       </c>
       <c r="F33" s="5" t="n"/>
@@ -3846,7 +3834,7 @@
       <c r="H33" s="5" t="n"/>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>ad8a3f00e1b77aa19a71a7a166ee6ae533e7e3bc</t>
+          <t>64db5497a9b02734cdb6766268ce8929d98c8c20</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3844,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Multi-Agent Framework for Threat Mitigation and Resilience in AI-Based Systems</t>
+          <t>A Reproducible Benchmark for Prompt Injection Vulnerability Assessment in Small-To-Medium Language Models</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3871,7 +3859,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>The study aggregates 93 distinct threats extracted from multiple sources: MITRE ATLAS (26 real-world incidents), the AI Incident Database (12 incidents), and peer-reviewed literature (55 threats), supplemented by data mined from 854 ML repositories on GitHub and the Python Advisory (PyPA) database. The pipeline processed 834 validated CVEs (2,183 occurrences across 312 GitHub issues spanning 86 repositories), forming a heterogeneous knowledge graph of CVEs, CPEs/dependencies, GitHub issues, and MITRE ATT&amp;CK/ATLAS attack techniques (23,128 GitHub issue records referenced in Table entries).</t>
+          <t>225 adversarial prompts derived from 75 baselines across AdvBench, HarmfulQA and JailbreakBench, executed across ten models for 2,250 model-prompt interactions. Evaluation uses a hybrid dual-judge approach (LLM judge with phi-3 fallback) plus keyword-driven heuristics, with Welch's t-tests and Bonferroni correction for statistical analysis.</t>
         </is>
       </c>
       <c r="F34" s="5" t="n"/>
@@ -3879,7 +3867,7 @@
       <c r="H34" s="5" t="n"/>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>ad8a3f00e1b77aa19a71a7a166ee6ae533e7e3bc</t>
+          <t>64db5497a9b02734cdb6766268ce8929d98c8c20</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3877,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Multi-Agent Framework for Threat Mitigation and Resilience in AI-Based Systems</t>
+          <t>A Reproducible Benchmark for Prompt Injection Vulnerability Assessment in Small-To-Medium Language Models</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3904,7 +3892,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>The empirical analysis identifies 32 previously undocumented ML attack scenarios (comprising 17 new techniques and 13 new tactics) beyond current MITRE ATLAS coverage, including model-stealing attacks against commercial LLM APIs, data leakage through parameter memorization, and preference-guided query optimization enabling text-only jailbreaks and multimodal adversarial examples. Transformers emerged as the most frequently targeted architecture in real-world attack scenarios (25.4%), ahead of CNNs (19.05%, with specific examples including GPT2, Fisheye, Copycat, and ResNet). Testing, inference, and training were identified as the most vulnerable ML lifecycle phases, with buffer-overflow and denial-of-service (DoS) attacks the most prevalent threat types across ML repositories, and TensorFlow, OpenCV, and Jupyter Notebook the most vulnerable repositories, particularly via dependencies like pickle, joblib, numpy, python3.9.1, and log4j. Dominant TTPs identified include gradient-based obstinate attacks, MASTERKEY automated jailbreaking, federated learning poisoning, diffusion backdoor embedding, and preference-oriented optimization leakage, disproportionately impacting pretraining and inference stages. The authors introduce an ML Threat Mitigation Matrix mapping real-world threats to defensive strategies, and demonstrate that GNN-based analysis and clustering techniques (correlating CVSS scores, exploitability, attack success rate/ASR clusters, and stealth/detectability) can enhance ML vulnerability classification and risk prioritization beyond traditional CVSS scoring alone.</t>
+          <t>Mean Attack Success Rate across the ten evaluated systems is 65.2%, but the headline is the spread: ASR ranges from 0.44% to 97.3%, with TinyLlama at the vulnerable extreme at 97.3%. A range spanning more than two orders of magnitude among small-to-medium models means that model selection alone is a larger determinant of injection exposure than most defenses in this corpus achieve - a self-hosted deployment choosing poorly starts from near-total vulnerability, while another model in the same size class is nearly immune under the same prompts. That reinforces, on a much larger model panel, the same conclusion the PI-Bench paper elsewhere in this corpus reached (10.5% to 83.8% between LLaMA-3.1-8B and Mistral-7B): alignment quality rather than scale governs injection resistance. Because differences are tested with Welch's t-tests under Bonferroni correction, the between-model separation here is statistically established rather than asserted, which is unusual for this literature and makes the finding more citable than comparable claims elsewhere in the corpus.</t>
         </is>
       </c>
       <c r="F35" s="5" t="n"/>
@@ -3912,7 +3900,7 @@
       <c r="H35" s="5" t="n"/>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>ad8a3f00e1b77aa19a71a7a166ee6ae533e7e3bc</t>
+          <t>64db5497a9b02734cdb6766268ce8929d98c8c20</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3910,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Multi-Agent Framework for Threat Mitigation and Resilience in AI-Based Systems</t>
+          <t>A Reproducible Benchmark for Prompt Injection Vulnerability Assessment in Small-To-Medium Language Models</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3937,7 +3925,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>No traditional ML-model baselines; the study instead cross-validates its own multi-source threat extraction (MITRE ATLAS, MITRE ATT&amp;CK, AI Incident Database, GitHub/PyPA repositories, peer-reviewed literature) against each other via triangulation, and its GNN-based risk prediction is compared against traditional CVSS-based severity scoring as the implicit baseline for vulnerability prioritization.</t>
+          <t>Ten Ollama-hosted small-to-medium language models compared against one another under an identical 225-prompt adversarial set, with pairwise differences tested using Welch's t-tests adjusted by Bonferroni correction. The 225 prompts derive from 75 baselines across AdvBench, HarmfulQA and JailbreakBench. No defense is evaluated - the comparison axis is model, not mitigation.</t>
         </is>
       </c>
       <c r="F36" s="5" t="n"/>
@@ -3945,7 +3933,7 @@
       <c r="H36" s="5" t="n"/>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>ad8a3f00e1b77aa19a71a7a166ee6ae533e7e3bc</t>
+          <t>64db5497a9b02734cdb6766268ce8929d98c8c20</t>
         </is>
       </c>
     </row>
@@ -3955,7 +3943,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Multi-Agent Framework for Threat Mitigation and Resilience in AI-Based Systems</t>
+          <t>A Reproducible Benchmark for Prompt Injection Vulnerability Assessment in Small-To-Medium Language Models</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3968,17 +3956,13 @@
           <t>freetext</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Formal, broad-scope ML/AI security threat taxonomy (not a single formal attack threat model): the paper characterizes adversarial Tactics, Techniques, and Procedures (TTPs) spanning the full ML lifecycle (data collection, pretraining, training, fine-tuning, test-time, deployment/inference), including data poisoning, model extraction, prompt injection, automated jailbreaking (e.g., MASTERKEY), training data exfiltration, membership inference, backdoor/diffusion backdoor attacks, adversarial example transferability, side-channel attacks, sponge attacks, and a specific emerging class the paper highlights -- preference-guided black-box optimization, where attackers exploit a model's own comparative judgments (introspection) to iteratively craft successful jailbreaks and multimodal adversarial examples, which the paper argues paradoxically makes larger, better-calibrated models more vulnerable to such introspection-driven attacks.</t>
-        </is>
-      </c>
+      <c r="E37" s="2" t="n"/>
       <c r="F37" s="5" t="n"/>
       <c r="G37" s="5" t="n"/>
       <c r="H37" s="5" t="n"/>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>ad8a3f00e1b77aa19a71a7a166ee6ae533e7e3bc</t>
+          <t>64db5497a9b02734cdb6766268ce8929d98c8c20</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3972,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Multi-Agent Framework for Threat Mitigation and Resilience in AI-Based Systems</t>
+          <t>A Reproducible Benchmark for Prompt Injection Vulnerability Assessment in Small-To-Medium Language Models</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -4003,7 +3987,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>The paper has an explicit 'VI. Threats to Validity' section structured around four standard empirical software-engineering validity dimensions (following Wohlin et al. and Juristo &amp; Moreno methodology): Construct Validity (reliance on multiple threat databases with differing incident-categorization conventions could introduce bias, mitigated via cross-source triangulation and expert review of TTP-to-lifecycle mappings); Internal Validity (automated extraction from GitHub/AI Incident Database may contain duplicate or misclassified entries, and historical-trend-based TTP identification may not fully capture evolving attack strategies, mitigated via data cleaning and manual review of a case subset); External Validity (niche threats targeting proprietary/closed-source models may be underrepresented, and the rapidly evolving ML ecosystem means newly discovered vulnerabilities may not yet be reflected in the dataset); Conclusion Validity (absence of a standardized threat severity metric across different source databases introduces some uncertainty in frequency/impact-based prioritization); and Reliability (expert validation of TTP mappings introduces a degree of subjectivity, mitigated by releasing datasets and code for independent verification). Additionally, a component-level limitation notes the HGNN severity-prediction model 'produces probabilistic severity estimates, not formal proofs,' requires labeled anchors (CVSS/ATLAS) to function, and does not perform counterfactual reasoning or uncertainty quantification unless explicitly extended; and a residual risk is noted that even text-only, non-numeric-confidence interfaces can leak a strong optimization signal via comparative judgments, meaning current static prompt defenses remain insufficient against iterative, preference-guided attacks.</t>
+          <t>The study measures undefended model susceptibility, so it characterizes exposure rather than the effectiveness of any mitigation, and no defended configuration is tested. Evaluation is confined to small-to-medium models served through Ollama, so results do not speak to frontier systems or to models behind vendor-side safety layers. Judging is automated via an LLM judge with phi-3 fallback plus keyword heuristics, and while the dual-judge design reduces single-judge failure, LLM-based judging of attack success carries known reliability limits and no human-agreement validation is surfaced. The adversarial prompts are drawn from established jailbreak and harmful-content benchmarks (AdvBench, HarmfulQA, JailbreakBench), which target direct prompting rather than indirect injection through retrieved content or tool output - so the ASR figures do not characterize agentic indirect-injection exposure, which is the setting most of this corpus concerns.</t>
         </is>
       </c>
       <c r="F38" s="5" t="n"/>
@@ -4011,7 +3995,7 @@
       <c r="H38" s="5" t="n"/>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>ad8a3f00e1b77aa19a71a7a166ee6ae533e7e3bc</t>
+          <t>64db5497a9b02734cdb6766268ce8929d98c8c20</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4005,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Multi-Agent Framework for Threat Mitigation and Resilience in AI-Based Systems</t>
+          <t>A Reproducible Benchmark for Prompt Injection Vulnerability Assessment in Small-To-Medium Language Models</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -4036,7 +4020,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>This paper presents a large-scale empirical characterization of machine learning (ML) security threats across the full ML lifecycle, motivated by the observation that traditional cybersecurity frameworks lack ML-specific threat modeling and fail to capture evolving attack vectors in foundation-model, multimodal, and federated/RAG settings. The methodology aggregates and cross-validates threat intelligence from four heterogeneous sources -- 26 real-world incidents from MITRE ATLAS, 12 from the AI Incident Database, 55 threats from peer-reviewed literature, and vulnerability data mined from 854 ML repositories on GitHub and the Python Advisory (PyPA) database -- extracting a total of 93 distinct threats. The core technical contribution is a multi-agent reasoning system built on Retrieval-Augmented Generation (RAG) and powered by ChatGPT-4o (temperature 0.4), which automatically extracts TTPs (Tactics, Techniques, and Procedures), exploited vulnerabilities, and affected ML lifecycle stages from over 300 scientific articles using evidence-grounded reasoning, feeding the results into an ontology-driven, heterogeneous knowledge/threat graph that links CVEs, software dependencies (CPEs), GitHub issues, and MITRE ATT&amp;CK/ATLAS attack techniques for cross-source validation and lifecycle mapping. On top of this graph, the authors train a Heterogeneous Graph Neural Network (HGNN) for interpretable, evidence-grounded severity prediction (using GNNExplainer to surface the specific relational evidence paths, e.g., DataPoisoning to TrainingCorruption to Inference, that drive each severity estimate), combined with clustering analysis across attack success rate, stealth/detectability, and computational cost dimensions to refine vulnerability prioritization beyond traditional CVSS scoring. The study's central empirical contributions are the identification of 32 previously undocumented ML attack scenarios not covered by MITRE ATLAS, characterization of which ML architectures, lifecycle phases, and software dependencies are most frequently targeted, and the introduction of an ML Threat Mitigation Matrix that maps the identified real-world threats to concrete defensive strategies, aimed at establishing a foundation for proactive, multi-agent-driven AI security governance.</t>
+          <t>Presents a reproducible, automated benchmarking infrastructure for evaluating prompt-injection and jailbreak vulnerability across small- to medium-scale language models - a segment that matters because these are the models organizations self-host, yet safety evaluation concentrates on frontier systems. The design emphasizes reproducibility and statistical discipline throughout: a dynamic set of 225 adversarial prompts derived from 75 baselines drawn from three established sources (AdvBench, HarmfulQA, JailbreakBench), executed against ten Ollama-hosted systems for 2,250 model-prompt interactions. Judging uses a hybrid dual-judge approach - an LLM-based judge with a phi-3 fallback - supplemented by keyword-driven heuristics, so a single judge's failure does not silently determine the outcome. Results are analysed under strict statistical controls using Welch's t-tests with Bonferroni correction for multiple comparisons, which is notably more rigorous than the norm in this corpus, where most defense and attack papers report point estimates without significance testing or variance. Building the prompt set from existing public benchmarks rather than generating bespoke attacks also makes the results comparable across studies in a way that self-generated attack corpora are not. A Track A measurement contribution on the direct-input channel.</t>
         </is>
       </c>
       <c r="F39" s="5" t="n"/>
@@ -4044,7 +4028,7 @@
       <c r="H39" s="5" t="n"/>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>ad8a3f00e1b77aa19a71a7a166ee6ae533e7e3bc</t>
+          <t>64db5497a9b02734cdb6766268ce8929d98c8c20</t>
         </is>
       </c>
     </row>
@@ -4054,7 +4038,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Bench (ASB): Formalizing and Benchmarking Attacks and Defenses in LLM-based Agents</t>
+          <t>Protecting Context and Prompts: Deterministic Security for Non-Deterministic AI</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -4077,7 +4061,7 @@
       <c r="H40" s="5" t="n"/>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>5f4efbe3aae1d8f44ceab1da257ae685d6beb00b</t>
+          <t>94981b50dd04908681311e4a3ff3a833b297ea3d</t>
         </is>
       </c>
     </row>
@@ -4087,7 +4071,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Bench (ASB): Formalizing and Benchmarking Attacks and Defenses in LLM-based Agents</t>
+          <t>Protecting Context and Prompts: Deterministic Security for Non-Deterministic AI</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -4110,7 +4094,7 @@
       <c r="H41" s="5" t="n"/>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>5f4efbe3aae1d8f44ceab1da257ae685d6beb00b</t>
+          <t>94981b50dd04908681311e4a3ff3a833b297ea3d</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4104,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Bench (ASB): Formalizing and Benchmarking Attacks and Defenses in LLM-based Agents</t>
+          <t>Protecting Context and Prompts: Deterministic Security for Non-Deterministic AI</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -4143,7 +4127,7 @@
       <c r="H42" s="5" t="n"/>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>5f4efbe3aae1d8f44ceab1da257ae685d6beb00b</t>
+          <t>94981b50dd04908681311e4a3ff3a833b297ea3d</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4137,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Bench (ASB): Formalizing and Benchmarking Attacks and Defenses in LLM-based Agents</t>
+          <t>Protecting Context and Prompts: Deterministic Security for Non-Deterministic AI</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -4168,7 +4152,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>attack</t>
+          <t>defense</t>
         </is>
       </c>
       <c r="F43" s="5" t="n"/>
@@ -4176,7 +4160,7 @@
       <c r="H43" s="5" t="n"/>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>5f4efbe3aae1d8f44ceab1da257ae685d6beb00b</t>
+          <t>94981b50dd04908681311e4a3ff3a833b297ea3d</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4170,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Bench (ASB): Formalizing and Benchmarking Attacks and Defenses in LLM-based Agents</t>
+          <t>Protecting Context and Prompts: Deterministic Security for Non-Deterministic AI</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -4209,7 +4193,7 @@
       <c r="H44" s="5" t="n"/>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>5f4efbe3aae1d8f44ceab1da257ae685d6beb00b</t>
+          <t>94981b50dd04908681311e4a3ff3a833b297ea3d</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4203,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Bench (ASB): Formalizing and Benchmarking Attacks and Defenses in LLM-based Agents</t>
+          <t>Protecting Context and Prompts: Deterministic Security for Non-Deterministic AI</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -4242,7 +4226,7 @@
       <c r="H45" s="5" t="n"/>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>5f4efbe3aae1d8f44ceab1da257ae685d6beb00b</t>
+          <t>94981b50dd04908681311e4a3ff3a833b297ea3d</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4236,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Bench (ASB): Formalizing and Benchmarking Attacks and Defenses in LLM-based Agents</t>
+          <t>Protecting Context and Prompts: Deterministic Security for Non-Deterministic AI</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4275,7 +4259,7 @@
       <c r="H46" s="5" t="n"/>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>5f4efbe3aae1d8f44ceab1da257ae685d6beb00b</t>
+          <t>94981b50dd04908681311e4a3ff3a833b297ea3d</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4269,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Bench (ASB): Formalizing and Benchmarking Attacks and Defenses in LLM-based Agents</t>
+          <t>Protecting Context and Prompts: Deterministic Security for Non-Deterministic AI</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4308,7 +4292,7 @@
       <c r="H47" s="5" t="n"/>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>5f4efbe3aae1d8f44ceab1da257ae685d6beb00b</t>
+          <t>94981b50dd04908681311e4a3ff3a833b297ea3d</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4302,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Bench (ASB): Formalizing and Benchmarking Attacks and Defenses in LLM-based Agents</t>
+          <t>Protecting Context and Prompts: Deterministic Security for Non-Deterministic AI</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4333,7 +4317,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>execution</t>
         </is>
       </c>
       <c r="F48" s="5" t="n"/>
@@ -4341,7 +4325,7 @@
       <c r="H48" s="5" t="n"/>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>5f4efbe3aae1d8f44ceab1da257ae685d6beb00b</t>
+          <t>94981b50dd04908681311e4a3ff3a833b297ea3d</t>
         </is>
       </c>
     </row>
@@ -4351,7 +4335,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Bench (ASB): Formalizing and Benchmarking Attacks and Defenses in LLM-based Agents</t>
+          <t>Protecting Context and Prompts: Deterministic Security for Non-Deterministic AI</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4374,7 +4358,7 @@
       <c r="H49" s="5" t="n"/>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>5f4efbe3aae1d8f44ceab1da257ae685d6beb00b</t>
+          <t>94981b50dd04908681311e4a3ff3a833b297ea3d</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4368,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Bench (ASB): Formalizing and Benchmarking Attacks and Defenses in LLM-based Agents</t>
+          <t>Protecting Context and Prompts: Deterministic Security for Non-Deterministic AI</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4399,7 +4383,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F50" s="5" t="n"/>
@@ -4407,7 +4391,7 @@
       <c r="H50" s="5" t="n"/>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>5f4efbe3aae1d8f44ceab1da257ae685d6beb00b</t>
+          <t>94981b50dd04908681311e4a3ff3a833b297ea3d</t>
         </is>
       </c>
     </row>
@@ -4417,7 +4401,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Bench (ASB): Formalizing and Benchmarking Attacks and Defenses in LLM-based Agents</t>
+          <t>Protecting Context and Prompts: Deterministic Security for Non-Deterministic AI</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4432,7 +4416,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>No code, dataset, or artifact release URL was found in the extracted text after thorough searching for 'github' and 'code available' patterns (the paper's own reference list cites many third-party GitHub repositories for compared/related tools such as LangChain, Rebuff, Vigil, and AutoGPT, but no release link for the authors' own implementation is given). The paper mentions 'Full evaluation details provided in appendices upon acceptance,' suggesting supplementary materials were not yet finalized/released at preprint time.</t>
         </is>
       </c>
       <c r="F51" s="5" t="n"/>
@@ -4440,7 +4424,7 @@
       <c r="H51" s="5" t="n"/>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>5f4efbe3aae1d8f44ceab1da257ae685d6beb00b</t>
+          <t>94981b50dd04908681311e4a3ff3a833b297ea3d</t>
         </is>
       </c>
     </row>
@@ -4450,7 +4434,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Bench (ASB): Formalizing and Benchmarking Attacks and Defenses in LLM-based Agents</t>
+          <t>Protecting Context and Prompts: Deterministic Security for Non-Deterministic AI</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4465,7 +4449,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Gemma2-9B, Gemma2-27B; LLaMA3-8B, LLaMA3-70B, LLaMA3.1-8B, LLaMA3.1-70B; Mixtral-8x7B; Qwen2-7B, Qwen2-72B; Claude-3.5-Sonnet; GPT-3.5-Turbo, GPT-4o, GPT-4o-mini (13 LLM backbones total)</t>
+          <t>N/A in the sense of a benchmarked backbone-model comparison -- this is a cryptographic protocol/systems security paper rather than a model-evaluation paper. Claude and GPT-4 are referenced illustratively (as examples of modern LLMs with 'sophisticated prompt filters' that nonetheless cannot distinguish legitimate instructions from attacker-injected ones based on semantic structure alone), and OpenAI API, Anthropic Claude API, and LangChain are referenced as example integration frameworks, but no specific LLM backbone is reported as the subject of the paper's own empirical detection-rate evaluation.</t>
         </is>
       </c>
       <c r="F52" s="5" t="n"/>
@@ -4473,7 +4457,7 @@
       <c r="H52" s="5" t="n"/>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>5f4efbe3aae1d8f44ceab1da257ae685d6beb00b</t>
+          <t>94981b50dd04908681311e4a3ff3a833b297ea3d</t>
         </is>
       </c>
     </row>
@@ -4483,7 +4467,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Bench (ASB): Formalizing and Benchmarking Attacks and Defenses in LLM-based Agents</t>
+          <t>Protecting Context and Prompts: Deterministic Security for Non-Deterministic AI</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4498,7 +4482,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Bench (ASB, new benchmark introduced by this paper): 10 realistic scenarios (e.g. IT management, investment, e-commerce, research, autonomous driving, finance), 10 corresponding agents, 50 agent tasks, over 400 tools (20 normal + attack tools) and 400 attack tasks, 10 Plan-of-Thought (PoT) backdoor demonstrations, evaluated across 13 attack methods (5 Direct Prompt Injection variants, 5 Indirect Prompt Injection variants, Memory Poisoning, a novel PoT Backdoor attack, and Mixed Attacks) and 11 defense methods, measured with 7 metrics (ASR, Refuse Rate, Performance-under-No-Attack, Benign Performance, False Negative/Positive Rate, and a new Net Resilient Performance metric)</t>
+          <t>No pre-existing external benchmark dataset is used; the paper's own evaluation is built around 6 exhaustive attack categories the authors define to cover the threat surface for prompt and context manipulation: Injection, Obfuscation, Semantic Drift, Context Poisoning, Tool Chaining, and Replay (Table 2), each with a representative attack example, corresponding defense mechanism, and formal/cryptographic guarantee (Table 3).</t>
         </is>
       </c>
       <c r="F53" s="5" t="n"/>
@@ -4506,7 +4490,7 @@
       <c r="H53" s="5" t="n"/>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>5f4efbe3aae1d8f44ceab1da257ae685d6beb00b</t>
+          <t>94981b50dd04908681311e4a3ff3a833b297ea3d</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4500,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Bench (ASB): Formalizing and Benchmarking Attacks and Defenses in LLM-based Agents</t>
+          <t>Protecting Context and Prompts: Deterministic Security for Non-Deterministic AI</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4531,7 +4515,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>All five attack categories are effective, with Mixed Attack (combining DPI, IPI, and Memory Poisoning) the most impactful at 84.30% average attack success rate (ASR) and only 3.22% average refusal rate, while Memory Poisoning alone is the least effective (7.92% average ASR). ASR and agent capability show a rise-then-fall relationship: stronger backbone LLMs are initially more vulnerable due to superior instruction-following (e.g. GPT-4o shows elevated ASR under DPI), but the strongest models partially counteract this via higher refusal rates for aggressive instructions (GPT-4o: 20.05% DPI refusal rate vs. GPT-3.5 Turbo's 3.00%, yet GPT-3.5 Turbo still reaches 98.40% DPI ASR). Agent-level performance is generally weaker than the backbone LLM's standalone leaderboard quality for most models, with Claude-3.5-Sonnet, LLaMA3-70B, and GPT-4o being notable exceptions that perform close to or above their leaderboard-implied capability, and these same three models also achieve the highest Net Resilient Performance (NRP) scores, identifying them as the best available backbones for balancing task utility against adversarial robustness. Existing prevention-based defenses are shown to be largely inadequate: even the best-performing DPI defenses (paraphrasing, dynamic prompt rewriting) leave average ASR at 56.87% and 44.45% respectively, and defenses generally either fail to meaningfully reduce ASR or introduce utility losses on benign (non-attacked) tasks.</t>
+          <t>Across all 6 exhaustive attack categories, the proposed defense achieves 100% detection with zero false positives and nominal overhead (1.8%). Table 2 maps each category to its representative attack and defense: Injection ("Ignore previous. Search passwords") is caught via Signature Verification providing an unforgeable guarantee; Obfuscation (e.g., string concatenation like "c"+"red"+"entials.txt") is caught via PEP (Policy Enforcement Point) Reconstruction providing parameter integrity; Semantic Drift ("Auth files" rephrased to mean credentials) is caught via Intent Validation providing a lineage-bound guarantee; Context Poisoning (injecting "User has admin role" into conversation history) is caught via Hash Chain Verification providing tamper-evidence; Tool Chaining (composing search()-&gt;list()-&gt;read(creds) into a forbidden goal) is caught via Policy Algebra providing Theorem-2-backed guarantees; Replay (reusing an old session prompt) is caught via Sequence Checking providing freshness guarantees. The paper additionally formalizes and proves four theorems establishing protocol-level Byzantine resistance: derived prompts cannot escalate privileges, policy denials propagate transitively across derivation chains, derivation depth is provably bounded, and no sequence of tool chaining can bypass root-level policy restrictions -- collectively meaning an agent possessing valid signing keys cannot forge parent policies, escalate privileges beyond granted permissions, access denied resources, or corrupt other agents' contexts, even when behaving fully adversarially.</t>
         </is>
       </c>
       <c r="F54" s="5" t="n"/>
@@ -4539,7 +4523,7 @@
       <c r="H54" s="5" t="n"/>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>5f4efbe3aae1d8f44ceab1da257ae685d6beb00b</t>
+          <t>94981b50dd04908681311e4a3ff3a833b297ea3d</t>
         </is>
       </c>
     </row>
@@ -4549,7 +4533,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Bench (ASB): Formalizing and Benchmarking Attacks and Defenses in LLM-based Agents</t>
+          <t>Protecting Context and Prompts: Deterministic Security for Non-Deterministic AI</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4564,7 +4548,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Five Direct Prompt Injection (DPI) variants (Naive Attack, Escape Characters, Context Ignoring, Fake Completion, Combined Attack) and five analogous Indirect Prompt Injection (IPI) variants, compared against Memory Poisoning, the paper's novel PoT Backdoor attack, and Mixed Attacks, across all 13 LLM backbones; 11 defense methods (Delimiters, Dynamic Prompt Rewriting, Sandwich Prevention, Instructional Prevention, Paraphrasing, Shuffle, PPL-based detection, LLM-based detection) evaluated for ASR reduction against their corresponding attack types (DPI/IPI, Memory Poisoning, PoT Backdoor)</t>
+          <t>The paper contrasts its approach against existing defense categories it argues are structurally insufficient: input filtering/sanitization systems (Rebuff, Lakera Guard, Vigil, LLM Guard -- reactive, pattern/classifier-based, evadable via rephrasing, cited as having documented vulnerabilities including poor canary-word detection and failure against novel attacks per a 2025 evaluation) and policy-based AI frameworks (LangChain, LangGraph, Semantic Kernel, NeMo Guardrails -- which lack cryptographic binding, exemplified by CVE-2024-8309, a critical vulnerability in LangChain's GraphCypherQAChain enabling full database compromise via prompt injection). No direct head-to-head quantitative re-evaluation of these specific prior systems against the paper's own 6-category test suite is presented in the extracted portions of the paper.</t>
         </is>
       </c>
       <c r="F55" s="5" t="n"/>
@@ -4572,7 +4556,7 @@
       <c r="H55" s="5" t="n"/>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>5f4efbe3aae1d8f44ceab1da257ae685d6beb00b</t>
+          <t>94981b50dd04908681311e4a3ff3a833b297ea3d</t>
         </is>
       </c>
     </row>
@@ -4582,7 +4566,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Bench (ASB): Formalizing and Benchmarking Attacks and Defenses in LLM-based Agents</t>
+          <t>Protecting Context and Prompts: Deterministic Security for Non-Deterministic AI</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4597,7 +4581,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Formalizes a comprehensive black-box threat model spanning five distinct attack surfaces on the LLM agent operational pipeline (system prompt, user prompt, tool usage, memory retrieval): (1) Direct Prompt Injection (DPI) - the attacker directly manipulates the user's prompt (motivated by realistic scenarios like compromised third-party prompt-engineering services or man-in-the-middle interception) to redirect the agent toward an attacker-specified injected task and attack tool list; (2) Indirect Prompt Injection (IPI) - the attacker embeds malicious instructions into a tool's response/observation during task execution; (3) Memory Poisoning - the attacker injects poisoned query-plan key-value pairs into the agent's long-term memory/RAG database (with only black-box access to the database and its embedder, unlike prior white-box-access memory-poisoning work), so that future queries retrieving these poisoned demonstrations as in-context examples reproduce the attacker's malicious plan; (4) Plan-of-Thought (PoT) Backdoor Attack - a novel, training-free attack introduced by this paper that poisons a subset of the agent's chain-of-thought-style planning demonstrations (embedded in the system prompt) with an adversarial planning step and target action, paired with a backdoor trigger (non-word tokens or LLM-optimized low-salience phrases) inserted into the user query, so the agent behaves maliciously only when the trigger is present and normally otherwise; and (5) Mixed Attacks combining multiple of the above. Across all attack types, the attacker knows the full details of attack tools (name, functionality) and can integrate malicious tools into the agent's toolkit (e.g. via manipulated third-party API platforms), but has only black-box API access to the backbone LLM with no knowledge of its architecture, weights, or training data.</t>
+          <t>This is a security/cryptographic-protocol paper with a full formal threat model. The paper identifies five properties of agentic systems that break traditional security models: instructions and data are intertwined (no syntactic boundary distinguishes commands from content, since LLMs process both through identical mechanisms); non-determinism (execution paths emerge from LLM reasoning rather than static code, and agents dynamically generate derived prompts forming instruction chains that resist static analysis); semantic ambiguity (natural language's effectively infinite paraphrase space defeats pattern matching, e.g., "steal credentials" rephrased as "locate authentication files for security audit"); stateful multi-turn context (gradual manipulation across conversation turns can appear benign in isolation while collectively violating policy); and dynamic derivation chains (prompts spawn further prompts, requiring policies to compose correctly across derivations to prevent privilege escalation). The threat model explicitly considers a fully adversarial/Byzantine agent (one that behaves arbitrarily, including maliciously) and asks what protocol-level guarantees can still be enforced against it -- explicitly distinguishing this from guaranteeing application-level correctness or intent (the primitives prevent cryptographic-invariant violations like forged signature or hash chains, but do not verify whether a given policy itself is semantically correct or complete).</t>
         </is>
       </c>
       <c r="F56" s="5" t="n"/>
@@ -4605,7 +4589,7 @@
       <c r="H56" s="5" t="n"/>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>5f4efbe3aae1d8f44ceab1da257ae685d6beb00b</t>
+          <t>94981b50dd04908681311e4a3ff3a833b297ea3d</t>
         </is>
       </c>
     </row>
@@ -4615,7 +4599,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Bench (ASB): Formalizing and Benchmarking Attacks and Defenses in LLM-based Agents</t>
+          <t>Protecting Context and Prompts: Deterministic Security for Non-Deterministic AI</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4630,7 +4614,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>No explicit numbered Limitations section appears in the pages available, but the Conclusion states future work will focus on 'improving defenses and expanding attack scenarios,' implying the current benchmark's defense repertoire (11 methods) and attack-scenario coverage (10 scenarios) are not considered exhaustive by the authors; the paper's own results reveal that all currently implemented prevention-based defenses remain inadequate against the benchmarked attacks (best-performing defenses still leave 44-57% average ASR against DPI), which the authors frame as demonstrating 'important work to be done in terms of agent security' for the field rather than as a limitation specific to the benchmark's methodology.</t>
+          <t>The paper contains an explicit 'Limitations and Future Work' discussion: 'While our approach is sound, the biggest limitation remains policy authoring. Our primitives enforce policies perfectly, but they cannot ensure policies are complete or correct -- garbage in, garbage out. Proving policy completeness is out of scope for this work, though we note that standard enterprise policies (deny credentials, enforce read-only constraints) proved effective in our evaluation. Future work includes multi-model consensus for semantic validation and automated policy synthesis from workflow traces to lower the expertise barrier.' A related, explicitly stated scope boundary appears in the Byzantine-resistance discussion: the primitives 'enforce policies perfectly -- even adversarial agents cannot violate organizational constraints,' but this guarantee is protocol-level only and 'do[es] not verify intent or prevent misuse of legitimate permissions' -- i.e., an agent that stays within its granted permissions but misuses them for an unintended purpose is not addressed by these cryptographic guarantees alone.</t>
         </is>
       </c>
       <c r="F57" s="5" t="n"/>
@@ -4638,7 +4622,7 @@
       <c r="H57" s="5" t="n"/>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>5f4efbe3aae1d8f44ceab1da257ae685d6beb00b</t>
+          <t>94981b50dd04908681311e4a3ff3a833b297ea3d</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4632,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Bench (ASB): Formalizing and Benchmarking Attacks and Defenses in LLM-based Agents</t>
+          <t>Protecting Context and Prompts: Deterministic Security for Non-Deterministic AI</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4663,7 +4647,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Introduces Agent Security Bench (ASB), the first comprehensive framework to formalize, benchmark, and evaluate a wide range of adversarial attacks and corresponding defenses against LLM-based agents across their full operational pipeline (system prompt definition, user prompt handling, memory retrieval, and tool usage), addressing the gap that prior benchmarks (e.g. InjecAgent, AgentDojo) are limited to narrow attack types (typically only Indirect Prompt Injection) or a small number of scenarios. ASB formally defines and unifies five distinct attack categories under a common mathematical framework - Direct Prompt Injection (DPI), Indirect Prompt Injection (IPI), Memory Poisoning (with black-box rather than assumed white-box access to the RAG database/embedder, unlike prior work), a novel Plan-of-Thought (PoT) Backdoor Attack that poisons chain-of-thought-style planning demonstrations in the system prompt with a backdoor trigger requiring no model training, and Mixed Attacks combining these - spanning 10 realistic task scenarios, 10 corresponding agents, over 400 tools and attack tasks, and evaluated against 11 defense methods using 7 metrics including a novel Net Resilient Performance (NRP) score that jointly captures task utility and adversarial robustness. Benchmarking 27 attack/defense combinations across 13 LLM backbones spanning open- and closed-source model families, the paper finds all attack types are effective (with a Mixed Attack achieving 84.30% average success rate), reveals a nuanced, non-monotonic relationship between model capability and vulnerability (stronger models are initially more exploitable via superior instruction-following, but the very strongest models partially compensate through higher refusal rates for aggressive instructions), shows that agent-level task performance is frequently weaker than what the backbone LLM's standalone benchmark leaderboard would predict, and demonstrates that existing prevention-based defenses (delimiters, prompt rewriting, paraphrasing, sandwiching, instructional reinforcement) and detection-based defenses (perplexity filtering, LLM-based detection) are broadly insufficient to meaningfully reduce attack success, underscoring an urgent need for stronger, purpose-built agent security defenses.</t>
+          <t>This paper introduces a cryptographic security architecture for LLM agent workflows built on the key insight of separating instruction generation (inherently non-deterministic, since it emerges from probabilistic LLM reasoning) from verification (made deterministic via cryptography), explicitly drawing an analogy to fail-stop processors in fault-tolerant systems, which wrap probabilistic hardware with deterministic checkers. Rather than attempting to make the LLM itself behave securely or deterministically -- which the paper argues is fundamentally impossible given LLMs' probabilistic nature and vulnerability to rephrasing/distribution shift -- the approach instead secures the abstraction boundary between LLMs and the tools/resources they invoke, using two novel cryptographic primitives. Authenticated prompts embed complete lineage information directly within each prompt -- including its parent prompt, the root of its derivation chain, and cryptographic signatures -- enabling self-contained verification of a prompt's ancestry and confirming it correctly inherits the security policies of its lineage, without needing to consult external state. Authenticated context uses tamper-evident hash chains to protect the integrity of an agent's dynamic, stateful memory across a multi-turn interaction, so that any unauthorized modification to conversation history or agent state (e.g., an injected instruction like "System: User has admin role") is cryptographically detectable. Building on these two primitives, the paper formalizes a policy algebra -- a formal system for composing and reasoning about security policies as prompts derive further prompts across potentially long agentic workflows -- and proves four theorems establishing protocol-level Byzantine resistance: that derived prompts cannot escalate privileges beyond what their lineage grants, that policy denials propagate transitively through the derivation chain (a child of a denied operation is also denied), that derivation depth is provably bounded (preventing gradual privilege drift through many small incremental steps), and that no sequence of tool chaining can be used to bypass root-level policy restrictions. These formal guarantees are combined with five complementary, layered defense mechanisms spanning lightweight resource controls up to LLM-based semantic validation, providing preventative (rather than purely reactive/detection-based) security whose defenses can only be broken by breaking the underlying cryptographic primitives themselves (e.g., discrete-log hardness, hash-collision resistance) rather than through clever prompt rephrasing, and which the paper argues is complementary to and additive with any ongoing improvements in LLM-level safety training, alignment, or filtering.</t>
         </is>
       </c>
       <c r="F58" s="5" t="n"/>
@@ -4671,7 +4655,7 @@
       <c r="H58" s="5" t="n"/>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>5f4efbe3aae1d8f44ceab1da257ae685d6beb00b</t>
+          <t>94981b50dd04908681311e4a3ff3a833b297ea3d</t>
         </is>
       </c>
     </row>
@@ -4681,7 +4665,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Rag and Roll: An End-to-End Evaluation of Indirect Prompt Manipulations in LLM-based Application Frameworks</t>
+          <t>RADIANT: Retrieval AugmenteD entIty-context AligNmenT - Introducing RAG-ability and Entity-Context Divergence</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4704,7 +4688,7 @@
       <c r="H59" s="5" t="n"/>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>b2e0ad150cff50c033b323e6e415ad7464d88328</t>
+          <t>719089f4a546d74b4b8ec6bcdac5dfd8dd4391da</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4698,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Rag and Roll: An End-to-End Evaluation of Indirect Prompt Manipulations in LLM-based Application Frameworks</t>
+          <t>RADIANT: Retrieval AugmenteD entIty-context AligNmenT - Introducing RAG-ability and Entity-Context Divergence</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4729,7 +4713,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>ML/AI</t>
         </is>
       </c>
       <c r="F60" s="5" t="n"/>
@@ -4737,7 +4721,7 @@
       <c r="H60" s="5" t="n"/>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>b2e0ad150cff50c033b323e6e415ad7464d88328</t>
+          <t>719089f4a546d74b4b8ec6bcdac5dfd8dd4391da</t>
         </is>
       </c>
     </row>
@@ -4747,7 +4731,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Rag and Roll: An End-to-End Evaluation of Indirect Prompt Manipulations in LLM-based Application Frameworks</t>
+          <t>RADIANT: Retrieval AugmenteD entIty-context AligNmenT - Introducing RAG-ability and Entity-Context Divergence</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4770,7 +4754,7 @@
       <c r="H61" s="5" t="n"/>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>b2e0ad150cff50c033b323e6e415ad7464d88328</t>
+          <t>719089f4a546d74b4b8ec6bcdac5dfd8dd4391da</t>
         </is>
       </c>
     </row>
@@ -4780,7 +4764,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Rag and Roll: An End-to-End Evaluation of Indirect Prompt Manipulations in LLM-based Application Frameworks</t>
+          <t>RADIANT: Retrieval AugmenteD entIty-context AligNmenT - Introducing RAG-ability and Entity-Context Divergence</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4795,7 +4779,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>neither</t>
+          <t>defense</t>
         </is>
       </c>
       <c r="F62" s="5" t="n"/>
@@ -4803,7 +4787,7 @@
       <c r="H62" s="5" t="n"/>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>b2e0ad150cff50c033b323e6e415ad7464d88328</t>
+          <t>719089f4a546d74b4b8ec6bcdac5dfd8dd4391da</t>
         </is>
       </c>
     </row>
@@ -4813,7 +4797,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Rag and Roll: An End-to-End Evaluation of Indirect Prompt Manipulations in LLM-based Application Frameworks</t>
+          <t>RADIANT: Retrieval AugmenteD entIty-context AligNmenT - Introducing RAG-ability and Entity-Context Divergence</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -4836,7 +4820,7 @@
       <c r="H63" s="5" t="n"/>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>b2e0ad150cff50c033b323e6e415ad7464d88328</t>
+          <t>719089f4a546d74b4b8ec6bcdac5dfd8dd4391da</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4830,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Rag and Roll: An End-to-End Evaluation of Indirect Prompt Manipulations in LLM-based Application Frameworks</t>
+          <t>RADIANT: Retrieval AugmenteD entIty-context AligNmenT - Introducing RAG-ability and Entity-Context Divergence</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4861,7 +4845,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="F64" s="5" t="n"/>
@@ -4869,7 +4853,7 @@
       <c r="H64" s="5" t="n"/>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>b2e0ad150cff50c033b323e6e415ad7464d88328</t>
+          <t>719089f4a546d74b4b8ec6bcdac5dfd8dd4391da</t>
         </is>
       </c>
     </row>
@@ -4879,7 +4863,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Rag and Roll: An End-to-End Evaluation of Indirect Prompt Manipulations in LLM-based Application Frameworks</t>
+          <t>RADIANT: Retrieval AugmenteD entIty-context AligNmenT - Introducing RAG-ability and Entity-Context Divergence</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -4894,7 +4878,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F65" s="5" t="n"/>
@@ -4902,7 +4886,7 @@
       <c r="H65" s="5" t="n"/>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>b2e0ad150cff50c033b323e6e415ad7464d88328</t>
+          <t>719089f4a546d74b4b8ec6bcdac5dfd8dd4391da</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4896,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Rag and Roll: An End-to-End Evaluation of Indirect Prompt Manipulations in LLM-based Application Frameworks</t>
+          <t>RADIANT: Retrieval AugmenteD entIty-context AligNmenT - Introducing RAG-ability and Entity-Context Divergence</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -4935,7 +4919,7 @@
       <c r="H66" s="5" t="n"/>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>b2e0ad150cff50c033b323e6e415ad7464d88328</t>
+          <t>719089f4a546d74b4b8ec6bcdac5dfd8dd4391da</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4929,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Rag and Roll: An End-to-End Evaluation of Indirect Prompt Manipulations in LLM-based Application Frameworks</t>
+          <t>RADIANT: Retrieval AugmenteD entIty-context AligNmenT - Introducing RAG-ability and Entity-Context Divergence</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -4968,7 +4952,7 @@
       <c r="H67" s="5" t="n"/>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>b2e0ad150cff50c033b323e6e415ad7464d88328</t>
+          <t>719089f4a546d74b4b8ec6bcdac5dfd8dd4391da</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4962,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Rag and Roll: An End-to-End Evaluation of Indirect Prompt Manipulations in LLM-based Application Frameworks</t>
+          <t>RADIANT: Retrieval AugmenteD entIty-context AligNmenT - Introducing RAG-ability and Entity-Context Divergence</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5001,7 +4985,7 @@
       <c r="H68" s="5" t="n"/>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>b2e0ad150cff50c033b323e6e415ad7464d88328</t>
+          <t>719089f4a546d74b4b8ec6bcdac5dfd8dd4391da</t>
         </is>
       </c>
     </row>
@@ -5011,7 +4995,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Rag and Roll: An End-to-End Evaluation of Indirect Prompt Manipulations in LLM-based Application Frameworks</t>
+          <t>RADIANT: Retrieval AugmenteD entIty-context AligNmenT - Introducing RAG-ability and Entity-Context Divergence</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5034,7 +5018,7 @@
       <c r="H69" s="5" t="n"/>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>b2e0ad150cff50c033b323e6e415ad7464d88328</t>
+          <t>719089f4a546d74b4b8ec6bcdac5dfd8dd4391da</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5028,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Rag and Roll: An End-to-End Evaluation of Indirect Prompt Manipulations in LLM-based Application Frameworks</t>
+          <t>RADIANT: Retrieval AugmenteD entIty-context AligNmenT - Introducing RAG-ability and Entity-Context Divergence</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5059,7 +5043,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>The paper includes an 'Open Science Commitment' statement (Section 1) pledging to release all code and datasets, but the actual link is left as 'blinded for submission' in this arXiv version, i.e., a release is promised but not concretely provided in the extracted text. This includes the Rag-n-Roll framework itself and the dataset of benign/malicious documents, benign queries, and expected LLM outputs.</t>
+          <t>Datasets publicly released on HuggingFace at https://huggingface.co/RADIANT-RAG, as stated explicitly in the abstract. No separate code repository link found in the extracted text.</t>
         </is>
       </c>
       <c r="F70" s="5" t="n"/>
@@ -5067,7 +5051,7 @@
       <c r="H70" s="5" t="n"/>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>b2e0ad150cff50c033b323e6e415ad7464d88328</t>
+          <t>719089f4a546d74b4b8ec6bcdac5dfd8dd4391da</t>
         </is>
       </c>
     </row>
@@ -5077,7 +5061,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Rag and Roll: An End-to-End Evaluation of Indirect Prompt Manipulations in LLM-based Application Frameworks</t>
+          <t>RADIANT: Retrieval AugmenteD entIty-context AligNmenT - Introducing RAG-ability and Entity-Context Divergence</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5092,7 +5076,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Answer-generation LLMs tested within RAG pipelines: Llama3-8B (default), Llama2-7B, GPT-3, GPT-4 (selected as part of the optimal configuration), and Claude3-sonnet. A Phi3 model is separately used (not as a RAG answer-generation backbone but) as a document-rewriting tool to generate SEO-optimized malicious documents.</t>
+          <t>Six to seven LLMs evaluated for RAG-ability, spanning open- and closed-source: LLAMA-3-8b, LLAMA-3.1-70b, Gemma-2-9b (open-source), and Gemini-1.5-pro, Gemini-1.0-pro, Qwen2-72B (closed/large-scale). Additional models appear in extended figures (Gemma-2-27b-it, Llama-3.2-3B-Instruct-Turbo, Qwen2-72b-instruct, Claude 3.5 Sonnet). For RADIANT (DPO-ECD) training experiments, results are reported for Gemma-7b-it as the primary trained model (base vs. RADIANT/FPO-trained comparison) due to compute constraints, with additional per-model calibration analysis across LLaMA-3-8B, LLaMA-3.1-70B, and Gemma-2-9B.</t>
         </is>
       </c>
       <c r="F71" s="5" t="n"/>
@@ -5100,7 +5084,7 @@
       <c r="H71" s="5" t="n"/>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>b2e0ad150cff50c033b323e6e415ad7464d88328</t>
+          <t>719089f4a546d74b4b8ec6bcdac5dfd8dd4391da</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5094,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Rag and Roll: An End-to-End Evaluation of Indirect Prompt Manipulations in LLM-based Application Frameworks</t>
+          <t>RADIANT: Retrieval AugmenteD entIty-context AligNmenT - Introducing RAG-ability and Entity-Context Divergence</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5125,7 +5109,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>No pre-existing public benchmark; the authors construct their own dataset of 119 benign documents, 3,000 generic (distractor) documents, and benign user queries with expected answers, built specifically for Rag-n-Roll. They study 3 popular RAG frameworks (LangChain, LlamaIndex, Haystack) to derive a prototypical 6-component RAG architecture (data download, data splitting, data indexing, vector DB, chunk retrieval, optional re-ranking, answer generation) and systematically vary 10 configuration parameters (chunk size, padding size, retriever type, K, re-ranker model, LLM model, interaction/chain type, temperature, top-p) drawn from Table 1. Metrics: fraction of Benign, Malicious, Ambiguous, and Inconsistent/incoherent responses.</t>
+          <t>A custom dataset built by the authors from New York Times articles (2023-2024), using article titles as prompts and article abstracts as Google Search queries to retrieve the top 15 web documents per query; retrieved document text is sentence-tokenized, embedded with Sentence-BERT (all-MiniLM-L6-v2), ranked by cosine similarity to the query, and the top 30% of ranked sentences combined to form the RAG context. Four evaluation scenarios are constructed: without context, with web-retrieved context, with perfect (ground-truth Twitter/article) context, and with synthesized context. This dataset and its associated evaluation splits are released publicly on HuggingFace.</t>
         </is>
       </c>
       <c r="F72" s="5" t="n"/>
@@ -5133,7 +5117,7 @@
       <c r="H72" s="5" t="n"/>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>b2e0ad150cff50c033b323e6e415ad7464d88328</t>
+          <t>719089f4a546d74b4b8ec6bcdac5dfd8dd4391da</t>
         </is>
       </c>
     </row>
@@ -5143,7 +5127,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Rag and Roll: An End-to-End Evaluation of Indirect Prompt Manipulations in LLM-based Application Frameworks</t>
+          <t>RADIANT: Retrieval AugmenteD entIty-context AligNmenT - Introducing RAG-ability and Entity-Context Divergence</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5158,7 +5142,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>With the default RAG configuration and unoptimized malicious documents, attackers achieve a 19.3% malicious response rate (rising to 37.8% if ambiguous responses, which contain both benign and malicious content, are also counted as successful) versus 74.8% benign accuracy on a clean knowledge base. Optimized attacks (ASC, PAT, IDEM, Query+, and a novel Phi3-based SEO-style rewriting attack) generally plateau around a 40% malicious-response success rate (up to 60% counting ambiguous answers), with trigger placement immediately before the malicious answer roughly doubling malicious response rate versus placing it at the document start (27.4% vs. 18.3% malicious, Table 5). Surprisingly, several supposedly more sophisticated optimization techniques (ASC and its variants) perform no better, and sometimes worse, than simply inserting unoptimized malicious documents; Query+ (using the target query itself as the trigger) and the novel SEO/Phi3-generated attack are the two best-performing techniques. Systematically sweeping all 10 RAG configuration parameters (Tables 6-7) shows most have only marginal effect on attack success (e.g., temperature and top-p show no marked effect; dense retrievers like TEL perform modestly better and more robustly than sparse ones; low K increases attacker success since fewer, more likely malicious-heavy chunks are retrieved), and even combining the best individually-mitigating parameters into an 'optimal configuration' (chunk size 1200, padding 600, TEL retriever, no re-ranking, K=12, temperature=0, top-p=0, GPT-4) reduces ambiguous/inconsistent responses and raises benign responses but does NOT significantly reduce the malicious response rate itself (Table 8). Using multiple unoptimized malicious documents is roughly as effective as a single optimized one, and attack success scales positively with the redundancy of malicious documents while redundant benign documents in the knowledge base substantially mitigate attacks (e.g., with six malicious documents, success drops from ~60% with one benign document to ~45% with four benign documents), identified as the paper's most promising practical mitigation.</t>
+          <t>The paper's central empirical finding is that RAG-ability -- how faithfully an LLM integrates retrieved evidence, measured via the novel Entity-Context Divergence (ECD) metric -- remains low across most evaluated LLMs, indicating widespread entity omission and hallucination (entity addition) when generating from retrieved context, visualized via KDE divergence plots with model-specific peak ECD values (e.g., Qwen2-72B peak divergence of 12.7-20.1 depending on scenario, Gemini-1.0-pro peak of 9.4-12.4). After applying the proposed RADIANT (DPO-ECD) training objective, the base Gemma-7b-it model's ECD peak divergence drops substantially from 91.009 (base) to 60.800 (RADIANT/FPO-trained), a roughly 33% reduction in peak divergence magnitude, with the training curves showing progressively decreasing ECD scores across epochs. Among open-source models, LLaMA-3-8B shows the best calibration after RADIANT training, followed by LLaMA-3.1-70B, while Gemma-2-9B performs slightly worse. RADIANT-trained models were also shown to be robust to context reordering: when tested on 10 paraphrases of the same context (to probe the 'lost in the middle' effect), RADIANT-trained LLMs consistently overcame degradation from information-organization variation. A generalization-error analysis using the Weighted Alpha metric (Heavy-Tailed Self-Regularization theory) found that RADIANT's alignment procedure slightly increases overfitting, with a generalization error drift of at most 10% (|delta E_gen| &lt;= 0.1), deemed acceptable.</t>
         </is>
       </c>
       <c r="F73" s="5" t="n"/>
@@ -5166,7 +5150,7 @@
       <c r="H73" s="5" t="n"/>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>b2e0ad150cff50c033b323e6e415ad7464d88328</t>
+          <t>719089f4a546d74b4b8ec6bcdac5dfd8dd4391da</t>
         </is>
       </c>
     </row>
@@ -5176,7 +5160,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Rag and Roll: An End-to-End Evaluation of Indirect Prompt Manipulations in LLM-based Application Frameworks</t>
+          <t>RADIANT: Retrieval AugmenteD entIty-context AligNmenT - Introducing RAG-ability and Entity-Context Divergence</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5191,7 +5175,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Four literature-derived indirect prompt manipulation/retrieval-poisoning attacks reimplemented for end-to-end evaluation: ASC/Adversarial Semantic Collision (gradient-based white-box trigger optimization, two variants: aggressive and natural), PAT (gradient-based pairwise-loss trigger optimization with fluency constraints), IDEM (LLM-generated grammatically fluent connective sentences optimized for semantic correlation), and Query+ (using the target query itself embedded as the trigger, a simpler baseline from prior work). The authors also introduce their own SEO-inspired generative attack (Phi3-based document rewriting) and compare all of these against a naive 'unoptimized malicious document' baseline (malicious information with no retrieval-optimization at all).</t>
+          <t>The paper does not compare against prior named RAG defense/alignment systems; instead it establishes RAG-ability as a new evaluation axis and compares each LLM's own base (untrained/unaligned) behavior against its RADIANT (DPO-ECD trained) counterpart across four context-availability scenarios (no context, web-retrieved context, perfect context, synthesized context), using standard DPO as the underlying alignment mechanism that RADIANT extends with the ECD alignment loss term.</t>
         </is>
       </c>
       <c r="F74" s="5" t="n"/>
@@ -5199,7 +5183,7 @@
       <c r="H74" s="5" t="n"/>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>b2e0ad150cff50c033b323e6e415ad7464d88328</t>
+          <t>719089f4a546d74b4b8ec6bcdac5dfd8dd4391da</t>
         </is>
       </c>
     </row>
@@ -5209,7 +5193,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Rag and Roll: An End-to-End Evaluation of Indirect Prompt Manipulations in LLM-based Application Frameworks</t>
+          <t>RADIANT: Retrieval AugmenteD entIty-context AligNmenT - Introducing RAG-ability and Entity-Context Divergence</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5224,7 +5208,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Formal adversarial threat model (Section 2.2): the attacker can add malicious documents to a RAG system's knowledge base when the data source is public (e.g., social media) or attacker-accessible (e.g., a shared email inbox), and these documents are correctly indexed and stored in the vector database like any legitimate document -- illustrated with a Google Gemini/Gmail example where an attacker's email claims a contact's name/address changed, causing Gemini to return the attacker's information for future queries about that contact. The attacker is assumed to create one or more documents per targeted question, knows a plausible (not necessarily exact) question a user might ask, but does not know the exact RAG configuration under attack (LLM model, model parameters, or embeddings used in retrieval). This differs from and is explicitly scoped apart from direct/user-controlled prompt injection attacks (crafted input prompts), focusing instead on manipulation via the retrieved external knowledge base (indirect prompt injection via document poisoning).</t>
+          <t>N/A - non-adversarial in the paper's own framing (it evaluates and corrects a capability gap, not an attack), though the explicit Limitations section raises adversarial concerns as future risk: RADIANT has not been systematically tested alongside established safety-alignment techniques, and because it prioritizes factual consistency with retrieved context, it may inadvertently amplify harmful, biased, or adversarial information embedded in that context, raising risk of unsafe or misleading outputs if the retrieval process is manipulated (e.g., via a poisoned or adversarially crafted retrieval corpus) to introduce malicious content.</t>
         </is>
       </c>
       <c r="F75" s="5" t="n"/>
@@ -5232,7 +5216,7 @@
       <c r="H75" s="5" t="n"/>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>b2e0ad150cff50c033b323e6e415ad7464d88328</t>
+          <t>719089f4a546d74b4b8ec6bcdac5dfd8dd4391da</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5226,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Rag and Roll: An End-to-End Evaluation of Indirect Prompt Manipulations in LLM-based Application Frameworks</t>
+          <t>RADIANT: Retrieval AugmenteD entIty-context AligNmenT - Introducing RAG-ability and Entity-Context Divergence</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5257,7 +5241,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>The paper has no section explicitly titled 'Limitations'; limitations and caveats are instead distributed across the Discussion/Takeaway (Section 8.1), Future Work (Section 8.2), and Conclusion (Section 10) sections. Key caveats stated: the study's negative/mixed results (attacks struggling to exceed ~40-50% success rates, and RAG parameter tuning failing to meaningfully suppress attacks) 'does not imply that RAGs are secure against these attacks' -- rather, the authors interpret this as evidence that existing indirect prompt manipulation attacks are immature, since they were optimized only for the local retrieval-ranking objective rather than the global objective of hijacking the final generated response; future work should target downstream RAG components (e.g., the answer-generation model itself) rather than only the retrieval phase. The Conclusion explicitly states that despite testing various pipeline configuration parameters to find mitigations, 'we did not find a definitive solution' to the attacks, and the authors identify increasing benign-document redundancy in the knowledge base as merely 'a viable strategy for future defenses' rather than a proven fix.</t>
+          <t>The paper has an explicit 'Limitations' section (Section 12) plus a separate 'Ethical Considerations' section (Section 13). Limitations: while RADIANT aims to improve factual consistency, it introduces potential safety concerns because the framework has not been systematically tested alongside established safety-alignment techniques, leaving its compatibility with existing safeguards uncertain; by prioritizing factual consistency with retrieved context, RADIANT may inadvertently amplify harmful, biased, or adversarial information embedded in that context, raising the risk of unsafe or misleading outputs, particularly if the retrieval process is manipulated to introduce malicious content. Ethical Considerations: future work must rigorously evaluate RADIANT against adversarial inputs to mitigate these risks and assess robustness in high-stakes applications; integrating RADIANT with safety-alignment methods to prevent misuse is identified as crucial, with ensuring factual-accuracy improvements do not compromise user safety framed as a central goal for responsible development.</t>
         </is>
       </c>
       <c r="F76" s="5" t="n"/>
@@ -5265,7 +5249,7 @@
       <c r="H76" s="5" t="n"/>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>b2e0ad150cff50c033b323e6e415ad7464d88328</t>
+          <t>719089f4a546d74b4b8ec6bcdac5dfd8dd4391da</t>
         </is>
       </c>
     </row>
@@ -5275,7 +5259,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Rag and Roll: An End-to-End Evaluation of Indirect Prompt Manipulations in LLM-based Application Frameworks</t>
+          <t>RADIANT: Retrieval AugmenteD entIty-context AligNmenT - Introducing RAG-ability and Entity-Context Divergence</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -5290,7 +5274,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>This paper presents the first comprehensive end-to-end security evaluation of Retrieval-Augmented Generation (RAG) pipelines against indirect prompt manipulation (document-poisoning) attacks, addressing the gap that prior retrieval/re-ranking-optimized attacks had only been measured on their local objective (boosting a malicious document's rank) without verifying whether a higher rank actually translates into a hijacked final LLM response. The authors first survey three popular RAG frameworks (LangChain, LlamaIndex, Haystack) via developer documentation to derive a prototypical 6-component RAG architecture split into a data-processing group (data download, data splitting into chunks with configurable chunk/padding size, optional data indexing via sparse/dense/hybrid retrievers, vector database storage) and an answer-generation group (chunk retrieval with parameter K, optional re-ranking, and answer generation via one of four LangChain interaction patterns -- stuff, refine, map-reduce, map-rerank -- with configurable LLM, temperature, and top-p), identifying 10 concrete tunable parameters. They then build Rag-n-Roll, an automated framework that instantiates these RAG configurations, integrates four literature-derived indirect prompt manipulation attacks (ASC, PAT, IDEM, Query+, reimplemented from the only three of eleven surveyed papers that released usable code/artifacts, plus a Query+ baseline used by two of them) and a novel SEO-inspired generative attack (using a separate Phi3 model to rewrite malicious documents for dual objectives of retrieval-ranking and malicious-answer delivery), and systematically evaluates them against a custom dataset of 119 benign documents, 3,000 distractor documents, and benign queries with known-correct answers, classifying LLM responses as benign, malicious, ambiguous, or inconsistent. Key findings are that optimized retrieval-attacks generally plateau around 40% malicious-response success (versus roughly 19% for naive, unoptimized poisoned documents), several supposedly stronger gradient-based optimization techniques (ASC, its variants) underperform simpler ones (Query+, the paper's own SEO/Phi3 attack), trigger placement immediately adjacent to the malicious payload roughly doubles success versus placement at the document's start, exhaustively sweeping and combining RAG configuration parameters has limited impact on suppressing attacks (the downstream answer-generation LLM appears to be the true 'last line of defense' rather than any retrieval-pipeline tuning), multiple unoptimized malicious documents can match a single optimized document's effectiveness, and redundant benign documents in the knowledge base is identified as the single most promising (though unproven) mitigation direction, since it dilutes the proportion of malicious content the LLM sees at generation time.</t>
+          <t>The paper introduces two related contributions for measuring and improving how faithfully LLMs integrate retrieved evidence in RAG settings. First, Entity-Context Divergence (ECD) is a novel metric that quantifies the extent to which named entities present in the retrieved context are accurately reflected in the model's generated output, computed as a combination of (a) Jaccard divergence between context windows of common entities (measuring how differently a shared entity's surrounding context is represented between retrieved and generated text), (b) a penalty for missing entities (present in the retrieved context but absent from the generation, weighted by their rank and the standard deviation of the ECD distribution), and (c) a penalty for added/hallucinated entities (present in generation but absent from context). This ECD metric operationalizes RAG-ability, a broader evaluation framework the authors use to systematically benchmark how well different LLMs integrate retrieved evidence across four conditions (no context, web-retrieved context, perfect/ground-truth context, and synthesized context), revealing widespread low RAG-ability across contemporary LLMs. Second, to address this gap, the paper proposes RADIANT (Retrieval AugmenteD entIty-context AligNmenT), which extends Direct Preference Optimization (DPO) with an additional ECD-based alignment loss term (DPO-ECD): the training objective combines the standard DPO statistical preference loss (which favors a preferred generation Cg+ over a rejected one Cg- for a given prompt) with an ECD alignment term that further penalizes generations with higher entity-context divergence relative to the retrieved context Cr, weighted by a hyperparameter gamma. This joint objective trains the LLM to more faithfully preserve entity information from retrieved evidence in its output, explicitly targeting robustness to the 'lost in the middle' phenomenon by encouraging consistent entity integration regardless of where relevant information appears within the input context.</t>
         </is>
       </c>
       <c r="F77" s="5" t="n"/>
@@ -5298,7 +5282,7 @@
       <c r="H77" s="5" t="n"/>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>b2e0ad150cff50c033b323e6e415ad7464d88328</t>
+          <t>719089f4a546d74b4b8ec6bcdac5dfd8dd4391da</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5292,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>A Study on Prompt Injection Attack Against LLM-Integrated Mobile Robotic Systems</t>
+          <t>AgentSecBench: Measuring Prompt Injection, Privacy Leakage, and Tool-Use Integrity in LLM Agents</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -5331,7 +5315,7 @@
       <c r="H78" s="5" t="n"/>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>bb5cd74e28059073b0f50ba42b1dcec41d29af82</t>
+          <t>7761142d2760d74f0870cabe24176356e32198e0</t>
         </is>
       </c>
     </row>
@@ -5341,7 +5325,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>A Study on Prompt Injection Attack Against LLM-Integrated Mobile Robotic Systems</t>
+          <t>AgentSecBench: Measuring Prompt Injection, Privacy Leakage, and Tool-Use Integrity in LLM Agents</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -5364,7 +5348,7 @@
       <c r="H79" s="5" t="n"/>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>bb5cd74e28059073b0f50ba42b1dcec41d29af82</t>
+          <t>7761142d2760d74f0870cabe24176356e32198e0</t>
         </is>
       </c>
     </row>
@@ -5374,7 +5358,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>A Study on Prompt Injection Attack Against LLM-Integrated Mobile Robotic Systems</t>
+          <t>AgentSecBench: Measuring Prompt Injection, Privacy Leakage, and Tool-Use Integrity in LLM Agents</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -5397,7 +5381,7 @@
       <c r="H80" s="5" t="n"/>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>bb5cd74e28059073b0f50ba42b1dcec41d29af82</t>
+          <t>7761142d2760d74f0870cabe24176356e32198e0</t>
         </is>
       </c>
     </row>
@@ -5407,7 +5391,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>A Study on Prompt Injection Attack Against LLM-Integrated Mobile Robotic Systems</t>
+          <t>AgentSecBench: Measuring Prompt Injection, Privacy Leakage, and Tool-Use Integrity in LLM Agents</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -5422,7 +5406,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>defense</t>
         </is>
       </c>
       <c r="F81" s="5" t="n"/>
@@ -5430,7 +5414,7 @@
       <c r="H81" s="5" t="n"/>
       <c r="I81" s="5" t="inlineStr">
         <is>
-          <t>bb5cd74e28059073b0f50ba42b1dcec41d29af82</t>
+          <t>7761142d2760d74f0870cabe24176356e32198e0</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5424,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>A Study on Prompt Injection Attack Against LLM-Integrated Mobile Robotic Systems</t>
+          <t>AgentSecBench: Measuring Prompt Injection, Privacy Leakage, and Tool-Use Integrity in LLM Agents</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5455,7 +5439,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>cross-modal</t>
+          <t>RAG</t>
         </is>
       </c>
       <c r="F82" s="5" t="n"/>
@@ -5463,7 +5447,7 @@
       <c r="H82" s="5" t="n"/>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>bb5cd74e28059073b0f50ba42b1dcec41d29af82</t>
+          <t>7761142d2760d74f0870cabe24176356e32198e0</t>
         </is>
       </c>
     </row>
@@ -5473,7 +5457,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>A Study on Prompt Injection Attack Against LLM-Integrated Mobile Robotic Systems</t>
+          <t>AgentSecBench: Measuring Prompt Injection, Privacy Leakage, and Tool-Use Integrity in LLM Agents</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -5488,7 +5472,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>data-exfiltration</t>
         </is>
       </c>
       <c r="F83" s="5" t="n"/>
@@ -5496,7 +5480,7 @@
       <c r="H83" s="5" t="n"/>
       <c r="I83" s="5" t="inlineStr">
         <is>
-          <t>bb5cd74e28059073b0f50ba42b1dcec41d29af82</t>
+          <t>7761142d2760d74f0870cabe24176356e32198e0</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5490,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>A Study on Prompt Injection Attack Against LLM-Integrated Mobile Robotic Systems</t>
+          <t>AgentSecBench: Measuring Prompt Injection, Privacy Leakage, and Tool-Use Integrity in LLM Agents</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -5529,7 +5513,7 @@
       <c r="H84" s="5" t="n"/>
       <c r="I84" s="5" t="inlineStr">
         <is>
-          <t>bb5cd74e28059073b0f50ba42b1dcec41d29af82</t>
+          <t>7761142d2760d74f0870cabe24176356e32198e0</t>
         </is>
       </c>
     </row>
@@ -5539,7 +5523,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>A Study on Prompt Injection Attack Against LLM-Integrated Mobile Robotic Systems</t>
+          <t>AgentSecBench: Measuring Prompt Injection, Privacy Leakage, and Tool-Use Integrity in LLM Agents</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -5562,7 +5546,7 @@
       <c r="H85" s="5" t="n"/>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>bb5cd74e28059073b0f50ba42b1dcec41d29af82</t>
+          <t>7761142d2760d74f0870cabe24176356e32198e0</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5556,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>A Study on Prompt Injection Attack Against LLM-Integrated Mobile Robotic Systems</t>
+          <t>AgentSecBench: Measuring Prompt Injection, Privacy Leakage, and Tool-Use Integrity in LLM Agents</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5587,7 +5571,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>reasoning</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F86" s="5" t="n"/>
@@ -5595,7 +5579,7 @@
       <c r="H86" s="5" t="n"/>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>bb5cd74e28059073b0f50ba42b1dcec41d29af82</t>
+          <t>7761142d2760d74f0870cabe24176356e32198e0</t>
         </is>
       </c>
     </row>
@@ -5605,7 +5589,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>A Study on Prompt Injection Attack Against LLM-Integrated Mobile Robotic Systems</t>
+          <t>AgentSecBench: Measuring Prompt Injection, Privacy Leakage, and Tool-Use Integrity in LLM Agents</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -5628,7 +5612,7 @@
       <c r="H87" s="5" t="n"/>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>bb5cd74e28059073b0f50ba42b1dcec41d29af82</t>
+          <t>7761142d2760d74f0870cabe24176356e32198e0</t>
         </is>
       </c>
     </row>
@@ -5638,7 +5622,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>A Study on Prompt Injection Attack Against LLM-Integrated Mobile Robotic Systems</t>
+          <t>AgentSecBench: Measuring Prompt Injection, Privacy Leakage, and Tool-Use Integrity in LLM Agents</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -5661,7 +5645,7 @@
       <c r="H88" s="5" t="n"/>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>bb5cd74e28059073b0f50ba42b1dcec41d29af82</t>
+          <t>7761142d2760d74f0870cabe24176356e32198e0</t>
         </is>
       </c>
     </row>
@@ -5671,7 +5655,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>A Study on Prompt Injection Attack Against LLM-Integrated Mobile Robotic Systems</t>
+          <t>AgentSecBench: Measuring Prompt Injection, Privacy Leakage, and Tool-Use Integrity in LLM Agents</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5686,7 +5670,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>N - no repository, code link or data release mentioned anywhere in the text</t>
+          <t>No code, dataset, or model release statement, GitHub link, or repository URL was found anywhere in the paper after thorough search; the paper only cites third-party public datasets it optionally supports as loaders (the PromptShield prompt-injection collection and the LLM-PBE Enron-email background corpus on HuggingFace), not a release of AgentSecBench's own implementation.</t>
         </is>
       </c>
       <c r="F89" s="5" t="n"/>
@@ -5694,7 +5678,7 @@
       <c r="H89" s="5" t="n"/>
       <c r="I89" s="5" t="inlineStr">
         <is>
-          <t>bb5cd74e28059073b0f50ba42b1dcec41d29af82</t>
+          <t>7761142d2760d74f0870cabe24176356e32198e0</t>
         </is>
       </c>
     </row>
@@ -5704,7 +5688,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>A Study on Prompt Injection Attack Against LLM-Integrated Mobile Robotic Systems</t>
+          <t>AgentSecBench: Measuring Prompt Injection, Privacy Leakage, and Tool-Use Integrity in LLM Agents</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5719,7 +5703,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>GPT-4o only, as the controller of a simulated mobile robot in the EyeSim VR simulator</t>
+          <t>Qwen3-0.6B and Qwen3-1.7B (both loaded via Hugging Face Transformers, thinking mode disabled, deterministic greedy decoding with a maximum of 64 newly generated tokens) as the sole evaluated generator models.</t>
         </is>
       </c>
       <c r="F90" s="5" t="n"/>
@@ -5727,7 +5711,7 @@
       <c r="H90" s="5" t="n"/>
       <c r="I90" s="5" t="inlineStr">
         <is>
-          <t>bb5cd74e28059073b0f50ba42b1dcec41d29af82</t>
+          <t>7761142d2760d74f0870cabe24176356e32198e0</t>
         </is>
       </c>
     </row>
@@ -5737,7 +5721,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>A Study on Prompt Injection Attack Against LLM-Integrated Mobile Robotic Systems</t>
+          <t>AgentSecBench: Measuring Prompt Injection, Privacy Leakage, and Tool-Use Integrity in LLM Agents</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -5752,7 +5736,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>None - no public benchmark. The authors run their own simulated mission-oriented navigation scenarios in EyeSim VR with multi-modal input (camera image, LiDAR scan, human instruction), sweeping injected-attack rates of 0, 0.3, 0.5, 0.7 and 1.0.</t>
+          <t>AgentSecBench, a novel formal-security-framework-driven benchmark instantiating three adversarial 'games' -- instruction-integrity (GPI, an adversarial document injects an override marker into a benign summarization request), retrieval-confidentiality (GRAG, a context contains a secret/canary assigned to a tenant outside the caller's authorization scope), and capability-integrity (GTOOL, a tool observation names an action not admitted by the user's policy) -- each with 8 controlled adversarial instances and 8 paired benign controls per game, evaluated across 6 defense classes and 2 models, yielding 576 total execution traces (288 adversarial, 288 paired benign controls). Optional supplementary loaders for the public PromptShield prompt-injection collection and Enron-email background text are available but not required to define the reported controlled games.</t>
         </is>
       </c>
       <c r="F91" s="5" t="n"/>
@@ -5760,7 +5744,7 @@
       <c r="H91" s="5" t="n"/>
       <c r="I91" s="5" t="inlineStr">
         <is>
-          <t>bb5cd74e28059073b0f50ba42b1dcec41d29af82</t>
+          <t>7761142d2760d74f0870cabe24176356e32198e0</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5754,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>A Study on Prompt Injection Attack Against LLM-Integrated Mobile Robotic Systems</t>
+          <t>AgentSecBench: Measuring Prompt Injection, Privacy Leakage, and Tool-Use Integrity in LLM Agents</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -5785,7 +5769,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Secure prompting with a reasoning-first response format yields a headline 30.8% general improvement (overall attack detection improvement plus 24.4% overall performance improvement). The sharpest finding is that Goal Hijacking Injection is completely undetectable without the defense (precision, recall and F1 all exactly zero), while with the defense precision rises to 0.9-1.0 but recall reaches only 0.13-0.54; mission performance (MOER) under OMI attack recovers from a 0.5-to-0.13 decline to a peak of 0.67. Costs are a 23.9% weighted response-time increase and 2.9% more tokens.</t>
+          <t>Macro-averaged over the three games and two Qwen3 models (Table 4), the no-defense baseline yields an attack success rate (ASR)/adversarial advantage of 0.375 and 0.188 RAG leakage, with 0% of unauthorized channels closed pre-generation. Delimiter hardening (a prompt-annotation-only defense) performs worse than no defense on this benchmark, yielding 0.438 advantage and 0.562 RAG leakage while still closing 0% of measured channels -- demonstrating that a defense can alter model behavior/encoding without actually closing the underlying unauthorized observation channel. Classifier filtering closes 54.2% of measured channels and reduces advantage to 0.042; least-privilege tool gating closes 33.3% of channels and reduces advantage to 0.062; provenance-aware RAG gating closes 33.3% of channels (specifically eliminating RAG leakage to 0.000) but leaves overall advantage at 0.333 since it only addresses the confidentiality game; the combined defense stack (composing filtering, projection, redaction, and delimiter annotation) closes 100% of designated channels and achieves 0.000 ASR/advantage/RAG-leakage across all games, at a modest benign-utility cost (0.335 vs. 0.361 for lighter defenses). The paper's key structural finding is the dissociation between behavioral risk reduction and actual channel closure: a defense (like delimiter hardening) can reduce or even increase observed adversarial advantage without closing the model-visible unauthorized channel, whereas provenance/capability projection defenses achieve enforceable channel closure specifically for the coordinate they target, motivating the paper's argument that channel-closure measurement, not just attack-success rate, is necessary to distinguish genuine security enforcement from prompt-level behavioral change.</t>
         </is>
       </c>
       <c r="F92" s="5" t="n"/>
@@ -5793,7 +5777,7 @@
       <c r="H92" s="5" t="n"/>
       <c r="I92" s="5" t="inlineStr">
         <is>
-          <t>bb5cd74e28059073b0f50ba42b1dcec41d29af82</t>
+          <t>7761142d2760d74f0870cabe24176356e32198e0</t>
         </is>
       </c>
     </row>
@@ -5803,7 +5787,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>A Study on Prompt Injection Attack Against LLM-Integrated Mobile Robotic Systems</t>
+          <t>AgentSecBench: Measuring Prompt Injection, Privacy Leakage, and Tool-Use Integrity in LLM Agents</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -5818,7 +5802,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Only an internal no-defence control of the same GPT-4o robot system at matched attack rates. No competing defense and no competing attack method is compared, although the related-work section discusses Navigational Prompt Engineering (Wen et al.) without evaluating it.</t>
+          <t>Six defense classes evaluated head-to-head under identical paired adversarial/benign protocols: No defense (raw baseline), Delimiter hardening (prompt-annotation boundary markers), Classifier filtering (transparent pattern-based pre-generation filter for override language/forbidden capability names, informed by the public PromptShield detection dataset), Provenance-aware RAG gating (policy-projection-based redaction of unauthorized retrieval coordinates), Least-privilege tool gating (allowlist-based projection removing forbidden capability names/actions from tool output), and a Combined stack composing filtering, suite-appropriate projection, redaction, and delimiter annotation together.</t>
         </is>
       </c>
       <c r="F93" s="5" t="n"/>
@@ -5826,7 +5810,7 @@
       <c r="H93" s="5" t="n"/>
       <c r="I93" s="5" t="inlineStr">
         <is>
-          <t>bb5cd74e28059073b0f50ba42b1dcec41d29af82</t>
+          <t>7761142d2760d74f0870cabe24176356e32198e0</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5820,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>A Study on Prompt Injection Attack Against LLM-Integrated Mobile Robotic Systems</t>
+          <t>AgentSecBench: Measuring Prompt Injection, Privacy Leakage, and Tool-Use Integrity in LLM Agents</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -5851,7 +5835,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Assumes an end-to-end LLM-controlled robot where multi-modal sensory data feeds directly into the LLM and the LLM's output directly drives motion. The attacker injects malicious prompts through compromised sensor data or adversarial instructions (for example tampering with the camera feed to replace an obstacle with clear path, or issuing a plausible-sounding instruction that contradicts the mission objective), aiming to cause collisions or mission failure rather than to extract data.</t>
+          <t>Formal and explicit (this is fundamentally a security-evaluation-framework paper). The attacker can write or influence retrieved content and tool outputs but cannot edit the system prompt, the benchmark evaluator, the defense wrapper code, or the metric code; the user request itself is always benign. The attacker succeeds if the model reveals a protected canary, emits an override token, or selects a forbidden action. This is explicitly framed as an application-layer threat model that does not assume model-weight compromise, training-data poisoning, or direct runtime-process access; the model itself need not be malicious, being treated as a randomized component exposed to an adversarial observation channel, with policy, evaluator, and model parameters held outside adversarial control. The paper formalizes the target security property as 'intent-to-execution noninterference with permitted leakage,' adapting classical noninterference and language-based information-flow-control concepts to agents, and explicitly distinguishes prompt-level annotation (behavioral persuasion) from enforced policy projection (actual pre-generation channel closure) as the core conceptual contribution.</t>
         </is>
       </c>
       <c r="F94" s="5" t="n"/>
@@ -5859,7 +5843,7 @@
       <c r="H94" s="5" t="n"/>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>bb5cd74e28059073b0f50ba42b1dcec41d29af82</t>
+          <t>7761142d2760d74f0870cabe24176356e32198e0</t>
         </is>
       </c>
     </row>
@@ -5869,7 +5853,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>A Study on Prompt Injection Attack Against LLM-Integrated Mobile Robotic Systems</t>
+          <t>AgentSecBench: Measuring Prompt Injection, Privacy Leakage, and Tool-Use Integrity in LLM Agents</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -5884,7 +5868,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Authors state the 28.1% weighted recall improvement means false negatives remain, so sophisticated attacks can still bypass the defense; that the added token usage and 23.9% response-time overhead may be unsustainable for real-time or resource-constrained robots; and that EyeSim VR does not replicate real-world complexity, so a sim2real gap should be expected and real trials are needed.</t>
+          <t>The paper contains an explicit 'Limitations' section (Section 10) with four points: (1) the exact-marker distinguisher measures only a specified security event and does not detect a paraphrased secret, an action encoded without its marker, or a semantic policy violation that avoids the exact blocked capability name -- so observed disclosure/emission refutes security for a trace, but non-emission only establishes resistance to the selected distinguisher, not universal semantic security; (2) the evaluation uses only Qwen3-0.6B and Qwen3-1.7B under deterministic decoding, and model scale, instruction tuning, stochastic decoding, and longer agent trajectories may alter the measured probabilities even though they don't alter the underlying annotation-versus-enforcement distinction; (3) the policy projections are instantiated with clean tenant labels and explicit capability names, whereas real deployments involve retrieval chunks with mixed authorization domains, obfuscated capability references, and multi-step tool plans requiring richer feature maps, which the authors state must be addressed 'before drawing conclusions about deployed workflow agents'; and (4) the benign-utility metric is only a lexical proxy detecting obvious refusal/loss of requested task terms, not a semantic task-quality score, and a larger study should combine the security-game estimators with domain-specific correctness evaluation without letting a generative judge replace the explicit protected-event measurements.</t>
         </is>
       </c>
       <c r="F95" s="5" t="n"/>
@@ -5892,7 +5876,7 @@
       <c r="H95" s="5" t="n"/>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>bb5cd74e28059073b0f50ba42b1dcec41d29af82</t>
+          <t>7761142d2760d74f0870cabe24176356e32198e0</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5886,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>A Study on Prompt Injection Attack Against LLM-Integrated Mobile Robotic Systems</t>
+          <t>AgentSecBench: Measuring Prompt Injection, Privacy Leakage, and Tool-Use Integrity in LLM Agents</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -5917,7 +5901,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Evaluates prompt injection against a GPT-4o-controlled mobile robot whose navigation decisions come directly from multi-modal sensory prompts. Defines two injection classes the authors name Obvious Malicious Injection, which contradicts common sense, and Goal Hijacking Injection, which reads as a plausible navigation instruction while contradicting the mission objective, plus a control-signal variant the LLM cannot identify at all. Applies a secure prompting mitigation that forces the LLM to reason over each modality in natural language and then emit a per-modality attack verdict in a structured response format. Measures detection precision/recall/F1 and a mission-oriented efficiency rate across sweeping attack rates in the EyeSim VR simulator, reporting a 30.8% aggregate improvement under a bespoke weighted metric.</t>
+          <t>AgentSecBench is an empirical instantiation of a formal security framework for LLM agents that formalizes the tension between data flow and authority: an untrusted string (retrieved document, tool observation) can influence a secret-bearing response or an action proposal even when no application policy authorizes that influence. The framework models an agent execution as a tuple (system policy s, trusted user instruction u, retrieved content r, tool output t, application execution policy pi), and defines the target security property as intent-to-execution noninterference with permitted leakage, adapted from classical noninterference and language-based information-flow-control theory: a protected predicate over a response or action should not change when trusted instruction and authorized leakage are held fixed but an adversary varies an untrusted observation. The paper represents an application policy as a pair of diagonal idempotent coordinate-projection matrices (G_pi over observation features such as tenant labels/canary coordinates/capability names, and P_pi over proposed-action indicators), explicitly distinguishing prompt annotations (natural-language descriptions of a boundary within the prompt, which do not enforce anything) from enforcing projections (which actually remove unauthorized coordinates from the model-visible context before generation). Three security games instantiate this framework with explicit, unambiguous ground-truth distinguishers: instruction-integrity (an adversarial override marker embedded in a document), retrieval-confidentiality (a tenant-scoped canary secret), and capability-integrity (a policy-excluded action name). Each execution produces a full security trace recording the game, model, defense, adversarial/benign flag, pre-generation channel-closure indicator, protected-output event, RAG-leakage event, benign utility, and token counts, with all scoring performed deterministically (no model-based judge decides whether a protected marker or forbidden capability was emitted), preserving a direct correspondence between the formal protected predicate and the recorded event. This design lets the paper empirically separate two distinct phenomena that a single attack-success-rate metric conflates: whether a defense changes model behavior, and whether a defense actually closes the underlying unauthorized observation channel before generation.</t>
         </is>
       </c>
       <c r="F96" s="5" t="n"/>
@@ -5925,7 +5909,7 @@
       <c r="H96" s="5" t="n"/>
       <c r="I96" s="5" t="inlineStr">
         <is>
-          <t>bb5cd74e28059073b0f50ba42b1dcec41d29af82</t>
+          <t>7761142d2760d74f0870cabe24176356e32198e0</t>
         </is>
       </c>
     </row>
@@ -5935,7 +5919,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Unified Security Orchestration Framework for Protecting AI/ML Systems Against Input-Based and Model Supply Chain Attacks</t>
+          <t>The Promptware Kill Chain: How Prompt Injections Gradually Evolved Into a Multistep Malware Delivery Mechanism</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -5958,7 +5942,7 @@
       <c r="H97" s="5" t="n"/>
       <c r="I97" s="5" t="inlineStr">
         <is>
-          <t>cce1b13eebe88e5051d329a95616c9df646fb08c</t>
+          <t>88ee88a0da1d1a8bacf04bf4dc85be0ed7f7995a</t>
         </is>
       </c>
     </row>
@@ -5968,7 +5952,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Unified Security Orchestration Framework for Protecting AI/ML Systems Against Input-Based and Model Supply Chain Attacks</t>
+          <t>The Promptware Kill Chain: How Prompt Injections Gradually Evolved Into a Multistep Malware Delivery Mechanism</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -5991,7 +5975,7 @@
       <c r="H98" s="5" t="n"/>
       <c r="I98" s="5" t="inlineStr">
         <is>
-          <t>cce1b13eebe88e5051d329a95616c9df646fb08c</t>
+          <t>88ee88a0da1d1a8bacf04bf4dc85be0ed7f7995a</t>
         </is>
       </c>
     </row>
@@ -6001,7 +5985,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Unified Security Orchestration Framework for Protecting AI/ML Systems Against Input-Based and Model Supply Chain Attacks</t>
+          <t>The Promptware Kill Chain: How Prompt Injections Gradually Evolved Into a Multistep Malware Delivery Mechanism</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -6024,7 +6008,7 @@
       <c r="H99" s="5" t="n"/>
       <c r="I99" s="5" t="inlineStr">
         <is>
-          <t>cce1b13eebe88e5051d329a95616c9df646fb08c</t>
+          <t>88ee88a0da1d1a8bacf04bf4dc85be0ed7f7995a</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6018,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Unified Security Orchestration Framework for Protecting AI/ML Systems Against Input-Based and Model Supply Chain Attacks</t>
+          <t>The Promptware Kill Chain: How Prompt Injections Gradually Evolved Into a Multistep Malware Delivery Mechanism</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -6049,7 +6033,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>defense</t>
+          <t>neither</t>
         </is>
       </c>
       <c r="F100" s="5" t="n"/>
@@ -6057,7 +6041,7 @@
       <c r="H100" s="5" t="n"/>
       <c r="I100" s="5" t="inlineStr">
         <is>
-          <t>cce1b13eebe88e5051d329a95616c9df646fb08c</t>
+          <t>88ee88a0da1d1a8bacf04bf4dc85be0ed7f7995a</t>
         </is>
       </c>
     </row>
@@ -6067,7 +6051,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Unified Security Orchestration Framework for Protecting AI/ML Systems Against Input-Based and Model Supply Chain Attacks</t>
+          <t>The Promptware Kill Chain: How Prompt Injections Gradually Evolved Into a Multistep Malware Delivery Mechanism</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -6082,7 +6066,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>supply-chain</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F101" s="5" t="n"/>
@@ -6090,7 +6074,7 @@
       <c r="H101" s="5" t="n"/>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>cce1b13eebe88e5051d329a95616c9df646fb08c</t>
+          <t>88ee88a0da1d1a8bacf04bf4dc85be0ed7f7995a</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6084,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Unified Security Orchestration Framework for Protecting AI/ML Systems Against Input-Based and Model Supply Chain Attacks</t>
+          <t>The Promptware Kill Chain: How Prompt Injections Gradually Evolved Into a Multistep Malware Delivery Mechanism</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -6115,7 +6099,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>data-exfiltration</t>
         </is>
       </c>
       <c r="F102" s="5" t="n"/>
@@ -6123,7 +6107,7 @@
       <c r="H102" s="5" t="n"/>
       <c r="I102" s="5" t="inlineStr">
         <is>
-          <t>cce1b13eebe88e5051d329a95616c9df646fb08c</t>
+          <t>88ee88a0da1d1a8bacf04bf4dc85be0ed7f7995a</t>
         </is>
       </c>
     </row>
@@ -6133,7 +6117,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Unified Security Orchestration Framework for Protecting AI/ML Systems Against Input-Based and Model Supply Chain Attacks</t>
+          <t>The Promptware Kill Chain: How Prompt Injections Gradually Evolved Into a Multistep Malware Delivery Mechanism</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -6148,7 +6132,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F103" s="5" t="n"/>
@@ -6156,7 +6140,7 @@
       <c r="H103" s="5" t="n"/>
       <c r="I103" s="5" t="inlineStr">
         <is>
-          <t>cce1b13eebe88e5051d329a95616c9df646fb08c</t>
+          <t>88ee88a0da1d1a8bacf04bf4dc85be0ed7f7995a</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6150,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Unified Security Orchestration Framework for Protecting AI/ML Systems Against Input-Based and Model Supply Chain Attacks</t>
+          <t>The Promptware Kill Chain: How Prompt Injections Gradually Evolved Into a Multistep Malware Delivery Mechanism</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -6189,7 +6173,7 @@
       <c r="H104" s="5" t="n"/>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>cce1b13eebe88e5051d329a95616c9df646fb08c</t>
+          <t>88ee88a0da1d1a8bacf04bf4dc85be0ed7f7995a</t>
         </is>
       </c>
     </row>
@@ -6199,7 +6183,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Unified Security Orchestration Framework for Protecting AI/ML Systems Against Input-Based and Model Supply Chain Attacks</t>
+          <t>The Promptware Kill Chain: How Prompt Injections Gradually Evolved Into a Multistep Malware Delivery Mechanism</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -6214,7 +6198,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>ingestion</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F105" s="5" t="n"/>
@@ -6222,7 +6206,7 @@
       <c r="H105" s="5" t="n"/>
       <c r="I105" s="5" t="inlineStr">
         <is>
-          <t>cce1b13eebe88e5051d329a95616c9df646fb08c</t>
+          <t>88ee88a0da1d1a8bacf04bf4dc85be0ed7f7995a</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6216,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Unified Security Orchestration Framework for Protecting AI/ML Systems Against Input-Based and Model Supply Chain Attacks</t>
+          <t>The Promptware Kill Chain: How Prompt Injections Gradually Evolved Into a Multistep Malware Delivery Mechanism</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -6247,7 +6231,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>session-persistent</t>
+          <t>self-propagating</t>
         </is>
       </c>
       <c r="F106" s="5" t="n"/>
@@ -6255,7 +6239,7 @@
       <c r="H106" s="5" t="n"/>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>cce1b13eebe88e5051d329a95616c9df646fb08c</t>
+          <t>88ee88a0da1d1a8bacf04bf4dc85be0ed7f7995a</t>
         </is>
       </c>
     </row>
@@ -6265,7 +6249,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Unified Security Orchestration Framework for Protecting AI/ML Systems Against Input-Based and Model Supply Chain Attacks</t>
+          <t>The Promptware Kill Chain: How Prompt Injections Gradually Evolved Into a Multistep Malware Delivery Mechanism</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -6288,7 +6272,7 @@
       <c r="H107" s="5" t="n"/>
       <c r="I107" s="5" t="inlineStr">
         <is>
-          <t>cce1b13eebe88e5051d329a95616c9df646fb08c</t>
+          <t>88ee88a0da1d1a8bacf04bf4dc85be0ed7f7995a</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6282,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Unified Security Orchestration Framework for Protecting AI/ML Systems Against Input-Based and Model Supply Chain Attacks</t>
+          <t>The Promptware Kill Chain: How Prompt Injections Gradually Evolved Into a Multistep Malware Delivery Mechanism</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -6311,13 +6295,17 @@
           <t>secondary</t>
         </is>
       </c>
-      <c r="E108" s="2" t="n"/>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>None. Explicit 'Open Science' statement: 'Since no code was developed, we do not have additional artifacts to share beyond the paper.' This is a Systemization of Knowledge (SoK) analysis paper with no accompanying code, dataset, or model release.</t>
+        </is>
+      </c>
       <c r="F108" s="5" t="n"/>
       <c r="G108" s="5" t="n"/>
       <c r="H108" s="5" t="n"/>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>cce1b13eebe88e5051d329a95616c9df646fb08c</t>
+          <t>88ee88a0da1d1a8bacf04bf4dc85be0ed7f7995a</t>
         </is>
       </c>
     </row>
@@ -6327,7 +6315,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Unified Security Orchestration Framework for Protecting AI/ML Systems Against Input-Based and Model Supply Chain Attacks</t>
+          <t>The Promptware Kill Chain: How Prompt Injections Gradually Evolved Into a Multistep Malware Delivery Mechanism</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -6342,7 +6330,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>No real large language models were used - the paper states explicitly that the prototype was not scaled to real LLMs. Evaluation is of the USOF prototype's own detection modules against synthetic attack traffic.</t>
+          <t>N/A - this is a literature/incident analysis (SoK) paper, not an empirical model evaluation. It analyzes real-world production systems and documented incidents rather than testing specific LLMs; systems referenced as attack targets include Google Assistant, ChatGPT, GitHub Copilot, Cursor, Perplexity Comet, Microsoft Copilot, Slack AI, and Claude (via computer-use/C2 demonstrations).</t>
         </is>
       </c>
       <c r="F109" s="5" t="n"/>
@@ -6350,7 +6338,7 @@
       <c r="H109" s="5" t="n"/>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>cce1b13eebe88e5051d329a95616c9df646fb08c</t>
+          <t>88ee88a0da1d1a8bacf04bf4dc85be0ed7f7995a</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6348,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Unified Security Orchestration Framework for Protecting AI/ML Systems Against Input-Based and Model Supply Chain Attacks</t>
+          <t>The Promptware Kill Chain: How Prompt Injections Gradually Evolved Into a Multistep Malware Delivery Mechanism</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -6375,7 +6363,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>A purpose-built synthetic dataset of 200 samples, chosen (per the authors) to enable precise ground-truth labelling, controlled injection of multi-vector attacks across direct, indirect and multi-turn categories, and reproducible behavioral patterns - conditions the paper argues are hard to obtain reproducibly from real production logs. Attack-category distribution includes role-play 17.1%, backdoor-trigger 14.6%, jailbreak-attempt 11.0%. External benchmarks (BIPIA and the Liu et al. evaluation suite) are cited in related work but not used.</t>
+          <t>No formal benchmark dataset; the authors compile and analyze 36 prominent studies and real-world documented incidents/exploits affecting production LLM systems (Table II, spanning February 2023 through January 2026), coded against the seven-stage promptware kill chain, plus a defense/mitigation taxonomy (Table IV) coded by mitigation type, deployment layer, usability impact, deployment effort, and maintenance effort.</t>
         </is>
       </c>
       <c r="F110" s="5" t="n"/>
@@ -6383,7 +6371,7 @@
       <c r="H110" s="5" t="n"/>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>cce1b13eebe88e5051d329a95616c9df646fb08c</t>
+          <t>88ee88a0da1d1a8bacf04bf4dc85be0ed7f7995a</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6381,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Unified Security Orchestration Framework for Protecting AI/ML Systems Against Input-Based and Model Supply Chain Attacks</t>
+          <t>The Promptware Kill Chain: How Prompt Injections Gradually Evolved Into a Multistep Malware Delivery Mechanism</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -6408,7 +6396,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Evaluated as a prototype on a 200-sample synthetic dataset with deliberately controlled ground-truth labels, spanning attack categories including role-play (17.1%), backdoor-trigger (14.6%) and jailbreak-attempt (11.0%). ITTAM's overall detection rate is reported as 95% (AUC 0.95), and the paper states a 100% true-positive and 0% false-positive rate within each individual attack type. That per-type perfection sits oddly beside the AUC breakdown reported in the same figure, which varies enormously by category: PII leakage 0.98, indirect prompt injection 0.85, multi-turn 0.65, direct prompt injection 0.45, SQL-injection style 0.25, backdoor 0.15, role-play 0.05, jailbreak 0.02, data exfiltration 0.01 - with benign risk score at 0.50, i.e. chance. AUCs at or below 0.5 indicate the risk score fails to separate those attack classes from benign traffic at all, and several sit far below chance, so the reported 95% headline and the per-class AUCs cannot both be describing the same discriminative ability; the paper interprets the low AUCs merely as a difficulty ranking rather than treating them as contradicting the perfect per-type detection claim. The honest reading is that the headline figure is not well supported by the accompanying per-class evidence.</t>
+          <t>Of the 36 analyzed prominent studies and real-world incidents, at least twenty-one documented attacks against production LLM systems traverse four or more stages of the proposed seven-stage promptware kill chain (Initial Access, Privilege Escalation, Reconnaissance, Persistence, Command &amp; Control, Lateral Movement, Actions on Objective), and at least fifteen traverse the full chain to some significant depth, demonstrating that the multistage promptware threat model is not merely theoretical but empirically observed against widely deployed systems (e.g., Google Assistant, ChatGPT, GitHub Copilot, Cursor, Perplexity Comet). Analysis of the defense landscape (Table IV) reveals a systemic imbalance: substantial research attention has been devoted to mitigations for the initial two stages (prompt injection and jailbreaking), while significantly less attention has been given to defenses against later-stage attack behaviors -- lateral movement (only three identified mitigations), Command &amp; Control (three mitigations), reconnaissance (zero identified mitigations), while actions-on-objective has the most mitigations (seven), reflecting that most existing security research addresses the entry point of the kill chain rather than its full progression. The analysis also finds a general trade-off: all identified prevention mechanisms significantly impact usability, and stronger prevention consistently comes at higher usability cost, with mechanisms varying widely in deployment effort (ranging from low-effort data instrumentation/behavioral monitoring to high-effort architectural changes like component isolation and dual-LLM data-minimization orchestration) and maintenance burden.</t>
         </is>
       </c>
       <c r="F111" s="5" t="n"/>
@@ -6416,7 +6404,7 @@
       <c r="H111" s="5" t="n"/>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>cce1b13eebe88e5051d329a95616c9df646fb08c</t>
+          <t>88ee88a0da1d1a8bacf04bf4dc85be0ed7f7995a</t>
         </is>
       </c>
     </row>
@@ -6426,7 +6414,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Unified Security Orchestration Framework for Protecting AI/ML Systems Against Input-Based and Model Supply Chain Attacks</t>
+          <t>The Promptware Kill Chain: How Prompt Injections Gradually Evolved Into a Multistep Malware Delivery Mechanism</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -6441,7 +6429,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>No implemented baseline is run against USOF. Prior work is discussed rather than reproduced: the formal prompt-injection taxonomy and comparative evaluation of five attacks against ten defense strategies across ten language models (Liu et al., 2023), the BIPIA benchmark for indirect prompt injection via RAG-retrieved content, static keyword/pattern input filtering (characterized as unable to resist semantically obfuscated attacks), and embedding-based anomaly detection. None of these is executed on the paper's own 200-sample dataset for comparison.</t>
+          <t>N/A - not a comparative empirical study; instead, the paper compares promptware/prompt injection conceptually against three classical injection-attack classes (Table I): SQL injection, script injection (JS/Python/etc.), and OS command injection, along dimensions including language/modality used, target layer, root cause, executor, outcome determinism, compromised space, blast radius, and possible outcomes, to argue that prompt injection is fundamentally broader in capability and blast radius than these classical analogues.</t>
         </is>
       </c>
       <c r="F112" s="5" t="n"/>
@@ -6449,7 +6437,7 @@
       <c r="H112" s="5" t="n"/>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>cce1b13eebe88e5051d329a95616c9df646fb08c</t>
+          <t>88ee88a0da1d1a8bacf04bf4dc85be0ed7f7995a</t>
         </is>
       </c>
     </row>
@@ -6459,7 +6447,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Unified Security Orchestration Framework for Protecting AI/ML Systems Against Input-Based and Model Supply Chain Attacks</t>
+          <t>The Promptware Kill Chain: How Prompt Injections Gradually Evolved Into a Multistep Malware Delivery Mechanism</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -6472,13 +6460,17 @@
           <t>freetext</t>
         </is>
       </c>
-      <c r="E113" s="2" t="n"/>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Formal, comprehensive threat model: the paper's central contribution is the seven-stage 'promptware kill chain,' explicitly adapted from the traditional cybersecurity Cyber Kill Chain (Lockheed Martin) framework to LLM-based systems: (1) Initial Access via prompt injection (natural language, obfuscated text, image, or audio); (2) Privilege Escalation via jailbreaking; (3) Reconnaissance of the target environment/system; (4) Persistence via memory and retrieval poisoning; (5) Command and Control (C2), establishing an ongoing attacker-controlled channel; (6) Lateral Movement, both on-device and off-device propagation to other systems/agents; and (7) Actions on Objective, ranging from data exfiltration to unauthorized financial transactions. The paper's central thesis is that treating prompt injection merely as the 'LLM analogue of SQL injection' -- a single-stage, classifier-solvable vulnerability -- fundamentally understates its systemic, multistage, malware-like nature (which they term 'promptware'), with non-deterministic outcomes, application-wide blast radius (spanning permissions, APIs, tools, and connected services), and outcomes including infostealers, spyware, cryptostealers, worms, trojans, and remote code execution.</t>
+        </is>
+      </c>
       <c r="F113" s="5" t="n"/>
       <c r="G113" s="5" t="n"/>
       <c r="H113" s="5" t="n"/>
       <c r="I113" s="5" t="inlineStr">
         <is>
-          <t>cce1b13eebe88e5051d329a95616c9df646fb08c</t>
+          <t>88ee88a0da1d1a8bacf04bf4dc85be0ed7f7995a</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6480,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Unified Security Orchestration Framework for Protecting AI/ML Systems Against Input-Based and Model Supply Chain Attacks</t>
+          <t>The Promptware Kill Chain: How Prompt Injections Gradually Evolved Into a Multistep Malware Delivery Mechanism</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -6503,7 +6495,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>The paper states its evaluation limitations directly and they are substantial. The dataset is only 200 samples, which it acknowledges restricts extrapolability. ITTAM shows only moderate recall on the stealthier attack classes, specifically indirect prompt injection and multi-turn attacks - the two most relevant categories for this corpus. MISCV, the supply-chain component, relies on simplified behavioral metrics rather than deep embeddings. Most consequentially, the prototype was never scaled to real Large Language Models and was not tested in production-like settings, so the framework is validated only against synthetic traffic. Beyond the stated list, the reported per-class AUCs (as low as 0.01-0.05 for role-play, jailbreak and data exfiltration, and 0.50 for benign) are difficult to reconcile with the claimed 100% per-type true-positive and 0% false-positive rates, and the paper does not resolve that tension; the 95% headline detection rate should therefore be treated as weakly evidenced.</t>
+          <t>The paper does not contain an explicit numbered 'Limitations' section; as a Systemization of Knowledge (SoK) paper, its Discussion section (Section VI) implicitly acknowledges scope boundaries by focusing on four positive contributions (analytical clarity, systematic risk assessment, common vocabulary, motivating defense-in-depth) rather than cataloguing weaknesses. The Ethical Considerations appendix notes: 'Our paper is a Systemization of Knowledge (SoK) paper, and no experiments have been performed that required ethical considerations,' implicitly flagging that the work's evidentiary basis rests entirely on secondary analysis of already-published incidents and studies rather than original experimentation, and the Analysis subsection (Section IV-G) explicitly identifies an asymmetry in the current defense literature -- reconnaissance lacks any identified mitigations, and lateral movement/C2 have only three mitigations each -- as a gap in existing research (rather than a limitation of this paper specifically) that the kill-chain framework is intended to help address going forward.</t>
         </is>
       </c>
       <c r="F114" s="5" t="n"/>
@@ -6511,7 +6503,7 @@
       <c r="H114" s="5" t="n"/>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>cce1b13eebe88e5051d329a95616c9df646fb08c</t>
+          <t>88ee88a0da1d1a8bacf04bf4dc85be0ed7f7995a</t>
         </is>
       </c>
     </row>
@@ -6521,7 +6513,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Unified Security Orchestration Framework for Protecting AI/ML Systems Against Input-Based and Model Supply Chain Attacks</t>
+          <t>The Promptware Kill Chain: How Prompt Injections Gradually Evolved Into a Multistep Malware Delivery Mechanism</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -6536,7 +6528,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Proposes the Unified Security Orchestration Framework (USOF), a model-independent security control plane spanning the AI/ML lifecycle, motivated by the argument that existing AI security tooling is fragmented - each tool protects one component, so coordinated or novel attacks that cross components go uncovered. USOF composes six modules: the Input Trust and Threat Analysis Module (ITTAM) detecting input-based attacks across direct, indirect, multi-turn and multimodal vectors; a Context-Aware Policy Enforcement Engine (CAPEE) applying dynamic context-sensitive policy at runtime; an Execution Isolation Layer (EIL) bounding agentic actions; a Model Integrity and Supply Chain Validator (MISCV) detecting supply-chain compromise via training-data-independent behavioral fingerprinting; a Response Governance Engine (RGE) screening outputs for sensitive-data leakage and second-order injection; and an Adaptive Learning and Feedback Mechanism (ALFM) that updates detection from confirmed incidents. Its distinguishing scope claim is that it spans both input-level and model-level (supply-chain) attack surfaces in one system, where most work addresses one or the other, and that it targets single-model, multi-model and agent-based architectures across cloud, on-premises and edge deployment. Notable for this corpus because it explicitly includes second-order injection screening on the output path (RGE) and execution isolation (EIL) alongside ingestion filtering - i.e. it nominally instruments ingestion, execution and output, though as a prototype rather than a deployed system.</t>
+          <t>This paper argues that prompt injection attacks against LLM-based applications have evolved over roughly three years from isolated, single-step input-manipulation exploits (originally framed, following Simon Willison's 2022 coinage, as the LLM analogue of SQL injection) into multistep, malware-like attack campaigns that the authors term 'promptware.' The paper's central contribution is a formal seven-stage 'promptware kill chain' -- Initial Access (prompt injection), Privilege Escalation (jailbreaking), Reconnaissance, Persistence (memory and retrieval poisoning), Command and Control, Lateral Movement (on-device and off-device propagation), and Actions on Objective -- explicitly modeled on the traditional cybersecurity Cyber Kill Chain framework, designed to capture the full lifecycle of modern LLM-targeted attacks rather than just their entry point. The authors first formally compare promptware against three classical injection-attack analogues (SQL injection, script injection, OS command injection) across dimensions like modality, target layer, root cause, outcome determinism, and blast radius, showing that prompt injection's non-deterministic outcomes and application-wide (rather than narrowly database- or OS-scoped) blast radius make the SQL-injection analogy significantly understate its true capability and danger. The paper then substantiates the kill-chain framework empirically by systematically analyzing 36 prominent published studies and real-world documented incidents against production LLM systems (spanning roughly February 2023 to January 2026, covering systems like Google Assistant, ChatGPT, GitHub Copilot, Cursor, and Perplexity Comet), coding each incident against the seven kill-chain stages and finding that at least 21 traverse four or more stages, empirically grounding the claim that this multistage threat model is already actively exploited rather than theoretical. Finally, the paper surveys and systematically catalogs existing defense mechanisms mapped to each kill-chain stage (assessing each mitigation's type, deployment layer, usability impact, deployment effort, and maintenance burden), revealing that the security research community has disproportionately concentrated defensive attention on the earliest stages (prompt injection and jailbreaking defenses) while leaving later stages of the kill chain -- particularly reconnaissance, persistence, lateral movement, and command-and-control -- comparatively under-defended, and argues this imbalance underscores the need for defense-in-depth security architectures spanning the entire promptware lifecycle rather than prompt-injection-specific point solutions.</t>
         </is>
       </c>
       <c r="F115" s="5" t="n"/>
@@ -6544,7 +6536,7 @@
       <c r="H115" s="5" t="n"/>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>cce1b13eebe88e5051d329a95616c9df646fb08c</t>
+          <t>88ee88a0da1d1a8bacf04bf4dc85be0ed7f7995a</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6546,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Failure-Gated Hierarchical Memory: Preventing Memory Pollution in Long-Horizon LLM Agents via Critic-Guided Write Control</t>
+          <t>Addressing Prompt Injection in Large Language Models via In-Context Learning</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -6577,7 +6569,7 @@
       <c r="H116" s="5" t="n"/>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>341883c91dabb788b32dae7d1bd6c6146d266b95</t>
+          <t>c30673d667b2875f2a7563c4755520d6961783f8</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6579,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Failure-Gated Hierarchical Memory: Preventing Memory Pollution in Long-Horizon LLM Agents via Critic-Guided Write Control</t>
+          <t>Addressing Prompt Injection in Large Language Models via In-Context Learning</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -6602,7 +6594,7 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>ML/AI</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="F117" s="5" t="n"/>
@@ -6610,7 +6602,7 @@
       <c r="H117" s="5" t="n"/>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>341883c91dabb788b32dae7d1bd6c6146d266b95</t>
+          <t>c30673d667b2875f2a7563c4755520d6961783f8</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6612,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Failure-Gated Hierarchical Memory: Preventing Memory Pollution in Long-Horizon LLM Agents via Critic-Guided Write Control</t>
+          <t>Addressing Prompt Injection in Large Language Models via In-Context Learning</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -6643,7 +6635,7 @@
       <c r="H118" s="5" t="n"/>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>341883c91dabb788b32dae7d1bd6c6146d266b95</t>
+          <t>c30673d667b2875f2a7563c4755520d6961783f8</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6645,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Failure-Gated Hierarchical Memory: Preventing Memory Pollution in Long-Horizon LLM Agents via Critic-Guided Write Control</t>
+          <t>Addressing Prompt Injection in Large Language Models via In-Context Learning</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -6668,7 +6660,7 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>defense</t>
         </is>
       </c>
       <c r="F119" s="5" t="n"/>
@@ -6676,7 +6668,7 @@
       <c r="H119" s="5" t="n"/>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>341883c91dabb788b32dae7d1bd6c6146d266b95</t>
+          <t>c30673d667b2875f2a7563c4755520d6961783f8</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6678,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Failure-Gated Hierarchical Memory: Preventing Memory Pollution in Long-Horizon LLM Agents via Critic-Guided Write Control</t>
+          <t>Addressing Prompt Injection in Large Language Models via In-Context Learning</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -6701,7 +6693,7 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F120" s="5" t="n"/>
@@ -6709,7 +6701,7 @@
       <c r="H120" s="5" t="n"/>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>341883c91dabb788b32dae7d1bd6c6146d266b95</t>
+          <t>c30673d667b2875f2a7563c4755520d6961783f8</t>
         </is>
       </c>
     </row>
@@ -6719,7 +6711,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Failure-Gated Hierarchical Memory: Preventing Memory Pollution in Long-Horizon LLM Agents via Critic-Guided Write Control</t>
+          <t>Addressing Prompt Injection in Large Language Models via In-Context Learning</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -6734,7 +6726,7 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>silent-corruption</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="F121" s="5" t="n"/>
@@ -6742,7 +6734,7 @@
       <c r="H121" s="5" t="n"/>
       <c r="I121" s="5" t="inlineStr">
         <is>
-          <t>341883c91dabb788b32dae7d1bd6c6146d266b95</t>
+          <t>c30673d667b2875f2a7563c4755520d6961783f8</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6744,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Failure-Gated Hierarchical Memory: Preventing Memory Pollution in Long-Horizon LLM Agents via Critic-Guided Write Control</t>
+          <t>Addressing Prompt Injection in Large Language Models via In-Context Learning</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -6767,7 +6759,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F122" s="5" t="n"/>
@@ -6775,7 +6767,7 @@
       <c r="H122" s="5" t="n"/>
       <c r="I122" s="5" t="inlineStr">
         <is>
-          <t>341883c91dabb788b32dae7d1bd6c6146d266b95</t>
+          <t>c30673d667b2875f2a7563c4755520d6961783f8</t>
         </is>
       </c>
     </row>
@@ -6785,7 +6777,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Failure-Gated Hierarchical Memory: Preventing Memory Pollution in Long-Horizon LLM Agents via Critic-Guided Write Control</t>
+          <t>Addressing Prompt Injection in Large Language Models via In-Context Learning</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -6808,7 +6800,7 @@
       <c r="H123" s="5" t="n"/>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>341883c91dabb788b32dae7d1bd6c6146d266b95</t>
+          <t>c30673d667b2875f2a7563c4755520d6961783f8</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6810,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Failure-Gated Hierarchical Memory: Preventing Memory Pollution in Long-Horizon LLM Agents via Critic-Guided Write Control</t>
+          <t>Addressing Prompt Injection in Large Language Models via In-Context Learning</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -6833,7 +6825,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>ingestion</t>
+          <t>reasoning</t>
         </is>
       </c>
       <c r="F124" s="5" t="n"/>
@@ -6841,7 +6833,7 @@
       <c r="H124" s="5" t="n"/>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>341883c91dabb788b32dae7d1bd6c6146d266b95</t>
+          <t>c30673d667b2875f2a7563c4755520d6961783f8</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6843,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Failure-Gated Hierarchical Memory: Preventing Memory Pollution in Long-Horizon LLM Agents via Critic-Guided Write Control</t>
+          <t>Addressing Prompt Injection in Large Language Models via In-Context Learning</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -6866,7 +6858,7 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>session-persistent</t>
+          <t>one-shot</t>
         </is>
       </c>
       <c r="F125" s="5" t="n"/>
@@ -6874,7 +6866,7 @@
       <c r="H125" s="5" t="n"/>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>341883c91dabb788b32dae7d1bd6c6146d266b95</t>
+          <t>c30673d667b2875f2a7563c4755520d6961783f8</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6876,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Failure-Gated Hierarchical Memory: Preventing Memory Pollution in Long-Horizon LLM Agents via Critic-Guided Write Control</t>
+          <t>Addressing Prompt Injection in Large Language Models via In-Context Learning</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -6899,7 +6891,7 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F126" s="5" t="n"/>
@@ -6907,7 +6899,7 @@
       <c r="H126" s="5" t="n"/>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>341883c91dabb788b32dae7d1bd6c6146d266b95</t>
+          <t>c30673d667b2875f2a7563c4755520d6961783f8</t>
         </is>
       </c>
     </row>
@@ -6917,7 +6909,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Failure-Gated Hierarchical Memory: Preventing Memory Pollution in Long-Horizon LLM Agents via Critic-Guided Write Control</t>
+          <t>Addressing Prompt Injection in Large Language Models via In-Context Learning</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -6936,7 +6928,7 @@
       <c r="H127" s="5" t="n"/>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>341883c91dabb788b32dae7d1bd6c6146d266b95</t>
+          <t>c30673d667b2875f2a7563c4755520d6961783f8</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6938,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Failure-Gated Hierarchical Memory: Preventing Memory Pollution in Long-Horizon LLM Agents via Critic-Guided Write Control</t>
+          <t>Addressing Prompt Injection in Large Language Models via In-Context Learning</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -6961,7 +6953,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>GPT-4o, Llama-3 and Qwen2.5-72B-Instruct.</t>
+          <t>Three LLMs serve as target models for the defense, selected as models with insufficient alignment to demonstrate rapid retrofit deployment; each is evaluated in vanilla form and with the proposed framework, against four baselines.</t>
         </is>
       </c>
       <c r="F128" s="5" t="n"/>
@@ -6969,7 +6961,7 @@
       <c r="H128" s="5" t="n"/>
       <c r="I128" s="5" t="inlineStr">
         <is>
-          <t>341883c91dabb788b32dae7d1bd6c6146d266b95</t>
+          <t>c30673d667b2875f2a7563c4755520d6961783f8</t>
         </is>
       </c>
     </row>
@@ -6979,7 +6971,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Failure-Gated Hierarchical Memory: Preventing Memory Pollution in Long-Horizon LLM Agents via Critic-Guided Write Control</t>
+          <t>Addressing Prompt Injection in Large Language Models via In-Context Learning</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -6994,7 +6986,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>ALFWorld (continuous 5-round reset, 670 scenarios), WebShop (200-task pipeline) and MemoryAgentBench FactConsolidation.</t>
+          <t>Publicly available prompt-injection/jailbreak classification datasets are used and explicitly critiqued - the paper argues their benign prompts are too easily distinguishable to support learning on borderline cases - and the framework supplements them with dynamically generated hard-to-distinguish prompts produced by the Analysis and Generation Team interaction. Evaluation uses macro-averaged binary classification metrics.</t>
         </is>
       </c>
       <c r="F129" s="5" t="n"/>
@@ -7002,7 +6994,7 @@
       <c r="H129" s="5" t="n"/>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>341883c91dabb788b32dae7d1bd6c6146d266b95</t>
+          <t>c30673d667b2875f2a7563c4755520d6961783f8</t>
         </is>
       </c>
     </row>
@@ -7012,7 +7004,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Failure-Gated Hierarchical Memory: Preventing Memory Pollution in Long-Horizon LLM Agents via Critic-Guided Write Control</t>
+          <t>Addressing Prompt Injection in Large Language Models via In-Context Learning</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -7027,7 +7019,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>FGHM reduces the long-term memory pollution rate from 38% under naive LLM summarization to 9%, while task success degrades only 4 percentage points over 5 rounds against 20+ points for the baselines - roughly a 4x reduction in pollution with long-horizon performance preserved.</t>
+          <t>Across three target LLMs, the proposed method outperformed four baselines on all evaluation metrics, with an average improvement of 16.6 points in F1 relative to the vanilla (undefended) models. The result is reported with macro-averaged binary classification metrics, which is appropriate given the paper's emphasis on not merely catching attacks but correctly accepting difficult benign prompts - a plain accuracy or attack-success-rate figure would obscure exactly the over-refusal behaviour the work targets. The mechanism behind the gain is the adversarially-generated hard-case curriculum: because the Analysis and Generation Teams jointly produce prompts near the harmful/benign boundary, the accumulated exemplars are informative in a way that public datasets' easily-separable benign prompts are not, which is the paper's explanation for why prior machine-learning approaches showed limited accuracy improvement. The claimed practical implication is sustainability: detection can be strengthened against evolving attacks through log accumulation alone, with no retraining of the underlying LLM.</t>
         </is>
       </c>
       <c r="F130" s="5" t="n"/>
@@ -7035,7 +7027,7 @@
       <c r="H130" s="5" t="n"/>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>341883c91dabb788b32dae7d1bd6c6146d266b95</t>
+          <t>c30673d667b2875f2a7563c4755520d6961783f8</t>
         </is>
       </c>
     </row>
@@ -7045,7 +7037,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Failure-Gated Hierarchical Memory: Preventing Memory Pollution in Long-Horizon LLM Agents via Critic-Guided Write Control</t>
+          <t>Addressing Prompt Injection in Large Language Models via In-Context Learning</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -7060,7 +7052,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Naive LLM summarization of memory and other memory-management baselines, which lose 20+ points of task success over the same 5 rounds.</t>
+          <t>Four baselines plus the vanilla (undefended) models, evaluated on three target LLMs with macro-averaged binary classification metrics; the reported 16.6-point average F1 gain is measured against the vanilla models. Related work discussed but not reimplemented includes the Liu et al. large-scale prompt-injection benchmark formalizing injection as diversion to an 'injected task' and its Combined Attack, and fine-tuning-based defenses such as Xu et al., which the paper criticizes for high implementation barriers due to parameter updates.</t>
         </is>
       </c>
       <c r="F131" s="5" t="n"/>
@@ -7068,7 +7060,7 @@
       <c r="H131" s="5" t="n"/>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>341883c91dabb788b32dae7d1bd6c6146d266b95</t>
+          <t>c30673d667b2875f2a7563c4755520d6961783f8</t>
         </is>
       </c>
     </row>
@@ -7078,7 +7070,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Failure-Gated Hierarchical Memory: Preventing Memory Pollution in Long-Horizon LLM Agents via Critic-Guided Write Control</t>
+          <t>Addressing Prompt Injection in Large Language Models via In-Context Learning</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -7091,17 +7083,13 @@
           <t>freetext</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
-        <is>
-          <t>Non-adversarial. Memory pollution arises from uncontrolled writes by the agent itself - erroneous, outdated or over-generalized entries that silently degrade later tasks through retrieval, compounding across hundreds of episodes via cascading error propagation.</t>
-        </is>
-      </c>
+      <c r="E132" s="2" t="n"/>
       <c r="F132" s="5" t="n"/>
       <c r="G132" s="5" t="n"/>
       <c r="H132" s="5" t="n"/>
       <c r="I132" s="5" t="inlineStr">
         <is>
-          <t>341883c91dabb788b32dae7d1bd6c6146d266b95</t>
+          <t>c30673d667b2875f2a7563c4755520d6961783f8</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7099,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Failure-Gated Hierarchical Memory: Preventing Memory Pollution in Long-Horizon LLM Agents via Critic-Guided Write Control</t>
+          <t>Addressing Prompt Injection in Large Language Models via In-Context Learning</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -7126,7 +7114,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Not explicitly stated. Evaluation covers three agent benchmarks and a 5-round horizon, which bounds claims about hundreds-of-episode deployments.</t>
+          <t>The paper includes a dedicated discussion of the method's limitations based on its experimental results, and its scope conditions are stated up front: it deliberately targets LLMs with insufficient alignment, so the demonstrated 16.6-point F1 gain is measured where there is most headroom and should not be read as transferring to well-aligned frontier models. Evaluation is framed as binary harmfulness classification of prompts rather than end-to-end agent security, so it does not establish protection in a tool-using or RAG setting where injected instructions arrive through retrieved content rather than the user turn - the indirect-injection case is not exercised. The hard-case curriculum is generated by the framework's own agents, which risks the training distribution being shaped by what those agents can invent rather than by what real attackers do, and no evaluation against an independent adaptive adversary is reported. Finally, ICL-based learning shifts cost from training to inference: accumulating exemplars consumes context window and per-query compute, and the paper does not quantify that overhead or the point at which exemplar accumulation stops helping.</t>
         </is>
       </c>
       <c r="F133" s="5" t="n"/>
@@ -7134,7 +7122,7 @@
       <c r="H133" s="5" t="n"/>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>341883c91dabb788b32dae7d1bd6c6146d266b95</t>
+          <t>c30673d667b2875f2a7563c4755520d6961783f8</t>
         </is>
       </c>
     </row>
@@ -7144,7 +7132,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Failure-Gated Hierarchical Memory: Preventing Memory Pollution in Long-Horizon LLM Agents via Critic-Guided Write Control</t>
+          <t>Addressing Prompt Injection in Large Language Models via In-Context Learning</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -7159,7 +7147,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>A three-tier memory architecture (working memory, episodic buffer, procedural long-term memory) in which an independently trained Failure Critic agent gates every write from the episodic buffer into long-term memory, returning APPROVE, REJECT_REDUNDANT or REJECT_CONFLICT, making the L2-to-L3 boundary the single control point for memory quality.</t>
+          <t>Proposes a multi-LLM agent framework for prompt-injection and jailbreak detection that learns through In-Context Learning rather than parameter updates. The paper is motivated by two specific failures it diagnoses in existing defenses: over-refusal, where prompts containing harmful vocabulary but semantically benign intent get rejected, degrading utility; and a dataset problem, namely that benign prompts in public prompt-injection datasets are trivially separable (its examples: 'When is the next Bundestag election?', 'How much money should I save per month?'), so training on them cannot improve performance on genuinely borderline cases. The proposed method attacks both by construction: two cooperating teams of LLM agents - an Analysis Team and a Generation Team - interact to dynamically generate prompts that are hard to classify, and those hard cases accumulate as in-context exemplars. Because learning happens through exemplar accumulation rather than fine-tuning, the framework requires no expensive parameter updates and can be extended against newly emerging attacks purely by accumulating logs, which the authors frame as its practical sustainability advantage. The paper deliberately targets LLMs with insufficient alignment, to show the method can retrofit detection capability onto weaker models rather than merely reinforcing already-aligned ones. Evaluation uses macro-averaged binary classification metrics for harmfulness detection. Sits in this corpus as an ingestion-stage Track A defense whose distinguishing property is the safety/utility trade-off framing - it targets false positives as explicitly as false negatives.</t>
         </is>
       </c>
       <c r="F134" s="5" t="n"/>
@@ -7167,7 +7155,7 @@
       <c r="H134" s="5" t="n"/>
       <c r="I134" s="5" t="inlineStr">
         <is>
-          <t>341883c91dabb788b32dae7d1bd6c6146d266b95</t>
+          <t>c30673d667b2875f2a7563c4755520d6961783f8</t>
         </is>
       </c>
     </row>
@@ -7177,7 +7165,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Fact-Augmented Lookahead Planning for LLM Agents</t>
+          <t>Agentic Permissions Policy Algebra for Taint Confinement in LLM Agents</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -7200,7 +7188,7 @@
       <c r="H135" s="5" t="n"/>
       <c r="I135" s="5" t="inlineStr">
         <is>
-          <t>93f50fbd4ed8303e86ebb5946339bb103a234ab5</t>
+          <t>a627218ebc531a61b3f43df433c8034165e32ba9</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7198,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Fact-Augmented Lookahead Planning for LLM Agents</t>
+          <t>Agentic Permissions Policy Algebra for Taint Confinement in LLM Agents</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -7225,7 +7213,7 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>ML/AI</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="F136" s="5" t="n"/>
@@ -7233,7 +7221,7 @@
       <c r="H136" s="5" t="n"/>
       <c r="I136" s="5" t="inlineStr">
         <is>
-          <t>93f50fbd4ed8303e86ebb5946339bb103a234ab5</t>
+          <t>a627218ebc531a61b3f43df433c8034165e32ba9</t>
         </is>
       </c>
     </row>
@@ -7243,7 +7231,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Fact-Augmented Lookahead Planning for LLM Agents</t>
+          <t>Agentic Permissions Policy Algebra for Taint Confinement in LLM Agents</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -7266,7 +7254,7 @@
       <c r="H137" s="5" t="n"/>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>93f50fbd4ed8303e86ebb5946339bb103a234ab5</t>
+          <t>a627218ebc531a61b3f43df433c8034165e32ba9</t>
         </is>
       </c>
     </row>
@@ -7276,7 +7264,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Fact-Augmented Lookahead Planning for LLM Agents</t>
+          <t>Agentic Permissions Policy Algebra for Taint Confinement in LLM Agents</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -7299,7 +7287,7 @@
       <c r="H138" s="5" t="n"/>
       <c r="I138" s="5" t="inlineStr">
         <is>
-          <t>93f50fbd4ed8303e86ebb5946339bb103a234ab5</t>
+          <t>a627218ebc531a61b3f43df433c8034165e32ba9</t>
         </is>
       </c>
     </row>
@@ -7309,7 +7297,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Fact-Augmented Lookahead Planning for LLM Agents</t>
+          <t>Agentic Permissions Policy Algebra for Taint Confinement in LLM Agents</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -7324,7 +7312,7 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>tool-output</t>
         </is>
       </c>
       <c r="F139" s="5" t="n"/>
@@ -7332,7 +7320,7 @@
       <c r="H139" s="5" t="n"/>
       <c r="I139" s="5" t="inlineStr">
         <is>
-          <t>93f50fbd4ed8303e86ebb5946339bb103a234ab5</t>
+          <t>a627218ebc531a61b3f43df433c8034165e32ba9</t>
         </is>
       </c>
     </row>
@@ -7342,7 +7330,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Fact-Augmented Lookahead Planning for LLM Agents</t>
+          <t>Agentic Permissions Policy Algebra for Taint Confinement in LLM Agents</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -7357,7 +7345,7 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>data-exfiltration</t>
         </is>
       </c>
       <c r="F140" s="5" t="n"/>
@@ -7365,7 +7353,7 @@
       <c r="H140" s="5" t="n"/>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>93f50fbd4ed8303e86ebb5946339bb103a234ab5</t>
+          <t>a627218ebc531a61b3f43df433c8034165e32ba9</t>
         </is>
       </c>
     </row>
@@ -7375,7 +7363,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Fact-Augmented Lookahead Planning for LLM Agents</t>
+          <t>Agentic Permissions Policy Algebra for Taint Confinement in LLM Agents</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -7390,7 +7378,7 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F141" s="5" t="n"/>
@@ -7398,7 +7386,7 @@
       <c r="H141" s="5" t="n"/>
       <c r="I141" s="5" t="inlineStr">
         <is>
-          <t>93f50fbd4ed8303e86ebb5946339bb103a234ab5</t>
+          <t>a627218ebc531a61b3f43df433c8034165e32ba9</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7396,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Fact-Augmented Lookahead Planning for LLM Agents</t>
+          <t>Agentic Permissions Policy Algebra for Taint Confinement in LLM Agents</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -7431,7 +7419,7 @@
       <c r="H142" s="5" t="n"/>
       <c r="I142" s="5" t="inlineStr">
         <is>
-          <t>93f50fbd4ed8303e86ebb5946339bb103a234ab5</t>
+          <t>a627218ebc531a61b3f43df433c8034165e32ba9</t>
         </is>
       </c>
     </row>
@@ -7441,7 +7429,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Fact-Augmented Lookahead Planning for LLM Agents</t>
+          <t>Agentic Permissions Policy Algebra for Taint Confinement in LLM Agents</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -7456,7 +7444,7 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>reasoning</t>
+          <t>execution</t>
         </is>
       </c>
       <c r="F143" s="5" t="n"/>
@@ -7464,7 +7452,7 @@
       <c r="H143" s="5" t="n"/>
       <c r="I143" s="5" t="inlineStr">
         <is>
-          <t>93f50fbd4ed8303e86ebb5946339bb103a234ab5</t>
+          <t>a627218ebc531a61b3f43df433c8034165e32ba9</t>
         </is>
       </c>
     </row>
@@ -7474,7 +7462,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Fact-Augmented Lookahead Planning for LLM Agents</t>
+          <t>Agentic Permissions Policy Algebra for Taint Confinement in LLM Agents</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -7489,7 +7477,7 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>session-persistent</t>
+          <t>one-shot</t>
         </is>
       </c>
       <c r="F144" s="5" t="n"/>
@@ -7497,7 +7485,7 @@
       <c r="H144" s="5" t="n"/>
       <c r="I144" s="5" t="inlineStr">
         <is>
-          <t>93f50fbd4ed8303e86ebb5946339bb103a234ab5</t>
+          <t>a627218ebc531a61b3f43df433c8034165e32ba9</t>
         </is>
       </c>
     </row>
@@ -7507,7 +7495,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Fact-Augmented Lookahead Planning for LLM Agents</t>
+          <t>Agentic Permissions Policy Algebra for Taint Confinement in LLM Agents</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -7530,7 +7518,7 @@
       <c r="H145" s="5" t="n"/>
       <c r="I145" s="5" t="inlineStr">
         <is>
-          <t>93f50fbd4ed8303e86ebb5946339bb103a234ab5</t>
+          <t>a627218ebc531a61b3f43df433c8034165e32ba9</t>
         </is>
       </c>
     </row>
@@ -7540,7 +7528,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Fact-Augmented Lookahead Planning for LLM Agents</t>
+          <t>Agentic Permissions Policy Algebra for Taint Confinement in LLM Agents</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -7555,7 +7543,7 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>The paper does not state a public code repository link in the sections reviewed (main text, main results, and appendix limitations); it instead provides extensive appendix material (implementation and evaluation details, persistent runtime state specification in Table 3, concrete hyperparameter defaults in Table 4, and full per-task results across 134 ALFWorld evaluation tasks) explicitly intended to enable replication, rather than releasing a named code artifact.</t>
+          <t>No public code/artifact release URL found in the sections reviewed (abstract, introduction, evaluation, limitations, conclusion, or reference list). The benchmark suite 'bench-corp' is described in detail but no repository link is given in the visible text.</t>
         </is>
       </c>
       <c r="F146" s="5" t="n"/>
@@ -7563,7 +7551,7 @@
       <c r="H146" s="5" t="n"/>
       <c r="I146" s="5" t="inlineStr">
         <is>
-          <t>93f50fbd4ed8303e86ebb5946339bb103a234ab5</t>
+          <t>a627218ebc531a61b3f43df433c8034165e32ba9</t>
         </is>
       </c>
     </row>
@@ -7573,7 +7561,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Fact-Augmented Lookahead Planning for LLM Agents</t>
+          <t>Agentic Permissions Policy Algebra for Taint Confinement in LLM Agents</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -7588,7 +7576,7 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>The primary backbone LLM used for the main benchmark results is not explicitly named in the reviewed sections beyond being referred to generically as the agent's underlying LLM, but a robustness/generalization experiment (Appendix J.7) additionally evaluates LWM-Planner with a smaller GPT-4o-mini backbone (Table 16) to test whether results hold with weaker models. All planning components (action proposer, latent world model simulator, value estimator, and the fact extractor) are instantiated by prompting the same underlying LLM in different roles.</t>
+          <t>Four models accessed via OpenRouter (2026-07-25, provider-default sampling): Gemini 3.5 Flash-Lite, GPT-5.6 Luna, GPT-4o, and Qwen 3.6 35B. A fifth model, Gemini 3.1 Flash-Lite, was excluded from analysis because its traces were dominated by native retry behavior rather than policy events.</t>
         </is>
       </c>
       <c r="F147" s="5" t="n"/>
@@ -7596,7 +7584,7 @@
       <c r="H147" s="5" t="n"/>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>93f50fbd4ed8303e86ebb5946339bb103a234ab5</t>
+          <t>a627218ebc531a61b3f43df433c8034165e32ba9</t>
         </is>
       </c>
     </row>
@@ -7606,7 +7594,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Fact-Augmented Lookahead Planning for LLM Agents</t>
+          <t>Agentic Permissions Policy Algebra for Taint Confinement in LLM Agents</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -7621,7 +7609,7 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Three procedurally generated/standard text environments: TextFrozenLake (a procedurally generated text version of classic Frozen Lake, evaluated at 4x4, 6x6, and 8x8 grid sizes with varying hole probabilities to test scaling of the state-action space), CrafterMini (a 5x5 procedurally generated miniature version of the Crafter 2D survival-crafting environment, where the goal is to craft an iron pickaxe via prerequisite items), and ALFWorld (a text-based embodied household task environment paralleling the ALFRED dataset, with three sampled main-paper environments -- ALFWorld-A/B/C -- plus a full 134-task evaluation suite reported in the appendix).</t>
+          <t>bench-corp, a controlled corporate-assistant benchmark developed by the authors specifically for this paper, consisting of 14 multi-step, multi-tool scenarios spanning restrictive-read tasks (check-hr-record, inspect-forum-post, check-forum-and-hr), five scenarios embedding indirect prompt injections in public forum content, data-field smuggling (hide-secret-in-status), accidental-over-disclosure scenarios without adversarial injection (check-hr-record, email-onboarding-buddy), and native-expressiveness scenarios isolating specific policy distinctions (joint-merger-brief, one-release-only, public-directory-card, vendor-trust-boundary, share-legal-packet, reply-and-file-ticket, review-then-notify). Utility is evaluated across 13 utility-bearing scenarios; security Attack Success Rate (ASR) across all 14; each scenario run 3 repetitions per arm, scored via declarative string-matching predicates (email presence/absence, required/forbidden substrings) rather than an LLM judge.</t>
         </is>
       </c>
       <c r="F148" s="5" t="n"/>
@@ -7629,7 +7617,7 @@
       <c r="H148" s="5" t="n"/>
       <c r="I148" s="5" t="inlineStr">
         <is>
-          <t>93f50fbd4ed8303e86ebb5946339bb103a234ab5</t>
+          <t>a627218ebc531a61b3f43df433c8034165e32ba9</t>
         </is>
       </c>
     </row>
@@ -7639,7 +7627,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Fact-Augmented Lookahead Planning for LLM Agents</t>
+          <t>Agentic Permissions Policy Algebra for Taint Confinement in LLM Agents</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -7654,7 +7642,7 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>LWM-Planner achieves the highest cumulative return on every complex multi-step environment tested (Table 1): 31.80 on TextFrozenLake (4x4, h=0.9) vs. 20.20 for the strongest baseline (ReAct+FEC) and -265.20 for plain ReAct; 150.30 on CrafterMini vs. 149.70 (ReAct+FEC); and 21.33/22.89/19.50 on ALFWorld-A/B/C vs. the next-best baselines' 15.50/17.80/14.20 (varying by environment). Search-only baselines without learned symbolic abstractions (Tree-of-Thought, RAP) underperform substantially at the same test-time compute budget, and an ablation (ReAct+FEC: ReAct with fact extraction/compression but no tree search) confirms fact learning alone provides a large benefit, while combining it with grounded lookahead in the full LWM-Planner yields the strongest results overall. As environment state-action space scales up (TextFrozenLake at 4x4, 6x6, and 8x8; Table 2), baseline methods' normalized cumulative return degrades sharply (e.g., ReAct falls to -336.36 normalized return at 8x8), while LWM-Planner maintains the top normalized score (100.00) across all three sizes by continuing to online-learn minimal fact representations of hole locations. Targeted ablations (Table 10, appendix) show that unguided lookahead search can actually harm performance relative to no search, and that grounding the LLM world model with learned atomic facts -- rather than search depth or breadth alone -- is the dominant contributor to the observed gains, supporting the paper's central claim that additional test-time search is most useful when grounded by compact, experience-derived facts.</t>
+          <t>Across all four evaluated models, APPA (guarded policy enforcement with branching enabled) consistently eliminates or drastically reduces exfiltration attacks, dropping Attack Success Rate from 31-50% under open/undefended baselines down to 0-7% under APPA. The causal ablation isolating branching specifically (APPA vs. APPA-no-fork, differing only in --max-forks 0) shows branching raises overall utility from 69% to 95% (GPT-5.6 Luna), 28% to 44% (Gemini 3.5 Flash-Lite), and 54% to 72% (Qwen 3.6 35B), since branching prevents a single restrictive read from permanently polluting the primary context; GPT-4o shows no net utility change (59% both arms) because it converts 4 of 9 branch-dependent episodes but loses an equal number elsewhere to mediation overhead. Guarded enforcement carries a utility cost relative to the open (undefended) baseline: utility falls by 5/39 episodes (Gemini 3.5 Flash-Lite), 10/39 (GPT-4o), and 8/39 (Qwen 3.6 35B), though rises by 1/39 for GPT-5.6 Luna. The primary comparison baseline, Fides (Microsoft Agent Framework's IFC system), achieves an identical 12/42 (29%) ASR across all four models regardless of model choice -- described as 'a deterministic policy mismatch rather than model-dependent susceptibility' -- at 33-56% utility, and is explicitly noted as not feature-equivalent since it cannot represent APPA's recipient sets, history predicates, or branching. Models actively used APPA's prospective remedy engine, issuing 32-50 remedy calls per arm across the 42 episodes to interactively resolve policy gaps. Every non-zero APPA breach traced to exactly two specific scenarios and was attributed not to an enforcement bypass but to gaps outside the label algebra's stated scope: one involved smuggled content riding a flow that was technically permitted per the recipient-set policy (a limitation of label algebra rather than a bypass), and the other involved a missing write-side contract enabling a store-mediated laundering path, which the paper notes prospective enforcement can only be as complete as the contracts it evaluates.</t>
         </is>
       </c>
       <c r="F149" s="5" t="n"/>
@@ -7662,7 +7650,7 @@
       <c r="H149" s="5" t="n"/>
       <c r="I149" s="5" t="inlineStr">
         <is>
-          <t>93f50fbd4ed8303e86ebb5946339bb103a234ab5</t>
+          <t>a627218ebc531a61b3f43df433c8034165e32ba9</t>
         </is>
       </c>
     </row>
@@ -7672,7 +7660,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Fact-Augmented Lookahead Planning for LLM Agents</t>
+          <t>Agentic Permissions Policy Algebra for Taint Confinement in LLM Agents</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -7687,7 +7675,7 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>ReAct (reasoning-then-acting using current observation, interaction history, and environment description), Reflexion (ReAct augmented with a buffer of verbal self-reflection lessons appended each episode), Tree-of-Thought (ToT, LLM-driven lookahead tree search without learned symbolic abstraction), Retrieval-Augmented Planning (RAP, LLM-driven lookahead expansion without learned abstraction), an internal ablation ReAct+FEC (ReAct augmented with the paper's own Fact Extraction and Compression mechanism but without the recursive tree search), and a Random policy as a floor baseline.</t>
+          <t>Five experimental arms: APPA (full guarded enforcement with fork and submit_result enabled), APPA-no-fork (identical binary/policy but branching disabled via --max-forks 0, isolating the causal contribution of branching), APPA-open (the APPA agent loop under a neutral/undefended baseline policy), Fides (Microsoft Agent Framework enforcing its own IFC policy with automatic untrusted-content hiding and tool-less quarantine -- the closest prior-work antecedent), and Fides-open (the Microsoft Agent Framework loop without SecureAgentConfig, i.e., undefended).</t>
         </is>
       </c>
       <c r="F150" s="5" t="n"/>
@@ -7695,7 +7683,7 @@
       <c r="H150" s="5" t="n"/>
       <c r="I150" s="5" t="inlineStr">
         <is>
-          <t>93f50fbd4ed8303e86ebb5946339bb103a234ab5</t>
+          <t>a627218ebc531a61b3f43df433c8034165e32ba9</t>
         </is>
       </c>
     </row>
@@ -7705,7 +7693,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Fact-Augmented Lookahead Planning for LLM Agents</t>
+          <t>Agentic Permissions Policy Algebra for Taint Confinement in LLM Agents</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -7720,7 +7708,7 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>N/A - non-adversarial. This is a capability/planning-architecture paper for LLM agents in partially observable, long-horizon interactive environments rather than a security study. The incidental failure mode of interest is planning sub-optimality arising from state aliasing (the agent being unable to distinguish environment states with different optimal actions) and inaccurate one-step world-model simulation, which the paper's atomic-fact mechanism aims to reduce by grounding action proposal, simulation, and value estimation in distilled, experience-derived facts rather than raw or insufficiently compressed interaction history.</t>
+          <t>Formal, explicitly stated threat model (Section 3): the LLM itself is policy-untrusted -- it may propose arbitrary tool calls as a function of its visible transcript, whether driven by injected content (indirect prompt injection) or its own miscalibrated/hallucinated reasoning. The trusted computing base (TCB) consists of the engine, engine configuration, registered authorities, and registered transformations; no security theorem depends on model behavior. The paper formally proves parent label preservation and merge confinement under a two-monoid model over security labels and shared append-only event logs. Explicitly stated out-of-scope threats (Section 8): covert timing channels from an actively malicious model are out of scope; sanitizer correctness is assumed within the TCB rather than verified; an undeclared write-side contract can admit a store-mediated laundering path (an acknowledged gap, not a claimed guarantee); and context branching enforces trajectory isolation rather than transactional side-effect rollback, meaning external network egresses committed by a child branch before it is discarded cannot be reverted.</t>
         </is>
       </c>
       <c r="F151" s="5" t="n"/>
@@ -7728,7 +7716,7 @@
       <c r="H151" s="5" t="n"/>
       <c r="I151" s="5" t="inlineStr">
         <is>
-          <t>93f50fbd4ed8303e86ebb5946339bb103a234ab5</t>
+          <t>a627218ebc531a61b3f43df433c8034165e32ba9</t>
         </is>
       </c>
     </row>
@@ -7738,7 +7726,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Fact-Augmented Lookahead Planning for LLM Agents</t>
+          <t>Agentic Permissions Policy Algebra for Taint Confinement in LLM Agents</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -7753,7 +7741,7 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>The paper has an extensive, explicit 'Discussion of Limitations' appendix (Appendix K), organized into five subsections. Fact management and quality: fact extraction relies on the LLM's heuristic interpretation with no formal guarantee that extracted facts are optimally atomic, critical, or non-redundant, and suboptimal facts could waste context or mislead planning; the deque-based fact memory with optional LLM compression may still grow unmanageably in very long deployments, straining the context window or losing relevant older facts; and the notion of 'atomic' facts is operationally defined rather than formally grounded in a symbolic ontology, limiting systematicity and verifiability. Planning and simulation: the recursive lookahead search incurs considerable computational cost scaling with search depth and branching factor, potentially prohibitive for environments needing rapid decisions; the LLM-based world model and value estimator can be imperfect (especially in novel situations or those requiring deep causal reasoning), directly causing suboptimal planning; and the current fixed search depth/branching factor is a simplification that a more adaptive, confidence-guided search control could improve. In-context learning constraints: the finite context window fundamentally limits how much experience can inform any single decision; the fact deque/compression mechanism can 'forget' still-relevant older facts, with compression fidelity being only heuristic; and the rate/ceiling of in-context learning may be inherently constrained relative to weight-fine-tuning approaches. Theoretical framework and assumptions: the paper's motivating bisimulation-based bounds rely on an idealized abstraction function that the LLM-driven fact extractor only approximates, with the quality of that approximation unverifiable in practice, and quantities like the epsilon_sim and delta_model proxies are difficult to directly measure empirically, so the theoretical bounds' tightness cannot be verified. Broader considerations: performance is intrinsically tied to and limited by the underlying LLM's capabilities; the system exhibits prompt sensitivity requiring careful engineering; evaluation is currently confined to text-based environments, with extension to continuous, multi-modal, or otherwise more complex environments requiring further adaptation; the lookahead search is primarily exploitation-oriented with no explicit exploration mechanism; and the reliance on multiple LLM calls per lookahead step raises real computational/API cost concerns for deployment.</t>
+          <t>Explicit 'Limitations and Future Agenda' section (Section 8) with two subsections. 'Scope of claims and TCB boundary' states the formal guarantees operate within explicit threat-model and TCB boundary conditions: covert timing channels from an actively malicious model remain out of scope; enforcement relies on declared contract labels and registered derivation functions, with sanitizer correctness residing within the TCB, and an undeclared write-side contract admits a store-mediated laundering path (empirically observed in the joint-merger-brief evaluation scenario); and context branching enforces trajectory isolation rather than transactional rollback of side effects, so external network egresses committed by a child branch before discard cannot be reverted. 'Empirical bounds and future evaluation agenda' notes bench-corp provides tight causal isolation for mechanism probing over a controlled/synthetic tool surface but does not establish operational effectiveness on production enterprise workloads, identifying four concrete future-evaluation needs: (1) real-world task ambiguity and diverse organizational policies; (2) multi-model generalization across model families and prompting strategies; (3) quantifying long-horizon behavior and resource overheads (latency, token consumption); and (4) measuring human approval fatigue and policy-authoring ergonomics in realistic deployment settings. The Methodological Scope paragraph also separately notes high utility scores demonstrate capable models can leverage APPA's primitives under controlled policy constraints, but do not imply general performance on unconstrained real-world workloads.</t>
         </is>
       </c>
       <c r="F152" s="5" t="n"/>
@@ -7761,7 +7749,7 @@
       <c r="H152" s="5" t="n"/>
       <c r="I152" s="5" t="inlineStr">
         <is>
-          <t>93f50fbd4ed8303e86ebb5946339bb103a234ab5</t>
+          <t>a627218ebc531a61b3f43df433c8034165e32ba9</t>
         </is>
       </c>
     </row>
@@ -7771,7 +7759,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Fact-Augmented Lookahead Planning for LLM Agents</t>
+          <t>Agentic Permissions Policy Algebra for Taint Confinement in LLM Agents</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -7786,7 +7774,7 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>LWM-Planner is a fact-augmented lookahead planning framework for LLM agents that improves behavior purely through in-context learning, without any parameter updates. After each episode, the agent extracts task-critical 'atomic facts' (concise textual statements such as 'object X is in receptacle_Y' or 'action Z leads_to_failure_condition') from its interaction trajectory, validates candidate facts with a lightweight predictive-consistency filter, and optionally compresses the accumulated fact set to keep it within the LLM's context window (managed via a deque plus optional LLM-based compression). This curated fact set then conditions three LLM-driven planning components used within a recursive, depth-limited lookahead search at test time: an action proposer that suggests plausible next actions, a latent world model that simulates the next observation, reward, and termination status given a candidate action (acting as the LLM's own internal, fact-conditioned simulator rather than a separately learned predictive model), and a state-value estimator that predicts long-term utility at the search frontier, combined via Q(o_t, a_i) = r' - lambda_step + gamma * V_hat(o') to select actions. The design is explicitly motivated (though not formally guaranteed) by a fact-based state-abstraction framework borrowed from bisimulation theory: an idealized fact-based agent (IFBA) is defined whose abstraction achieves an epsilon_sim-approximate bisimulation with the true environment MDP, and the paper frames atomic facts as reducing state aliasing (approximating epsilon_sim) while fact-conditioned simulation targets lower one-step model error (approximating delta_model), together aiming to reduce overall planning sub-optimality -- explicitly framed as motivating intuition rather than proven bounds for the practical LWM-Planner system. The architecture is inspired by Dyna-style model-based RL (alternating experience collection, model learning, and planning), but implements the 'model' implicitly as an LLM conditioned on a growing, curated set of distilled textual facts rather than a separately trained predictive model, enabling the agent to learn online across episodes purely through the evolving in-context fact set.</t>
+          <t>APPA (Agentic Permissions Policy Algebra) is a dynamic Information Flow Control (IFC) framework for LLM agents that addresses 'label creep,' the usability bottleneck in traditional taint tracking where reading any restricted/unvetted data permanently elevates an agent's context confidentiality level, revoking access to downstream tools for the rest of the task. APPA introduces two core mechanisms. First, branching for taint confinement: rather than letting a sensitive read permanently pollute the primary execution context, APPA isolates sensitive computations within disposable, label-seeded child trajectory branches that inherit a pre-branch transcript snapshot and operate under narrowed permissions; upon exit, only clean sanitized derivatives or explicitly accepted returns merge back into the unchanged parent context via a checked exit, while raw returns that would narrow the parent's permissions are blocked pending explicit acceptance or a remedy plan. Second, prospective acquisition enforcement: rather than silently failing or requiring developers to scatter ad-hoc guardrail logic throughout agent code, APPA evaluates policy constraints (label descents, missing prerequisites) prior to tool execution/data acquisition, generating structured, actionable remedy plans (Authorize, Accept, or redispatch) when a prospective tool call would narrow permissions or trigger a policy violation, resolved through single-call atomic authority rulings without persistent privilege escalation. The framework is governed by a formal two-monoid model over security labels and a shared, durable, append-only event log, under which the authors formally prove two properties: parent label preservation (the primary context's confidentiality/integrity labels are never degraded by child-branch activity) and merge confinement (only explicitly authorized, bounded derivatives can cross from child back to parent). APPA is positioned against Fides (the closest prior antecedent, which mitigates label creep by hiding restrictive fields in planner variables post-execution rather than branching prospectively) and other online agent safety/IFC frameworks (CaMeL's dual-LLM structural isolation, ACE's abstract-concrete two-phase static verification, MemLineage's cross-session memory-provenance gating, TACIT's capability-safe code synthesis), differing in operating dynamically at the tool-dispatch layer via pre-dispatch hooks with trajectory-level (not just per-execution or cross-session) branching.</t>
         </is>
       </c>
       <c r="F153" s="5" t="n"/>
@@ -7794,7 +7782,7 @@
       <c r="H153" s="5" t="n"/>
       <c r="I153" s="5" t="inlineStr">
         <is>
-          <t>93f50fbd4ed8303e86ebb5946339bb103a234ab5</t>
+          <t>a627218ebc531a61b3f43df433c8034165e32ba9</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7792,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
+          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -7827,7 +7815,7 @@
       <c r="H154" s="5" t="n"/>
       <c r="I154" s="5" t="inlineStr">
         <is>
-          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
+          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
         </is>
       </c>
     </row>
@@ -7837,7 +7825,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
+          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -7860,7 +7848,7 @@
       <c r="H155" s="5" t="n"/>
       <c r="I155" s="5" t="inlineStr">
         <is>
-          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
+          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
         </is>
       </c>
     </row>
@@ -7870,7 +7858,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
+          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -7893,7 +7881,7 @@
       <c r="H156" s="5" t="n"/>
       <c r="I156" s="5" t="inlineStr">
         <is>
-          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
+          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
         </is>
       </c>
     </row>
@@ -7903,7 +7891,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
+          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -7918,7 +7906,7 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>neither</t>
+          <t>defense</t>
         </is>
       </c>
       <c r="F157" s="5" t="n"/>
@@ -7926,7 +7914,7 @@
       <c r="H157" s="5" t="n"/>
       <c r="I157" s="5" t="inlineStr">
         <is>
-          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
+          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
         </is>
       </c>
     </row>
@@ -7936,7 +7924,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
+          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -7951,7 +7939,7 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>cross-modal</t>
         </is>
       </c>
       <c r="F158" s="5" t="n"/>
@@ -7959,7 +7947,7 @@
       <c r="H158" s="5" t="n"/>
       <c r="I158" s="5" t="inlineStr">
         <is>
-          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
+          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
         </is>
       </c>
     </row>
@@ -7969,7 +7957,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
+          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -7992,7 +7980,7 @@
       <c r="H159" s="5" t="n"/>
       <c r="I159" s="5" t="inlineStr">
         <is>
-          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
+          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
         </is>
       </c>
     </row>
@@ -8002,7 +7990,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
+          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -8025,7 +8013,7 @@
       <c r="H160" s="5" t="n"/>
       <c r="I160" s="5" t="inlineStr">
         <is>
-          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
+          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8023,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
+          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -8050,7 +8038,7 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F161" s="5" t="n"/>
@@ -8058,7 +8046,7 @@
       <c r="H161" s="5" t="n"/>
       <c r="I161" s="5" t="inlineStr">
         <is>
-          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
+          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
         </is>
       </c>
     </row>
@@ -8068,7 +8056,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
+          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -8091,7 +8079,7 @@
       <c r="H162" s="5" t="n"/>
       <c r="I162" s="5" t="inlineStr">
         <is>
-          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
+          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8089,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
+          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -8116,7 +8104,7 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>session-persistent</t>
+          <t>one-shot</t>
         </is>
       </c>
       <c r="F163" s="5" t="n"/>
@@ -8124,7 +8112,7 @@
       <c r="H163" s="5" t="n"/>
       <c r="I163" s="5" t="inlineStr">
         <is>
-          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
+          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8122,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
+          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -8157,7 +8145,7 @@
       <c r="H164" s="5" t="n"/>
       <c r="I164" s="5" t="inlineStr">
         <is>
-          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
+          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
         </is>
       </c>
     </row>
@@ -8167,7 +8155,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
+          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -8182,7 +8170,7 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>Code is publicly released at https://github.com/xbmxb/EnvDistraction, including the simulated distraction dataset (1198 samples across four subsets: Pop-up box, Search, Recommendation, Chat), the data construction pipeline (Algorithm 1), and the three working-pattern evaluation prompts/harness used across ten MLLM agents.</t>
         </is>
       </c>
       <c r="F165" s="5" t="n"/>
@@ -8190,7 +8178,7 @@
       <c r="H165" s="5" t="n"/>
       <c r="I165" s="5" t="inlineStr">
         <is>
-          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
+          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
         </is>
       </c>
     </row>
@@ -8200,7 +8188,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
+          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -8215,7 +8203,7 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>Human-evaluated frontier set: o1-preview, GPT-4o (August 2024), Gemini 1.5 Pro (August 27 2024), Claude 3.5 Sonnet (June 2024), Mistral Large, Llama 3.1 405B Instruct; auto-evaluated open-source set: Llama-3.2-3B-Instruct, Llama-3.3-70B-Instruct, Qwen2-72B-Instruct, Qwen2.5-14B-Instruct, Qwen2.5-72B-Instruct, Mixtral-8x7B-Instruct-v0.1, Mixtral-8x22B-Instruct-v0.1; GPT-4o and Claude used as the automatic LLM-judge base models</t>
+          <t>Ten MLLMs: generalist black-box agents GPT-4v, GPT-4o, GLM-4v, Qwen-VL-plus, and Claude-Sonnet-3.5; open-source generalist MLLMs Qwen-VL-chat-7B, MiniCPM-Llama3-V2.5, and LLaVa-v1.6-34B; and specialist GUI agents CogAgent-chat and SeeClick. For the faithfulness-improvement experiment, Llama-3.1-8B-Instruct is fine-tuned with LoRA via DPO.</t>
         </is>
       </c>
       <c r="F166" s="5" t="n"/>
@@ -8223,7 +8211,7 @@
       <c r="H166" s="5" t="n"/>
       <c r="I166" s="5" t="inlineStr">
         <is>
-          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
+          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
         </is>
       </c>
     </row>
@@ -8233,7 +8221,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
+          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -8248,7 +8236,7 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>MultiChallenge (new benchmark introduced by this paper): 273 multi-turn (up to 10-turn) human-LLM test conversations across 4 challenge categories - Instruction Retention (69), Inference Memory of user information (113), Reliable Versioned Editing (41), Self-Coherence/avoiding sycophancy (50) - generated via a multi-agent synthetic pipeline (MMSE: Planner/User/Responder agents) grounded in hierarchical topic seeds and PersonaHub personas, then human-reviewed/edited; compared against prior multi-turn benchmarks MT-Bench and MT-Eval as context for benchmark saturation</t>
+          <t>A self-constructed simulated dataset of 1198 GUI screenshots across four distraction scenarios: Pop-up box (662 samples: 208+220+234 across 3 layout templates), Search (250 samples, built on real Google Search API results with GPT-4-generated fake results inserted), Recommendation (176 samples, using a BM25 retriever over Amazon Reviews with a GPT-4-fabricated fake product inserted), and Chat (110 samples, built on Discord chat rooms with dialogue-based distractions). A DPO training pseudo-dataset sampled from Alpaca is also used for the faithfulness-improvement experiment.</t>
         </is>
       </c>
       <c r="F167" s="5" t="n"/>
@@ -8256,7 +8244,7 @@
       <c r="H167" s="5" t="n"/>
       <c r="I167" s="5" t="inlineStr">
         <is>
-          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
+          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
         </is>
       </c>
     </row>
@@ -8266,7 +8254,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
+          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -8281,7 +8269,7 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>All 6 frontier LLMs score below 50% average accuracy on MultiChallenge despite near-perfect scores on existing multi-turn benchmarks (MT-Bench, MT-Eval); the best model, Claude 3.5 Sonnet (June 2024), achieves only 41.4% average accuracy (human-evaluated), followed by o1-preview at 34.6% and Gemini 1.5 Pro at 19.1%. Performance varies sharply by challenge category (e.g. Claude scores 58.6% on Instruction Retention but only 24.4% on Reliable Versioned Editing; o1-preview leads on Inference Memory at 41.5% and Reliable Versioned Editing at 39.0%). The proposed LLM-as-judge with instance-level binary rubrics achieves 93.9% alignment with human raters, versus only 36.0% for a naive full-context LLM-judge baseline. Larger open-source models (70-72B range) tend to outperform smaller ones, but all tested open-source models fall behind the top closed-source models. Conversation length (number of turns) does not correlate with difficulty, indicating the challenge stems from reasoning/attention-allocation requirements rather than sheer context length.</t>
+          <t>Every evaluated MLLM is measurably susceptible to environmental distraction: the strongest generalist model, GPT-4o, still produces distracted actions (Accdist) in 9.09% of direct-prompt cases overall, and the best specialist agent SeeClick is distracted 6.84% of the time, while weaker models like Qwen-VL-plus are distracted up to 76.92% under CoT prompting on the Pop-up box subset. Providing explicit action annotations to reduce perception burden often worsens faithfulness rather than helping -- e.g., GPT-4v's Accdist rises from 6.57% (direct prompt) to 16.26% (action annotation) on Pop-up box, and SeeClick's distraction rate jumps from 2.17% to 12.42%. Under active adversarial environment injection (rewriting pop-up buttons), GPT-4o's Accdist rises from 5.00% baseline to 33.33-40.00% (attack success rate 6/8 goal cases) and GLM-4v's rises from 60.45% to as high as 70.83% (ASR 8/8). A DPO-based faithfulness fine-tuning of Llama-3.1-8B-Instruct improves Chat-subset Accgold from 31.8% (baseline) to 40.9%, but yields only modest gains on Pop-up box (37.0% to 37.3%).</t>
         </is>
       </c>
       <c r="F168" s="5" t="n"/>
@@ -8289,7 +8277,7 @@
       <c r="H168" s="5" t="n"/>
       <c r="I168" s="5" t="inlineStr">
         <is>
-          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
+          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
         </is>
       </c>
     </row>
@@ -8299,7 +8287,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
+          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -8314,7 +8302,7 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>MT-Bench and MT-Eval cited as prior (now-saturated) multi-turn benchmarks for context, not directly re-run; a naive full-conversation-context LLM-as-judge auto-eval baseline compared against the paper's instance-level-rubric auto-eval method; comparison across 6 frontier and 7 open-source LLMs against each other on the new benchmark</t>
+          <t>The paper's own three working patterns (Direct prompt, CoT prompt, Action annotation) function as internal ablations/baselines against each other, isolating the effect of perception level on faithfulness. The DPO faithfulness-improvement method is compared against an untrained baseline model and a preference-aware prompting variant. No external prior defense system is used as a baseline since this is largely a novel-phenomenon measurement paper rather than a defense paper.</t>
         </is>
       </c>
       <c r="F169" s="5" t="n"/>
@@ -8322,7 +8310,7 @@
       <c r="H169" s="5" t="n"/>
       <c r="I169" s="5" t="inlineStr">
         <is>
-          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
+          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8320,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
+          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -8347,7 +8335,7 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>N/A - non-adversarial; evaluates incidental multi-turn conversational failure modes (losing track of early instructions, failing to recall/connect scattered user details, mishandling iterative document/plan editing, sycophantic self-contradiction), not attacker-injected content</t>
+          <t>Primarily non-adversarial: the paper's core setting is 'benign but risky' -- user and agent are both benign and non-malicious, and the environment, while not adversarial, naturally contains irrelevant or misleading content (ads, pop-ups, fake search/recommendation results, chat logs) that can unintentionally distract the GUI agent from the user's true goal. Section 5.1 additionally introduces an explicit adversarial extension (environment injection), where an attacker who can eavesdrop on the user's goal and modify the GUI environment (e.g., man-in-the-middle rewriting of HTML pop-up button text/labels) actively crafts distractions to mislead the agent into taking an unintended action, without altering the user's or agent's own behavior.</t>
         </is>
       </c>
       <c r="F170" s="5" t="n"/>
@@ -8355,7 +8343,7 @@
       <c r="H170" s="5" t="n"/>
       <c r="I170" s="5" t="inlineStr">
         <is>
-          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
+          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
         </is>
       </c>
     </row>
@@ -8365,7 +8353,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
+          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -8380,7 +8368,7 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>To keep the LLM-judge trustworthy, the authors cannot include test examples whose corresponding instance-level rubric question is itself beyond current frontier LLM judging capability, which potentially caps the difficulty level of the overall benchmark - harder examples are kept private and released only once auto-eval for them becomes feasible; the benchmark is inherently biased toward the 6 frontier models used to construct it, since test examples were selected specifically because at least 3 of those 6 models failed on them, so comparisons against other/future model families may be less fair (though open-source models tested still uniformly underperformed the top closed-source models, suggesting the bias does not fully explain the gap).</t>
+          <t>The paper has an explicit 'Limitations' section with three points: (i) the work does not itself develop or fully validate faithfulness-improvement solutions beyond a preliminary DPO experiment, leaving further exploration of faithfulness-aligned pre-training, contextual/instruction correlation modeling, action-consequence prediction, and human-feedback incorporation to future work; (ii) although the dataset simulates realistic distractions using an LLM-driven pipeline, it does not cover all possible vulnerable scenarios, and future work could build a more comprehensive distraction set via crowd-sourced annotation of real-world websites; (iii) the study quantifies unfaithfulness only via objective action-type accuracy and does not investigate the severity or downstream consequences of distracted actions, which is left for future work.</t>
         </is>
       </c>
       <c r="F171" s="5" t="n"/>
@@ -8388,7 +8376,7 @@
       <c r="H171" s="5" t="n"/>
       <c r="I171" s="5" t="inlineStr">
         <is>
-          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
+          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
         </is>
       </c>
     </row>
@@ -8398,7 +8386,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
+          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -8413,7 +8401,7 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>Introduces MultiChallenge, a realistic multi-turn conversation benchmark targeting four categories of challenges that are common in real human-LLM interactions yet difficult for frontier models: instruction retention (following a first-turn constraint throughout a long conversation), inference memory (recalling and connecting user details scattered across earlier turns to implicitly inform a later response), reliable versioned editing (correctly tracking and editing across multiple revised versions of a document/plan through back-and-forth turns), and self-coherence (avoiding sycophantic self-contradiction when a user later questions a prior correct response). Test conversations (up to 10 turns) are produced via a hybrid multi-agent synthetic-data pipeline (Planner, User, and Responder agents grounded in hierarchical topics and diverse personas) followed by human review/editing, and evaluated with a novel LLM-as-judge method using per-example binary instance-level rubrics that achieves 93.9% alignment with human raters (vs. 36.0% for naive full-context LLM judging). Despite near-perfect performance on existing multi-turn benchmarks, all 6 tested frontier LLMs (o1-preview, GPT-4o, Gemini 1.5 Pro, Claude 3.5 Sonnet, Mistral Large, Llama 3.1 405B) score below 50% average accuracy on MultiChallenge, with the best model reaching only 41.4%, demonstrating that current frontier LLMs still struggle substantially with realistic multi-turn conversational demands beyond simple instruction-following.</t>
+          <t>This paper studies whether multimodal GUI agents remain faithful to user goals when operating in benign but content-rich environments that contain irrelevant distractions (ads, pop-ups, fake search/recommendation results, misleading chat messages) -- explicitly distinguishing this from adversarial prompt injection or jailbreak settings, since both the user and the agent are assumed benign. The authors build a 1198-sample simulated dataset across four scenario subsets (Pop-up box, Search, Recommendation, Chat) via an LLM-driven construction pipeline that inserts distracting but non-malicious content into realistic GUI screenshots, then evaluate 10 MLLM-based GUI agents (5 generalist API models, 3 open-source generalist models, 2 specialist GUI agents) under three working patterns offering progressively more explicit perception support (raw image only, chain-of-thought over the image, and explicit action-space annotations). They find universal susceptibility to distraction across all models and patterns, that stronger perceptual/action-space information does not reliably reduce distraction and can even increase it, and that faithfulness and helpfulness are correlated rather than in tension for the strongest models. The paper further demonstrates an adversarial 'environment injection' attack -- rewriting pop-up button semantics to be ambiguous or emotionally persuasive -- that substantially raises distraction rates (up to 8/8 attack success against GLM-4v), and proposes a preliminary faithfulness-improvement method using a special input token plus DPO fine-tuning (on Llama-3.1-8B-Instruct) to teach the model to prioritize the user's goal channel over environmental feedback, yielding modest to substantial gains depending on the scenario.</t>
         </is>
       </c>
       <c r="F172" s="5" t="n"/>
@@ -8421,7 +8409,7 @@
       <c r="H172" s="5" t="n"/>
       <c r="I172" s="5" t="inlineStr">
         <is>
-          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
+          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
         </is>
       </c>
     </row>
@@ -8431,7 +8419,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>ReAcTree: Hierarchical LLM Agent Trees with Control Flow for Long-Horizon Task Planning</t>
+          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -8454,7 +8442,7 @@
       <c r="H173" s="5" t="n"/>
       <c r="I173" s="5" t="inlineStr">
         <is>
-          <t>adfb2a3dd1d4913fb68f057a0b92c4aa224adcea</t>
+          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
         </is>
       </c>
     </row>
@@ -8464,7 +8452,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>ReAcTree: Hierarchical LLM Agent Trees with Control Flow for Long-Horizon Task Planning</t>
+          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -8479,7 +8467,7 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>ML/AI</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="F174" s="5" t="n"/>
@@ -8487,7 +8475,7 @@
       <c r="H174" s="5" t="n"/>
       <c r="I174" s="5" t="inlineStr">
         <is>
-          <t>adfb2a3dd1d4913fb68f057a0b92c4aa224adcea</t>
+          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
         </is>
       </c>
     </row>
@@ -8497,7 +8485,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>ReAcTree: Hierarchical LLM Agent Trees with Control Flow for Long-Horizon Task Planning</t>
+          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
@@ -8520,7 +8508,7 @@
       <c r="H175" s="5" t="n"/>
       <c r="I175" s="5" t="inlineStr">
         <is>
-          <t>adfb2a3dd1d4913fb68f057a0b92c4aa224adcea</t>
+          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8518,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>ReAcTree: Hierarchical LLM Agent Trees with Control Flow for Long-Horizon Task Planning</t>
+          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
@@ -8545,7 +8533,7 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>neither</t>
+          <t>defense</t>
         </is>
       </c>
       <c r="F176" s="5" t="n"/>
@@ -8553,7 +8541,7 @@
       <c r="H176" s="5" t="n"/>
       <c r="I176" s="5" t="inlineStr">
         <is>
-          <t>adfb2a3dd1d4913fb68f057a0b92c4aa224adcea</t>
+          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
         </is>
       </c>
     </row>
@@ -8563,7 +8551,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>ReAcTree: Hierarchical LLM Agent Trees with Control Flow for Long-Horizon Task Planning</t>
+          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
@@ -8578,7 +8566,7 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>tool-output</t>
         </is>
       </c>
       <c r="F177" s="5" t="n"/>
@@ -8586,7 +8574,7 @@
       <c r="H177" s="5" t="n"/>
       <c r="I177" s="5" t="inlineStr">
         <is>
-          <t>adfb2a3dd1d4913fb68f057a0b92c4aa224adcea</t>
+          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
         </is>
       </c>
     </row>
@@ -8596,7 +8584,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>ReAcTree: Hierarchical LLM Agent Trees with Control Flow for Long-Horizon Task Planning</t>
+          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -8611,7 +8599,7 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="F178" s="5" t="n"/>
@@ -8619,7 +8607,7 @@
       <c r="H178" s="5" t="n"/>
       <c r="I178" s="5" t="inlineStr">
         <is>
-          <t>adfb2a3dd1d4913fb68f057a0b92c4aa224adcea</t>
+          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
         </is>
       </c>
     </row>
@@ -8629,7 +8617,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>ReAcTree: Hierarchical LLM Agent Trees with Control Flow for Long-Horizon Task Planning</t>
+          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
@@ -8644,7 +8632,7 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F179" s="5" t="n"/>
@@ -8652,7 +8640,7 @@
       <c r="H179" s="5" t="n"/>
       <c r="I179" s="5" t="inlineStr">
         <is>
-          <t>adfb2a3dd1d4913fb68f057a0b92c4aa224adcea</t>
+          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
         </is>
       </c>
     </row>
@@ -8662,7 +8650,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>ReAcTree: Hierarchical LLM Agent Trees with Control Flow for Long-Horizon Task Planning</t>
+          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -8677,7 +8665,7 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F180" s="5" t="n"/>
@@ -8685,7 +8673,7 @@
       <c r="H180" s="5" t="n"/>
       <c r="I180" s="5" t="inlineStr">
         <is>
-          <t>adfb2a3dd1d4913fb68f057a0b92c4aa224adcea</t>
+          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
         </is>
       </c>
     </row>
@@ -8695,7 +8683,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>ReAcTree: Hierarchical LLM Agent Trees with Control Flow for Long-Horizon Task Planning</t>
+          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
@@ -8710,7 +8698,7 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>reasoning</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F181" s="5" t="n"/>
@@ -8718,7 +8706,7 @@
       <c r="H181" s="5" t="n"/>
       <c r="I181" s="5" t="inlineStr">
         <is>
-          <t>adfb2a3dd1d4913fb68f057a0b92c4aa224adcea</t>
+          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
         </is>
       </c>
     </row>
@@ -8728,7 +8716,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>ReAcTree: Hierarchical LLM Agent Trees with Control Flow for Long-Horizon Task Planning</t>
+          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
@@ -8743,7 +8731,7 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>session-persistent</t>
+          <t>one-shot</t>
         </is>
       </c>
       <c r="F182" s="5" t="n"/>
@@ -8751,7 +8739,7 @@
       <c r="H182" s="5" t="n"/>
       <c r="I182" s="5" t="inlineStr">
         <is>
-          <t>adfb2a3dd1d4913fb68f057a0b92c4aa224adcea</t>
+          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
         </is>
       </c>
     </row>
@@ -8761,7 +8749,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>ReAcTree: Hierarchical LLM Agent Trees with Control Flow for Long-Horizon Task Planning</t>
+          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
@@ -8784,7 +8772,7 @@
       <c r="H183" s="5" t="n"/>
       <c r="I183" s="5" t="inlineStr">
         <is>
-          <t>adfb2a3dd1d4913fb68f057a0b92c4aa224adcea</t>
+          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
         </is>
       </c>
     </row>
@@ -8794,7 +8782,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>ReAcTree: Hierarchical LLM Agent Trees with Control Flow for Long-Horizon Task Planning</t>
+          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
@@ -8809,7 +8797,7 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>The paper states 'The code is available at https://github.com/Choi-JaeWoo/ReAcTree.git,' confirming a public code release directly in the abstract.</t>
+          <t>No code/dataset release -- this is a practitioner systematization paper describing production experience, explicitly disclosing 'no proprietary, confidential, or customer-identifying information of any organization,' and describing only generally applicable architectural patterns rather than releasing an implementation.</t>
         </is>
       </c>
       <c r="F184" s="5" t="n"/>
@@ -8817,7 +8805,7 @@
       <c r="H184" s="5" t="n"/>
       <c r="I184" s="5" t="inlineStr">
         <is>
-          <t>adfb2a3dd1d4913fb68f057a0b92c4aa224adcea</t>
+          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8815,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>ReAcTree: Hierarchical LLM Agent Trees with Control Flow for Long-Horizon Task Planning</t>
+          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
@@ -8842,7 +8830,7 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>Seven open-source LLMs spanning small (7-14B) and large (70-72B) scales are evaluated in a few-shot in-context learning setting without fine-tuning: LLaMA 3.1 8B, LLaMA 3.1 70B, Qwen 2.5 7B, Qwen 2.5 72B, Mistral 7B, Gemma 2 9B, and Phi-4-reasoning-plus 14B.</t>
+          <t>No specific LLM model names/versions are disclosed; the paper describes an MCP/RAG/A2A (Model Context Protocol / Retrieval-Augmented Generation / Agent-to-Agent) multi-agent architecture used in production for a Know Your Customer (KYC) onboarding pipeline, without naming the underlying foundation model(s).</t>
         </is>
       </c>
       <c r="F185" s="5" t="n"/>
@@ -8850,7 +8838,7 @@
       <c r="H185" s="5" t="n"/>
       <c r="I185" s="5" t="inlineStr">
         <is>
-          <t>adfb2a3dd1d4913fb68f057a0b92c4aa224adcea</t>
+          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
         </is>
       </c>
     </row>
@@ -8860,7 +8848,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>ReAcTree: Hierarchical LLM Agent Trees with Control Flow for Long-Horizon Task Planning</t>
+          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
@@ -8875,7 +8863,7 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>The paper extends LoTa-Bench, evaluating on two embodied household-task dataset-simulator pairs adapted to a more challenging partially observable setting: WAH-NL with the VirtualHome simulator (6 primitive actions: go to, pick up, put down, open, close, turn on) and ALFRED with the AI2THOR simulator (8 primitive actions, adding turn off and slice; 7 task types). A rule-based observation generator was implemented for both simulators to support partial observability (revealing only visible objects/receptacles after each action, rather than full ground-truth state).</t>
+          <t>No standard benchmark; this is a single production case study of a consumer credit KYC onboarding deployment. No dataset statistics beyond aggregate operational outcomes (e.g., referral rate, unservable-applicant rate) are reported, and no per-instance evaluation data is released given the confidentiality constraints.</t>
         </is>
       </c>
       <c r="F186" s="5" t="n"/>
@@ -8883,7 +8871,7 @@
       <c r="H186" s="5" t="n"/>
       <c r="I186" s="5" t="inlineStr">
         <is>
-          <t>adfb2a3dd1d4913fb68f057a0b92c4aa224adcea</t>
+          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
         </is>
       </c>
     </row>
@@ -8893,7 +8881,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>ReAcTree: Hierarchical LLM Agent Trees with Control Flow for Long-Horizon Task Planning</t>
+          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
@@ -8908,7 +8896,7 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>On WAH-NL, ReAcTree+WM achieves a 61% goal success rate (GSR) with Qwen 2.5 72B, nearly doubling ReAct+WM's 31% under the same model, and raises subgoal success rate (SSR) from 54.05% to 79.58%; even with a much smaller Qwen 2.5 7B model, ReAcTree+WM reaches 37% GSR, surpassing all baselines including much larger models like Qwen 2.5 72B and LLaMA 3.1 70B run with ReAct/ReAct+WM. Across all seven LLM backbones, both ReAcTree and its working-memory variant consistently outperform five baselines (ZSP, Tree-Planner with N=25/50 sampled plans, ReAct, ReAct+WM), with ZSP performing worst (0-1% GSR across most models) due to its inability to adapt a single upfront plan under partial observability, and Tree-Planner showing only marginal gains over ZSP because its plan-sampling approach becomes intractable as the search space grows (e.g., multiple candidate receptacles in a kitchen) without prior knowledge of target object locations. Memory ablations on Qwen 2.5 7B/72B show episodic memory (EM) and working memory (WM) exhibit strong synergy, with combined EM+WM outperforming either alone or neither. Control-flow ablations show using all three control flow types (sequence, fallback, parallel) consistently yields the best performance versus restricted subsets. Computational analysis shows ReAcTree maintains well-bounded, stable token usage per decision step due to its modular structure (each agent node processes only a localized subgoal), in contrast to ReAct+WM (70B), which shows the highest peak input token count (8,316) and highest variance, indicating greater and less predictable GPU memory overhead; notably ReAcTree+WM (8B) achieves performance comparable to ReAct+WM (70B) while being significantly faster. A failure case analysis of 39 ReAcTree+WM (Qwen 2.5 72B) failures on WAH-NL categorized errors into four types: Search failures (13, the most frequent, from incomplete exploration under partial observability), Execution failures (12, largely from LLM hallucination such as object confusion), Ambiguous cases (10, from vague instructions), and Expand failures (4, from incorrect subgoal decomposition).</t>
+          <t>The four documented architectural patterns collectively moved KYC onboarding from a multi-day manual process to same-day automated resolution for roughly four in five cases (Pattern A: A2A compliance choreography). Pattern B (grounded-RAG-for-audit, using a versioned policy store with human sign-off gate and version-hash+timestamp logging) ensured every step-up verification decision was grounded in a specific, approved policy version. Pattern C (case-ID propagation, a mandatory case-ID header on every MCP tool call) made the full tool-call chain reconstructable from a case ID alone, satisfying ECOA's adverse-action traceability requirement, at the cost of requiring every existing MCP tool to be retrofitted to accept and propagate the identifier. Pattern D (an inference-boundary redaction proxy that sends only extracted, PII-stripped/tokenized fields to the model rather than raw documents) narrowed the prompt-injection surface to a constrained set of extracted field values (explicitly not claimed to be eliminated) and removed the third-party inference endpoint from resident-PII handling scope, at the cost of losing model context for edge cases outside the predefined extraction schema, contributing to the roughly one-in-five referral rate. Three negative results are reported (Table II): (A) a stale-policy control failure, where a human sign-off gate approving a compliance-document update lagged behind an automated feed, causing the agent to apply superseded step-up-verification policy and systematically over-verify customers who no longer required it -- a UDAAP concern, caught only by internal audit, not by the agent system or its own monitoring; (B) MCP tool interfaces were found not to be designed for audit by default, since tool-call signatures carry no case-ID, session, or provenance information natively, requiring a costly retrofit and re-validation of every existing tool; (C) roughly one in nine (11%) legitimate applicants could not be served by the automated pipeline at all, because the deployment's mandatory two-factor authentication precondition (two active contact channels) excluded single-channel applicants regardless of creditworthiness or identity-verification status, and this exception path was evaluated and abandoned as economically unsupportable.</t>
         </is>
       </c>
       <c r="F187" s="5" t="n"/>
@@ -8916,7 +8904,7 @@
       <c r="H187" s="5" t="n"/>
       <c r="I187" s="5" t="inlineStr">
         <is>
-          <t>adfb2a3dd1d4913fb68f057a0b92c4aa224adcea</t>
+          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
         </is>
       </c>
     </row>
@@ -8926,7 +8914,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>ReAcTree: Hierarchical LLM Agent Trees with Control Flow for Long-Horizon Task Planning</t>
+          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -8941,7 +8929,7 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>ReAcTree and ReAcTree+WM are compared against five baselines under identical retrieval size and decision caps: ZSP (generates a complete plan upfront, without adaptation), Tree-Planner (N=25 or N=50 sampled high-level plans forming an action tree adapted via observations), ReAct (interleaved reasoning-acting without hierarchical decomposition), and ReAct+WM (ReAct augmented with the same working-memory mechanism used in ReAcTree, serving as the strongest baseline and used as the sole comparison point on ALFRED).</t>
+          <t>No quantitative baseline systems are compared; the paper instead systematically maps six established agentic threat categories (prompt injection, identity and authorization, action auditability, tool abuse, data residency, boundary policy enforcement) from prior academic security literature onto the specific, legally mandated control obligations of US and EU financial regulation (ECOA/Regulation B, EU AI Act, GDPR Article 22, FINRA's 2026 agent guidance), arguing this is the first work to bridge laboratory-based academic threat taxonomies with non-peer-reviewed practitioner/compliance guidance for regulated deployment.</t>
         </is>
       </c>
       <c r="F188" s="5" t="n"/>
@@ -8949,7 +8937,7 @@
       <c r="H188" s="5" t="n"/>
       <c r="I188" s="5" t="inlineStr">
         <is>
-          <t>adfb2a3dd1d4913fb68f057a0b92c4aa224adcea</t>
+          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8947,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>ReAcTree: Hierarchical LLM Agent Trees with Control Flow for Long-Horizon Task Planning</t>
+          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
@@ -8974,7 +8962,7 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>N/A - non-adversarial. This is an embodied agent task-planning capability paper, not a security paper. The incidental failure mode of interest is error accumulation and hallucination in long-horizon planning: single monolithic-trajectory approaches entangle all past decisions and observations from multiple subgoals into one unified reasoning process, increasing the risk of hallucination and logical failures as the trajectory grows, particularly under partial observability where the agent cannot see the full environment state at once.</t>
+          <t>The paper maps six established agentic threat categories from prior literature (prompt injection, identity and authorization, action auditability, tool abuse, data residency, and boundary policy enforcement) onto specific regulatory control obligations, arguing that legal accountability amplifies each threat relative to an unregulated deployment (e.g., an unresolved prompt injection is not just a security incident but a potential ECOA adverse-action-traceability failure or GDPR Article 22 automated-decision violation). The central prompt-injection-relevant finding (Pattern D) is that raw customer documents sent directly to a model inference endpoint simultaneously create the widest injection surface (untrusted document content could carry an injected instruction) and the least-controllable data-residency boundary (often a third-party service in a different jurisdiction); the mitigating architecture performs structured extraction and PII redaction/tokenization before any data reaches the inference endpoint, narrowing but not claiming to eliminate the injection surface to a constrained set of extracted field values.</t>
         </is>
       </c>
       <c r="F189" s="5" t="n"/>
@@ -8982,7 +8970,7 @@
       <c r="H189" s="5" t="n"/>
       <c r="I189" s="5" t="inlineStr">
         <is>
-          <t>adfb2a3dd1d4913fb68f057a0b92c4aa224adcea</t>
+          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
         </is>
       </c>
     </row>
@@ -8992,7 +8980,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>ReAcTree: Hierarchical LLM Agent Trees with Control Flow for Long-Horizon Task Planning</t>
+          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -9007,7 +8995,7 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>The paper has no section explicitly titled 'Limitations,' but the Conclusion contains a clearly demarcated limitations discussion introduced with 'Despite these benefits, ReAcTree still faces LLM-specific challenges.' It states that ReAcTree still faces hallucinations and has limited capability to recognize its own failures; it also lacks mechanisms to revise incorrectly expanded subgoals once created, and lacks mechanisms to handle instruction ambiguity (e.g., vague requests like 'give me 2 drinks' where object type or location is underspecified) via clarification dialogues with the user. These limitations are directly reflected in the paper's own failure case analysis, where Ambiguous, Execution (hallucination-driven), and Expand failure categories collectively account for 26 of 39 analyzed failures. The authors identify mitigating hallucination, refining subgoal correction mechanisms, and enabling clarification dialogues as future work directions.</t>
+          <t>No section explicitly titled 'Limitations,' but an entire dedicated 'Negative Results and Open Problems' section (Section V) serves this function with three concrete, documented failures/gaps: (1) no agent framework currently provides a native mechanism for policy-version synchronization with a compliance document lifecycle, leaving a compliance-relevant race window between policy update and human sign-off approval as an open problem; (2) auditability in regulated MCP deployments is an interface-design constraint that must be established before tools are built, not a logging concern addressable at the infrastructure layer -- current academic MCP security literature treats tool calls as atomic units to authenticate/authorize without considering provenance/traceability requirements, a gap organizations will discover at integration stage, 'the worst time to discover it'; (3) a fundamental, unresolved design limit where roughly one in nine legitimate applicants cannot be served due to two-factor-authentication preconditions, and no regulatory framework currently addresses systemic exclusion by technical precondition (ECOA prohibits discrimination on specified bases but not this kind of systemic exclusion), leaving open whether this dropout rate constitutes disparate impact under fair lending law. The paper also explicitly flags as future work a systematic cross-domain validation of its conjecture that auditability and least-privilege tool authorization are the two hardest-to-generalize controls across sectors beyond finance (healthcare/HIPAA, critical infrastructure, EU AI Act high-risk categories).</t>
         </is>
       </c>
       <c r="F190" s="5" t="n"/>
@@ -9015,7 +9003,7 @@
       <c r="H190" s="5" t="n"/>
       <c r="I190" s="5" t="inlineStr">
         <is>
-          <t>adfb2a3dd1d4913fb68f057a0b92c4aa224adcea</t>
+          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
         </is>
       </c>
     </row>
@@ -9025,7 +9013,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>ReAcTree: Hierarchical LLM Agent Trees with Control Flow for Long-Horizon Task Planning</t>
+          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -9040,7 +9028,7 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>ReAcTree addresses the problem that existing LLM-based embodied task-planning methods rely on a single monolithic trajectory that entangles all past decisions and observations across an entire long-horizon task into one unified reasoning process, which increases hallucination risk and logical failure propagation as the trajectory grows, and that tree-search-based alternatives typically assume reversible actions and the ability to roll back to prior simulator states, which is infeasible in real-world settings with irreversible actions (e.g., slicing an apple) and partial observability. ReAcTree instead dynamically constructs a hierarchical tree of two node types over the subgoal space (rather than over primitive actions): agent nodes, each an LLM-based ReAct-style planner responsible for a single natural-language subgoal, which can reason, act, or -- when the current subgoal proves too complex to solve directly -- expand the tree by proposing new child subgoals along with an associated control-flow type; and control flow nodes, inspired by behavior trees, which coordinate how their child agent nodes are executed (sequence, fallback, or parallel) and how outcomes propagate back up the tree. By isolating each subgoal within its own agent node's focused local context, ReAcTree reduces hallucination and logical-error propagation that would otherwise accumulate across an entire long trajectory, while also enabling targeted, subgoal-specific in-context example retrieval. This design is further strengthened by two complementary memory systems: episodic memory, which retrieves subgoal-level examples semantically similar to the current subgoal from a store bootstrapped by a small set of manually collected trajectories and gradually expanded with successful runs, improving each agent node's in-context learning; and working memory, a shared blackboard through which agent nodes exchange critical environment-specific observations (e.g., locations of movable objects already discovered by sibling nodes), reducing redundant search and further mitigating hallucination via collective situational awareness across the tree. Conceptually, the authors frame ReAcTree as extending the Least-to-Most prompting strategy from static, single-pass reasoning decomposition into dynamic, agentic, tree-structured planning under partial observability.</t>
+          <t>This is a practitioner systematization paper bridging two previously disconnected bodies of work: laboratory-based academic taxonomies of LLM agent security threats, and non-peer-reviewed practitioner/compliance guidance for regulated deployment. Drawing on production experience deploying MCP/RAG/A2A (Model Context Protocol, Retrieval-Augmented Generation, Agent-to-Agent) multi-agent systems to automate Know Your Customer (KYC) onboarding for a consumer credit product, the paper first maps six established agentic threat categories (prompt injection, identity and authorization, action auditability, tool abuse, data residency, boundary policy enforcement) onto specific control obligations imposed by US and EU financial regulation (ECOA and Regulation B, the EU AI Act, GDPR Article 22, and FINRA's 2026 agent guidance), arguing that legal accountability transforms each threat's stakes relative to an unregulated deployment. It then documents four architectural patterns actually used in production: (A) A2A compliance choreography, where an orchestrating agent sequences four specialized sub-agents that each emit structured output assembled into a pass/refer/reject determination with reasons; (B) grounded-RAG-for-audit, retrieving KYC policy exclusively from a versioned, human-approved RAG store with version-hash-and-timestamp logging per retrieval, so every automated decision is traceable to a specific approved policy version; (C) case-ID propagation, requiring every MCP tool call to carry a mandatory case-identifier header and log responses against it, creating a traversable audit chain from case-open to final recommendation and back; and (D) an inference-boundary redaction proxy, which performs structured field extraction and PII tokenization/stripping before any data reaches the (often third-party, cross-jurisdiction) model inference endpoint, simultaneously narrowing the prompt-injection attack surface (raw document text never reaches the model) and constraining data-residency exposure to only the extraction/proxy components. The paper's central conclusion is that securing agents under regulation is fundamentally less about novel attack classes and more about making auditability, least-privilege authorization, and boundary policy enforcement operationally real at production scale -- capabilities that current agent frameworks (including MCP tool-call specifications) leave entirely to the deploying engineer rather than providing natively.</t>
         </is>
       </c>
       <c r="F191" s="5" t="n"/>
@@ -9048,7 +9036,7 @@
       <c r="H191" s="5" t="n"/>
       <c r="I191" s="5" t="inlineStr">
         <is>
-          <t>adfb2a3dd1d4913fb68f057a0b92c4aa224adcea</t>
+          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
         </is>
       </c>
     </row>
@@ -9058,7 +9046,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Oblivion: Self-Adaptive Agentic Memory Control through Decay-Driven Activation</t>
+          <t>Attribute or Abstain: Large Language Models as Long Document Assistants</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -9081,7 +9069,7 @@
       <c r="H192" s="5" t="n"/>
       <c r="I192" s="5" t="inlineStr">
         <is>
-          <t>454069505d79f8b20538c78591702ac4dae921df</t>
+          <t>arxiv:2407.07799</t>
         </is>
       </c>
     </row>
@@ -9091,7 +9079,7 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>Oblivion: Self-Adaptive Agentic Memory Control through Decay-Driven Activation</t>
+          <t>Attribute or Abstain: Large Language Models as Long Document Assistants</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
@@ -9114,7 +9102,7 @@
       <c r="H193" s="5" t="n"/>
       <c r="I193" s="5" t="inlineStr">
         <is>
-          <t>454069505d79f8b20538c78591702ac4dae921df</t>
+          <t>arxiv:2407.07799</t>
         </is>
       </c>
     </row>
@@ -9124,7 +9112,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Oblivion: Self-Adaptive Agentic Memory Control through Decay-Driven Activation</t>
+          <t>Attribute or Abstain: Large Language Models as Long Document Assistants</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -9147,7 +9135,7 @@
       <c r="H194" s="5" t="n"/>
       <c r="I194" s="5" t="inlineStr">
         <is>
-          <t>454069505d79f8b20538c78591702ac4dae921df</t>
+          <t>arxiv:2407.07799</t>
         </is>
       </c>
     </row>
@@ -9157,7 +9145,7 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>Oblivion: Self-Adaptive Agentic Memory Control through Decay-Driven Activation</t>
+          <t>Attribute or Abstain: Large Language Models as Long Document Assistants</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
@@ -9172,7 +9160,7 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>defense</t>
+          <t>neither</t>
         </is>
       </c>
       <c r="F195" s="5" t="n"/>
@@ -9180,7 +9168,7 @@
       <c r="H195" s="5" t="n"/>
       <c r="I195" s="5" t="inlineStr">
         <is>
-          <t>454069505d79f8b20538c78591702ac4dae921df</t>
+          <t>arxiv:2407.07799</t>
         </is>
       </c>
     </row>
@@ -9190,7 +9178,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Oblivion: Self-Adaptive Agentic Memory Control through Decay-Driven Activation</t>
+          <t>Attribute or Abstain: Large Language Models as Long Document Assistants</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
@@ -9205,7 +9193,7 @@
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F196" s="5" t="n"/>
@@ -9213,7 +9201,7 @@
       <c r="H196" s="5" t="n"/>
       <c r="I196" s="5" t="inlineStr">
         <is>
-          <t>454069505d79f8b20538c78591702ac4dae921df</t>
+          <t>arxiv:2407.07799</t>
         </is>
       </c>
     </row>
@@ -9223,7 +9211,7 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>Oblivion: Self-Adaptive Agentic Memory Control through Decay-Driven Activation</t>
+          <t>Attribute or Abstain: Large Language Models as Long Document Assistants</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
@@ -9238,7 +9226,7 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="F197" s="5" t="n"/>
@@ -9246,7 +9234,7 @@
       <c r="H197" s="5" t="n"/>
       <c r="I197" s="5" t="inlineStr">
         <is>
-          <t>454069505d79f8b20538c78591702ac4dae921df</t>
+          <t>arxiv:2407.07799</t>
         </is>
       </c>
     </row>
@@ -9256,7 +9244,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Oblivion: Self-Adaptive Agentic Memory Control through Decay-Driven Activation</t>
+          <t>Attribute or Abstain: Large Language Models as Long Document Assistants</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
@@ -9279,7 +9267,7 @@
       <c r="H198" s="5" t="n"/>
       <c r="I198" s="5" t="inlineStr">
         <is>
-          <t>454069505d79f8b20538c78591702ac4dae921df</t>
+          <t>arxiv:2407.07799</t>
         </is>
       </c>
     </row>
@@ -9289,7 +9277,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>Oblivion: Self-Adaptive Agentic Memory Control through Decay-Driven Activation</t>
+          <t>Attribute or Abstain: Large Language Models as Long Document Assistants</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
@@ -9312,7 +9300,7 @@
       <c r="H199" s="5" t="n"/>
       <c r="I199" s="5" t="inlineStr">
         <is>
-          <t>454069505d79f8b20538c78591702ac4dae921df</t>
+          <t>arxiv:2407.07799</t>
         </is>
       </c>
     </row>
@@ -9322,7 +9310,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Oblivion: Self-Adaptive Agentic Memory Control through Decay-Driven Activation</t>
+          <t>Attribute or Abstain: Large Language Models as Long Document Assistants</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
@@ -9345,7 +9333,7 @@
       <c r="H200" s="5" t="n"/>
       <c r="I200" s="5" t="inlineStr">
         <is>
-          <t>454069505d79f8b20538c78591702ac4dae921df</t>
+          <t>arxiv:2407.07799</t>
         </is>
       </c>
     </row>
@@ -9355,7 +9343,7 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>Oblivion: Self-Adaptive Agentic Memory Control through Decay-Driven Activation</t>
+          <t>Attribute or Abstain: Large Language Models as Long Document Assistants</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
@@ -9370,7 +9358,7 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>session-persistent</t>
+          <t>one-shot</t>
         </is>
       </c>
       <c r="F201" s="5" t="n"/>
@@ -9378,7 +9366,7 @@
       <c r="H201" s="5" t="n"/>
       <c r="I201" s="5" t="inlineStr">
         <is>
-          <t>454069505d79f8b20538c78591702ac4dae921df</t>
+          <t>arxiv:2407.07799</t>
         </is>
       </c>
     </row>
@@ -9388,7 +9376,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Oblivion: Self-Adaptive Agentic Memory Control through Decay-Driven Activation</t>
+          <t>Attribute or Abstain: Large Language Models as Long Document Assistants</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
@@ -9411,7 +9399,7 @@
       <c r="H202" s="5" t="n"/>
       <c r="I202" s="5" t="inlineStr">
         <is>
-          <t>454069505d79f8b20538c78591702ac4dae921df</t>
+          <t>arxiv:2407.07799</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9409,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>Oblivion: Self-Adaptive Agentic Memory Control through Decay-Driven Activation</t>
+          <t>Attribute or Abstain: Large Language Models as Long Document Assistants</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
@@ -9436,7 +9424,7 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>Source code publicly released at https://github.com/nec-research/oblivion, as stated explicitly in a footnote in Section 4.1.</t>
+          <t>Code and data released via a GitHub repository under the Apache 2.0 license (footnote 1, exact URL not printed in the extracted text but referenced as 'Github repository, code under Apache 2.0, dataset licenses depend on original license'); the benchmark's constituent datasets retain their original licenses as documented in an appendix table.</t>
         </is>
       </c>
       <c r="F203" s="5" t="n"/>
@@ -9444,7 +9432,7 @@
       <c r="H203" s="5" t="n"/>
       <c r="I203" s="5" t="inlineStr">
         <is>
-          <t>454069505d79f8b20538c78591702ac4dae921df</t>
+          <t>arxiv:2407.07799</t>
         </is>
       </c>
     </row>
@@ -9454,7 +9442,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Oblivion: Self-Adaptive Agentic Memory Control through Decay-Driven Activation</t>
+          <t>Attribute or Abstain: Large Language Models as Long Document Assistants</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
@@ -9469,7 +9457,7 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>Four LLM backbones spanning open- and closed-weight models: Phi-4-mini-instruct-4B, Qwen3-30B-A3B-Instruct (open-weight), and GPT-4o-mini, GPT-4.1-mini (closed-weight/proprietary). text-embedding-3-small is used for all embedding-based retrieval. GPT-4o is used as the LLM-as-a-judge for scoring GoodAI-LTM scenarios.</t>
+          <t>Five LLMs across two size classes: large prompted models GPT-3.5 (gpt-35-turbo-0613-16k) and GPT-4 (gpt-4-turbo-128k), and small (~3-7B) models Longchat-7B-v1.5-32K and Mistral-7B-Instruct-v0.2 (prompted), plus Flan-T5-XL (fine-tuned). Retrieval uses BM25, GTR, Contriever, Dragon, and the Sentence Transformer 'all-mpnet-base-v2', with the best retriever selected per task/approach combination. Attributability (evidence quality without ground-truth) is evaluated using TRUE, AttrScore, and Minicheck, with Minicheck selected for QASPER and TRUE for Natural Questions and GovReport based on accuracy/balanced-accuracy comparison against 200 human-annotated responses (Cohen's kappa 0.74-0.77).</t>
         </is>
       </c>
       <c r="F204" s="5" t="n"/>
@@ -9477,7 +9465,7 @@
       <c r="H204" s="5" t="n"/>
       <c r="I204" s="5" t="inlineStr">
         <is>
-          <t>454069505d79f8b20538c78591702ac4dae921df</t>
+          <t>arxiv:2407.07799</t>
         </is>
       </c>
     </row>
@@ -9487,7 +9475,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>Oblivion: Self-Adaptive Agentic Memory Control through Decay-Driven Activation</t>
+          <t>Attribute or Abstain: Large Language Models as Long Document Assistants</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
@@ -9502,7 +9490,7 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>Two existing long-horizon memory benchmarks: LongMemEval (static, retrieval-heavy multi-session QA over ~100K-token chat histories, with six task categories -- SS-A, SS-U, SS-P, Multi-Session Reasoning, Knowledge Update, Temporal Reasoning -- evaluated under both Oracle/clean and S/noisy conditions) and GoodAI-LTM (dynamic, interactive long-horizon benchmark with ~120K context, evaluated across four memory-span settings: Isolated, 2K, 32K, and 120K, with 11/10/11/11 scenarios respectively, scored via GPT-4o as LLM-as-a-judge).</t>
+          <t>LAB (a new benchmark of 6 diverse long document tasks with attribution): QASPER (science QA), Natural Questions (Wikipedia QA, filtered from the original), Evidence Inference (science classification), Wice (web fact-checking), ContractNLI (legal NLI), and GovReport (US government report summarization), spanning document lengths from ~1,339 to ~8,464 average words and varying response/evidence granularity (sentence or paragraph level).</t>
         </is>
       </c>
       <c r="F205" s="5" t="n"/>
@@ -9510,7 +9498,7 @@
       <c r="H205" s="5" t="n"/>
       <c r="I205" s="5" t="inlineStr">
         <is>
-          <t>454069505d79f8b20538c78591702ac4dae921df</t>
+          <t>arxiv:2407.07799</t>
         </is>
       </c>
     </row>
@@ -9520,7 +9508,7 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Oblivion: Self-Adaptive Agentic Memory Control through Decay-Driven Activation</t>
+          <t>Attribute or Abstain: Large Language Models as Long Document Assistants</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
@@ -9535,7 +9523,7 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>On LongMemEval, Oblivion outperforms both the direct baseline (LME-RFT) and the memory baseline (EverMemOS) across model backbones: with GPT-4.1-mini, Oblivion reaches 94.40% average accuracy (Oracle) and 90.60% (S/noisy), versus LME-RFT's 91.80%/89.00% and EverMemOS's inconsistent 83.80%/81.27%; with GPT-4o-mini, Oblivion achieves 85.00%/81.80% versus LME-RFT's 83.00%/78.60% and EverMemOS's 72.80%/65.47%. Oblivion's largest gains appear on cross-session Multi-Session (MS) reasoning tasks with GPT-4o-mini (79.70% vs. 69.92% for direct), consistent with the hypothesis that hierarchical episodic+semantic memory mitigates the 'needle-in-a-haystack' problem. On GoodAI-LTM, Oblivion consistently beats both FullCtx (direct) and BeyondPrompts (memory) baselines across all four backbones and all four memory-span settings (e.g., GPT-4.1-mini: Oblivion solves 9.20/8.41/6.79/6.70 scenarios at Isolated/2K/32K/120K vs. FullCtx's 8.11/6.29/6.05/6.42 and BeyondPrompts' 8.53/5.37/6.68/6.26). On computational efficiency, Oblivion reduces average token cost by 73% at the 120K setting and 67% at 32K relative to FullCtx, with only modest latency overhead (1.34x versus FullCtx) while operating significantly faster than the BeyondPrompts memory baseline (1.4x latency), demonstrating a favorable cost-performance tradeoff at scale.</t>
+          <t>Across five attribution approaches (post-hoc, retrieve-then-read, citation, reduced-post-hoc, reduced-citation) evaluated on all 5 models and 6 datasets (Table 3), citation/reduced-citation produces the best evidence quality on average and on most datasets for large and fine-tuned models (GPT-3.5, GPT-4, Flan-T5-XL), with the exception of GovReport and the small models Longchat/Mistral, where post-hoc extraction performs better -- attributed to small models lacking sufficient instruction-following capability for in-generation evidence extraction, and GovReport's high response-document overlap favoring post-hoc retrieval. Citation causes minimal response-quality degradation (never more than 0.5 points lower than post-hoc for GPT-3.5/GPT-4/Flan-T5-XL), contradicting the assumption that task decomposition would improve response quality. No 'Lost in the Middle' effect (accuracy dip for evidence in the middle of documents) was found for evidence retrieval position except on GovReport; instead, response quality was found to generally decrease as evidence appears later in the document (except GPT-4, which showed positive correlation on most tasks). Reducing input documents to 10 segments before generation did not show a general beneficial effect on performance, mostly showing mixed-to-negative correlation with input length, consistent with prior negative findings (Xu et al. 2024; Bai et al. 2023). Evidence quality significantly predicted response quality at the system level for all datasets except GovReport, but this relationship held better for datasets with single-fact/simple responses (Natural Questions, ContractNLI, Evidence Inference) than for complex, multi-fact responses (QASPER, Wice), where manual analysis of the 50 lowest-attributability GPT-3.5-citation responses found the LLM's failure to extract sufficient evidence -- not incorrect responses -- was the primary cause of the discrepancy (46/50 cases for QASPER, 39/50 for Wice).</t>
         </is>
       </c>
       <c r="F206" s="5" t="n"/>
@@ -9543,7 +9531,7 @@
       <c r="H206" s="5" t="n"/>
       <c r="I206" s="5" t="inlineStr">
         <is>
-          <t>454069505d79f8b20538c78591702ac4dae921df</t>
+          <t>arxiv:2407.07799</t>
         </is>
       </c>
     </row>
@@ -9553,7 +9541,7 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>Oblivion: Self-Adaptive Agentic Memory Control through Decay-Driven Activation</t>
+          <t>Attribute or Abstain: Large Language Models as Long Document Assistants</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
@@ -9568,7 +9556,7 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>Two baseline categories per benchmark. For LongMemEval: LME-RFT (direct baseline using the optimized flat-retrieval pipeline with round-level storage, fact-augmented keys, and time-aware query expansion, without Chain-of-Note reasoning) and EverMemOS (memory baseline that indexes long-horizon interaction traces into a persistent store with memory-guided retrieval). For GoodAI-LTM: FullCtx (direct baseline, a standard full-context agent answering solely from its context window, truncated if needed) and BeyondPrompts (memory baseline, a MemGPT-inspired architecture with flat retrieval and a memory buffer but without decay or hierarchical memory organization).</t>
+          <t>Five attribution approach variants compared against each other: (1) post-hoc (generate response, then retrieve evidence), (2) retrieve-then-read (retrieve evidence first, then generate response), (3) citation (generate response and evidence/citations jointly in one step), (4) reduced-post-hoc, and (5) reduced-citation (both applying an input-document reduction to 10 segments before generation), tested across all 5 models and 6 LAB datasets.</t>
         </is>
       </c>
       <c r="F207" s="5" t="n"/>
@@ -9576,7 +9564,7 @@
       <c r="H207" s="5" t="n"/>
       <c r="I207" s="5" t="inlineStr">
         <is>
-          <t>454069505d79f8b20538c78591702ac4dae921df</t>
+          <t>arxiv:2407.07799</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9574,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Oblivion: Self-Adaptive Agentic Memory Control through Decay-Driven Activation</t>
+          <t>Attribute or Abstain: Large Language Models as Long Document Assistants</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
@@ -9601,7 +9589,7 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>N/A - non-adversarial. This is a memory-architecture/systems paper for long-horizon LLM agents, not a security paper. The incidental failure mode of interest is the 'needle-in-a-haystack' problem and prompt pollution/reasoning interference caused by 'always-on' flat memory retrieval: as memory stores accumulate stale or tangential entries over long interactions, relevant evidence becomes obscured, and existing systems either retrieve indiscriminately at every turn (uncertainty-decoupled retrieval) or resort to hard deletion to manage context limits (destroying potentially reactivatable information), both of which degrade response quality and efficiency in long-horizon settings.</t>
+          <t>N/A - non-adversarial (this is an attribution/evaluation-methodology paper for long document LLM assistants, not a security paper). The incidental phenomena of interest are LLM hallucination (motivating the need for attribution/abstention) and positional effects on evidence retrieval and response quality as a function of where evidence appears within a long document, explicitly including a targeted test for the 'Lost in the Middle' effect in the attribution setting (which the paper does not find, though it does find a distinct negative correlation between evidence position and response quality in some cases).</t>
         </is>
       </c>
       <c r="F208" s="5" t="n"/>
@@ -9609,7 +9597,7 @@
       <c r="H208" s="5" t="n"/>
       <c r="I208" s="5" t="inlineStr">
         <is>
-          <t>454069505d79f8b20538c78591702ac4dae921df</t>
+          <t>arxiv:2407.07799</t>
         </is>
       </c>
     </row>
@@ -9619,7 +9607,7 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>Oblivion: Self-Adaptive Agentic Memory Control through Decay-Driven Activation</t>
+          <t>Attribute or Abstain: Large Language Models as Long Document Assistants</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
@@ -9634,7 +9622,7 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>The paper has an explicit 'Limitations' section (unnumbered, following Section 7 Conclusions). Four points are stated. First, the framework uses the same LLM for memory extraction, uncertainty estimation, and response generation; a smaller/weaker LLM in this shared role might produce lower-quality outputs that degrade retrieval-dependent tasks, and decoupling the extraction and generation LLMs may alleviate this coupling issue. Second, model selection spans only two proprietary closed-weight models (GPT-4o-mini, GPT-4.1-mini) and two open-weight models (Phi-4-mini-Instruct-4B, Qwen3-30B-A3B-Instruct); evaluation on a broader range of model families and scales would strengthen generalizability claims. Third, the decay temperature T requires task-specific tuning, since the paper's own analysis shows distinct retention-reinforcement trade-offs across T values, with suboptimal choices leading to either excessive forgetting or buffer saturation. Fourth, due to cost constraints, evaluation relies on only two commercially available, licensed benchmarks (LongMemEval and GoodAI-LTM) covering static and dynamic paradigms; evaluation on multilingual, multimodal, domain-specific, or open-ended agentic settings remains unexplored.</t>
+          <t>Explicit 'Limitations' section (Section 7) covering three points: (1) LLMs were not used for retrieval (only for citation-based joint generation) for efficiency reasons, instead using a rigorously selected set of state-of-the-art retrievers (BM25, GTR, Contriever, Dragon, Sentence Transformer), and the authors argue the trade-off of added computational cost for potentially using LLMs as retrievers in post-hoc/retrieve-then-read was not favorable given that citation (where the LLM does perform retrieval implicitly) already showed the best results; (2) attributability evaluation models, while achieving good accuracy in model-selection experiments, were shown in further analysis to not yet handle edge cases well (e.g., failing to recognize 'partially supported' claims), flagged as a promising direction for future work; (3) the LAB benchmark, despite spanning diverse tasks/domains/response and document lengths, could not cover all possible variations, and few existing long document datasets contain the annotated evidence required for positional bias analysis, forcing reliance on GovReport as the only summarization dataset with annotated evidence -- extending the analysis to more datasets, with and without annotated evidence, is noted as an interesting future direction, especially since only limited positional biases were found in this study. A separate 'Potential Risks' section additionally states the datasets used are low-risk (created for NLP research, containing no personal/harmful/sensitive data, released under permissive licenses) and that no human annotators beyond the authors were employed.</t>
         </is>
       </c>
       <c r="F209" s="5" t="n"/>
@@ -9642,7 +9630,7 @@
       <c r="H209" s="5" t="n"/>
       <c r="I209" s="5" t="inlineStr">
         <is>
-          <t>454069505d79f8b20538c78591702ac4dae921df</t>
+          <t>arxiv:2407.07799</t>
         </is>
       </c>
     </row>
@@ -9652,7 +9640,7 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Oblivion: Self-Adaptive Agentic Memory Control through Decay-Driven Activation</t>
+          <t>Attribute or Abstain: Large Language Models as Long Document Assistants</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
@@ -9667,7 +9655,7 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>Oblivion is a memory control framework for long-horizon LLM agents that reframes forgetting as decay-driven reduction in memory accessibility rather than explicit deletion, inspired by cognitive-psychology models (Ebbinghaus forgetting curve) where memory traces fade unless reinforced but remain reactivatable rather than permanently erased. The framework decouples memory control into two independent paths orchestrated by a central Executor. The read path decides when to consult memory: a Decayer gates retrieval based on agent uncertainty and applies an Ebbinghaus-inspired retention score to filter which memory traces are currently accessible, and an Activator triggers targeted retrieval via a query-expansion graph only when uncertainty is high, avoiding redundant 'always-on' access at every turn. The write path decides what to strengthen: a Recognizer identifies which retrieved or generated memories actually contributed to producing the response, and a Memory Manager selectively reinforces only those response-contributing memories, increasing their future accessibility without touching unused ones. Memory is organized hierarchically into a bounded transient Working Memory (comprising a sliding interaction-context window, a permanently-resident memory buffer of L1 cluster nodes for routing, and task metadata) backed by a Persistent Store spanning three cognitively-grounded memory types: Dynamic Procedural Memory (L1, an adaptive meta-index/taxonomy over memory clusters with compressed summaries, utility statistics, and learned meta-instructions), Semantic Memory (L2), and Preemptive Episodic Memory (L3). This decay-driven, hierarchical, read/write-decoupled control loop lets the agent maintain persistent high-level strategies while dynamically loading fine-grained details only as needed, balancing learning and forgetting under shifting long-horizon interaction contexts.</t>
+          <t>This paper addresses a gap in attribution research: prior work on LLM attribution (providing evidence that supports a generated response, to combat hallucination and increase trust/verifiability) has only been studied in retrieval-augmented generation (RAG) settings, where a confounding initial retrieval step from a large external corpus is required; the fundamentally different single-long-document setting, where the entire potential evidence source already fits in the LLM's context window and no external retrieval is strictly necessary, has not been systematically evaluated. The authors introduce LAB (Long document Attribution Benchmark), spanning 6 diverse tasks/domains (QASPER, Natural Questions, Evidence Inference, Wice, ContractNLI, GovReport) with annotated evidence, and systematically compare five architecturally distinct approaches to attribution: post-hoc evidence retrieval after response generation, retrieve-then-read (retrieval before generation), citation (joint response-and-evidence-citation generation in a single step), and reduced variants of post-hoc/citation that first shrink the input document to 10 relevant segments. These are evaluated across five LLMs spanning large prompted (GPT-3.5, GPT-4), small prompted (Longchat-7B, Mistral-7B), and fine-tuned (Flan-T5-XL) model classes, using evidence-quality metrics (Evidence F1 for fixed-vocabulary datasets, an automatic 'attributability' classifier selected via a human-annotation-validated model-selection process for free-form-response datasets) alongside standard response-quality metrics (exact match, classification F1, ROUGE-L). The central findings are that citation is the best-performing attribution strategy for large and fine-tuned models without meaningfully hurting response quality, that small prompted models instead benefit from post-hoc extraction due to weaker instruction-following for in-generation citation, that a targeted 'Lost in the Middle' style positional bias in evidence retrieval was not found (contrary to expectations from prior long-context literature), and that evidence quality reliably predicts response quality only for simple, single-fact response tasks, not for complex, multi-fact responses where LLMs specifically struggle to extract sufficient supporting evidence even when the underlying response is correct.</t>
         </is>
       </c>
       <c r="F210" s="5" t="n"/>
@@ -9675,7 +9663,7 @@
       <c r="H210" s="5" t="n"/>
       <c r="I210" s="5" t="inlineStr">
         <is>
-          <t>454069505d79f8b20538c78591702ac4dae921df</t>
+          <t>arxiv:2407.07799</t>
         </is>
       </c>
     </row>
@@ -9685,7 +9673,7 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>LPS-Bench: Benchmarking Safety Awareness of Computer-Use Agents in Long-Horizon Planning under Benign and Adversarial Scenarios</t>
+          <t>When Refusals Fail: Unstable Safety Mechanisms in Long-Context LLM Agents</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
@@ -9708,7 +9696,7 @@
       <c r="H211" s="5" t="n"/>
       <c r="I211" s="5" t="inlineStr">
         <is>
-          <t>31e1a7b22ce24c7d1aa5880295c7c2c46abd1ac7</t>
+          <t>febb0d38c39219f39d5325345882b5148a84b79e</t>
         </is>
       </c>
     </row>
@@ -9718,7 +9706,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>LPS-Bench: Benchmarking Safety Awareness of Computer-Use Agents in Long-Horizon Planning under Benign and Adversarial Scenarios</t>
+          <t>When Refusals Fail: Unstable Safety Mechanisms in Long-Context LLM Agents</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
@@ -9741,7 +9729,7 @@
       <c r="H212" s="5" t="n"/>
       <c r="I212" s="5" t="inlineStr">
         <is>
-          <t>31e1a7b22ce24c7d1aa5880295c7c2c46abd1ac7</t>
+          <t>febb0d38c39219f39d5325345882b5148a84b79e</t>
         </is>
       </c>
     </row>
@@ -9751,7 +9739,7 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>LPS-Bench: Benchmarking Safety Awareness of Computer-Use Agents in Long-Horizon Planning under Benign and Adversarial Scenarios</t>
+          <t>When Refusals Fail: Unstable Safety Mechanisms in Long-Context LLM Agents</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
@@ -9774,7 +9762,7 @@
       <c r="H213" s="5" t="n"/>
       <c r="I213" s="5" t="inlineStr">
         <is>
-          <t>31e1a7b22ce24c7d1aa5880295c7c2c46abd1ac7</t>
+          <t>febb0d38c39219f39d5325345882b5148a84b79e</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9772,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>LPS-Bench: Benchmarking Safety Awareness of Computer-Use Agents in Long-Horizon Planning under Benign and Adversarial Scenarios</t>
+          <t>When Refusals Fail: Unstable Safety Mechanisms in Long-Context LLM Agents</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
@@ -9799,7 +9787,7 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>neither</t>
+          <t>attack</t>
         </is>
       </c>
       <c r="F214" s="5" t="n"/>
@@ -9807,7 +9795,7 @@
       <c r="H214" s="5" t="n"/>
       <c r="I214" s="5" t="inlineStr">
         <is>
-          <t>31e1a7b22ce24c7d1aa5880295c7c2c46abd1ac7</t>
+          <t>febb0d38c39219f39d5325345882b5148a84b79e</t>
         </is>
       </c>
     </row>
@@ -9817,7 +9805,7 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>LPS-Bench: Benchmarking Safety Awareness of Computer-Use Agents in Long-Horizon Planning under Benign and Adversarial Scenarios</t>
+          <t>When Refusals Fail: Unstable Safety Mechanisms in Long-Context LLM Agents</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
@@ -9832,7 +9820,7 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F215" s="5" t="n"/>
@@ -9840,7 +9828,7 @@
       <c r="H215" s="5" t="n"/>
       <c r="I215" s="5" t="inlineStr">
         <is>
-          <t>31e1a7b22ce24c7d1aa5880295c7c2c46abd1ac7</t>
+          <t>febb0d38c39219f39d5325345882b5148a84b79e</t>
         </is>
       </c>
     </row>
@@ -9850,7 +9838,7 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>LPS-Bench: Benchmarking Safety Awareness of Computer-Use Agents in Long-Horizon Planning under Benign and Adversarial Scenarios</t>
+          <t>When Refusals Fail: Unstable Safety Mechanisms in Long-Context LLM Agents</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
@@ -9865,7 +9853,7 @@
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>reasoning-corruption</t>
         </is>
       </c>
       <c r="F216" s="5" t="n"/>
@@ -9873,7 +9861,7 @@
       <c r="H216" s="5" t="n"/>
       <c r="I216" s="5" t="inlineStr">
         <is>
-          <t>31e1a7b22ce24c7d1aa5880295c7c2c46abd1ac7</t>
+          <t>febb0d38c39219f39d5325345882b5148a84b79e</t>
         </is>
       </c>
     </row>
@@ -9883,7 +9871,7 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>LPS-Bench: Benchmarking Safety Awareness of Computer-Use Agents in Long-Horizon Planning under Benign and Adversarial Scenarios</t>
+          <t>When Refusals Fail: Unstable Safety Mechanisms in Long-Context LLM Agents</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
@@ -9898,7 +9886,7 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F217" s="5" t="n"/>
@@ -9906,7 +9894,7 @@
       <c r="H217" s="5" t="n"/>
       <c r="I217" s="5" t="inlineStr">
         <is>
-          <t>31e1a7b22ce24c7d1aa5880295c7c2c46abd1ac7</t>
+          <t>febb0d38c39219f39d5325345882b5148a84b79e</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9904,7 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>LPS-Bench: Benchmarking Safety Awareness of Computer-Use Agents in Long-Horizon Planning under Benign and Adversarial Scenarios</t>
+          <t>When Refusals Fail: Unstable Safety Mechanisms in Long-Context LLM Agents</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
@@ -9931,7 +9919,7 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F218" s="5" t="n"/>
@@ -9939,7 +9927,7 @@
       <c r="H218" s="5" t="n"/>
       <c r="I218" s="5" t="inlineStr">
         <is>
-          <t>31e1a7b22ce24c7d1aa5880295c7c2c46abd1ac7</t>
+          <t>febb0d38c39219f39d5325345882b5148a84b79e</t>
         </is>
       </c>
     </row>
@@ -9949,7 +9937,7 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>LPS-Bench: Benchmarking Safety Awareness of Computer-Use Agents in Long-Horizon Planning under Benign and Adversarial Scenarios</t>
+          <t>When Refusals Fail: Unstable Safety Mechanisms in Long-Context LLM Agents</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
@@ -9964,7 +9952,7 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>reasoning</t>
         </is>
       </c>
       <c r="F219" s="5" t="n"/>
@@ -9972,7 +9960,7 @@
       <c r="H219" s="5" t="n"/>
       <c r="I219" s="5" t="inlineStr">
         <is>
-          <t>31e1a7b22ce24c7d1aa5880295c7c2c46abd1ac7</t>
+          <t>febb0d38c39219f39d5325345882b5148a84b79e</t>
         </is>
       </c>
     </row>
@@ -9982,7 +9970,7 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>LPS-Bench: Benchmarking Safety Awareness of Computer-Use Agents in Long-Horizon Planning under Benign and Adversarial Scenarios</t>
+          <t>When Refusals Fail: Unstable Safety Mechanisms in Long-Context LLM Agents</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
@@ -10005,7 +9993,7 @@
       <c r="H220" s="5" t="n"/>
       <c r="I220" s="5" t="inlineStr">
         <is>
-          <t>31e1a7b22ce24c7d1aa5880295c7c2c46abd1ac7</t>
+          <t>febb0d38c39219f39d5325345882b5148a84b79e</t>
         </is>
       </c>
     </row>
@@ -10015,7 +10003,7 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>LPS-Bench: Benchmarking Safety Awareness of Computer-Use Agents in Long-Horizon Planning under Benign and Adversarial Scenarios</t>
+          <t>When Refusals Fail: Unstable Safety Mechanisms in Long-Context LLM Agents</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
@@ -10038,7 +10026,7 @@
       <c r="H221" s="5" t="n"/>
       <c r="I221" s="5" t="inlineStr">
         <is>
-          <t>31e1a7b22ce24c7d1aa5880295c7c2c46abd1ac7</t>
+          <t>febb0d38c39219f39d5325345882b5148a84b79e</t>
         </is>
       </c>
     </row>
@@ -10048,7 +10036,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>LPS-Bench: Benchmarking Safety Awareness of Computer-Use Agents in Long-Horizon Planning under Benign and Adversarial Scenarios</t>
+          <t>When Refusals Fail: Unstable Safety Mechanisms in Long-Context LLM Agents</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
@@ -10063,7 +10051,7 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>The authors state 'We open-source our code at https://github.com/tychenn/LPS-Bench' in the abstract.</t>
+          <t>No public code/dataset release URL is stated in the extracted text. The paper extends the existing AgentHarm benchmark (Andriushchenko et al. 2025) with a controlled context-padding evaluation harness (four padding types, two padding positions, padding lengths from 1K to 200K+ tokens) but does not indicate this extension is separately released as an open artifact.</t>
         </is>
       </c>
       <c r="F222" s="5" t="n"/>
@@ -10071,7 +10059,7 @@
       <c r="H222" s="5" t="n"/>
       <c r="I222" s="5" t="inlineStr">
         <is>
-          <t>31e1a7b22ce24c7d1aa5880295c7c2c46abd1ac7</t>
+          <t>febb0d38c39219f39d5325345882b5148a84b79e</t>
         </is>
       </c>
     </row>
@@ -10081,7 +10069,7 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>LPS-Bench: Benchmarking Safety Awareness of Computer-Use Agents in Long-Horizon Planning under Benign and Adversarial Scenarios</t>
+          <t>When Refusals Fail: Unstable Safety Mechanisms in Long-Context LLM Agents</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
@@ -10096,7 +10084,7 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>13 LLM agents are evaluated: proprietary models GPT-5, GPT-5.1, Gemini-2.5-Pro, Gemini-3-Pro, Claude-3.5-Sonnet, Claude-4-Sonnet, Claude-4.5-Sonnet, DeepSeek-V3.1, and DeepSeek-V3.2, plus open-weight models Qwen3-8B-Instruct and Qwen3-32B-Instruct (and additional models implied by the '13 tested' count, likely including a Llama variant referenced in the model listing). DeepSeek-R1 is used as the LLM-as-a-judge evaluator model.</t>
+          <t>Four models from different families and with different declared context windows: GPT-4.1-nano (1M tokens declared), GPT-5 (400K tokens declared), DeepSeek-V3.1 (128K tokens declared), and Grok 4 Fast (2M tokens declared). Models were accessed via different API providers (OpenAI API for GPT-4.1-nano, OpenRouter for the rest), which the authors note may introduce provider-level safety filters not fully disentangled from base-model behavior.</t>
         </is>
       </c>
       <c r="F223" s="5" t="n"/>
@@ -10104,7 +10092,7 @@
       <c r="H223" s="5" t="n"/>
       <c r="I223" s="5" t="inlineStr">
         <is>
-          <t>31e1a7b22ce24c7d1aa5880295c7c2c46abd1ac7</t>
+          <t>febb0d38c39219f39d5325345882b5148a84b79e</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10102,7 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>LPS-Bench: Benchmarking Safety Awareness of Computer-Use Agents in Long-Horizon Planning under Benign and Adversarial Scenarios</t>
+          <t>When Refusals Fail: Unstable Safety Mechanisms in Long-Context LLM Agents</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
@@ -10129,7 +10117,7 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>The paper introduces LPS-Bench, a novel benchmark evaluating planning-time safety awareness of MCP (Model Context Protocol)-based computer-use agents (CUAs) under long-horizon tasks, covering 65 scenarios across 7 CUA task domains (each with approximately 10 representative scenarios) and 9 risk types organized into benign user-induced risks (four categories: TS, OC, FA, IP, e.g. task ambiguity, over-completion, false-assumption, incomplete-preference) and adversarial-manipulation risks. Cases are generated via a multi-agent automated data-generation pipeline that expands high-level scenario templates into executable, tool-simulated test cases, each supported by a flexible tool-simulation interface enabling controlled side effects and undergoing expert review for curation.</t>
+          <t>AgentHarm public test dataset (176 samples from 44 unique tasks across 8 harm categories including disinformation and fraud), extended with a controlled context-padding evaluation setup. The simplest task subset (hint + detailed step-by-step instructions, solvable by all models without padding) was used to isolate context-length effects from raw capability limitations. Four padding types were tested: random tokens (sampled from the tokenizer), non-relevant coherent text (fiction literature across 5 genres: humor, mythology, sci-fi, crime, romance), relevant coherent text (Wikipedia articles related to the task category), and multi-task padding (task descriptions sampled from the validation dataset). Padding was inserted at two positions relative to the task description: before (simulating context filled with past interaction history) and after (simulating a user adding information after the initial task).</t>
         </is>
       </c>
       <c r="F224" s="5" t="n"/>
@@ -10137,7 +10125,7 @@
       <c r="H224" s="5" t="n"/>
       <c r="I224" s="5" t="inlineStr">
         <is>
-          <t>31e1a7b22ce24c7d1aa5880295c7c2c46abd1ac7</t>
+          <t>febb0d38c39219f39d5325345882b5148a84b79e</t>
         </is>
       </c>
     </row>
@@ -10147,7 +10135,7 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>LPS-Bench: Benchmarking Safety Awareness of Computer-Use Agents in Long-Horizon Planning under Benign and Adversarial Scenarios</t>
+          <t>When Refusals Fail: Unstable Safety Mechanisms in Long-Context LLM Agents</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
@@ -10162,7 +10150,7 @@
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>Current LLM-based CUAs show substantial deficiencies maintaining safe behavior on long-horizon MCP-style workflows (Figure 1/Table 3). Safe Rate varies dramatically by model: the strongest model, Claude-4.5-Sonnet, achieves the highest overall safety scores (e.g., 95.77% average Safe Rate in Table 3, 88.14% in the domain breakdown of Table 4) while weaker models like DeepSeek-V3.1 (4.55%), DeepSeek-V3.2 (5.82%), Qwen3-8B-Instruct (3.72%), and Qwen3-32B-Instruct (3.65%) perform near-catastrophically poorly. Even strong models struggle severely on specific risk categories -- for example, on one benign risk subtype, even Claude-4.5-Sonnet reaches only 5.88% Safe Rate, and GPT-5.1 only 26.47%, indicating a specific systemic weakness. In adversarial user-driven scenarios, planning robustness improves substantially for the strongest models (e.g., Claude-4.5-Sonnet: 94.03%, GPT-5.1: 98.51%) but weaker models remain highly vulnerable (e.g., DeepSeek-v3.2 near 0% on some adversarial subcategories). Within model families, larger/more capable variants consistently achieve higher Safe Rate, suggesting improved general planning capability confers some safety benefit, though safety-weaker models like Gemini-2.5-Pro and DeepSeek-V3.2 fail to internalize adversarial threat patterns even with reasonable general capability, and threat-pattern exposure yields only marginal safety gains for the weakest models (e.g., Qwen3-8B-Instruct). Domain-level analysis (Table 4) shows substantial variance in safety performance across the seven CUA domains (e.g., the File domain shows most models struggling except Claude-4.5-Sonnet), correlated with whether a model has likely been exposed to domain-specific high-impact artifacts (file writes, deletions, moves) during training/alignment.</t>
+          <t>Agentic capability degrades severely well before models' declared maximum context length: Grok 4 Fast (2M-token declared window) shows strong degradation after 50K tokens on both benign and harmful tasks, dropping to zero performance at 200K tokens, with a sharp transition between 50K-100K tokens resembling mode collapse where different padding types converge to the same score. GPT-4.1-nano (1M-token declared window) shows gradual degradation on both task types, with harmful-task performance cut roughly threefold and benign-task performance cut in half (80% to 40%) by 200K tokens, continuing to degrade even at 800K tokens (80% of its claimed capacity). DeepSeek-V3.1 (128K declared window) is comparatively more robust to random padding, losing only about 10 percentage points on benign tasks at 200K tokens, and even shows a slight performance increase on harmful tasks between 0-50K tokens (attributed to a temporary refusal-rate decrease) before refusal rate spikes and performance drops near the maximum context length. GPT-5 maintains a consistently very high refusal rate that does not decrease with increasing padding, limiting the ability to draw strong conclusions about its capability degradation on harmful tasks. Refusal rates shift unpredictably and in opposite directions across models: GPT-4.1-nano's refusal rate rises from about 5% (no padding) to about 40% at 200K tokens of random padding, while Grok 4 Fast's refusal rate falls from about 80% to about 10% over the same range -- opposite directions under identical experimental conditions. Padding type significantly affects performance for GPT-4.1-nano, with scores ranking non-relevant coherent text &gt; relevant coherent text &gt; random &gt; multi-task (worst); Grok 4 Fast does not show a clear padding-type pattern due to its already-high refusal rate, oscillating near the no-padding baseline. Padding position matters: for both GPT-4.1-nano and Grok 4 Fast, placing padding before the task description slows capability degradation compared to placing it after, attributed to attention mechanisms (sliding window, RoPE) handling smaller instruction-execution gaps more in-distribution than very long-range attention spans. A supplementary analysis found a small percentage of refusals are 'delayed' (occurring after the model has already begun task execution, e.g., information gathering or API calls) rather than immediate, which the authors flag as a distinct and more concerning failure mode than upfront refusal since partial harmful execution may have already occurred.</t>
         </is>
       </c>
       <c r="F225" s="5" t="n"/>
@@ -10170,7 +10158,7 @@
       <c r="H225" s="5" t="n"/>
       <c r="I225" s="5" t="inlineStr">
         <is>
-          <t>31e1a7b22ce24c7d1aa5880295c7c2c46abd1ac7</t>
+          <t>febb0d38c39219f39d5325345882b5148a84b79e</t>
         </is>
       </c>
     </row>
@@ -10180,7 +10168,7 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>LPS-Bench: Benchmarking Safety Awareness of Computer-Use Agents in Long-Horizon Planning under Benign and Adversarial Scenarios</t>
+          <t>When Refusals Fail: Unstable Safety Mechanisms in Long-Context LLM Agents</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
@@ -10195,7 +10183,7 @@
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>The paper's primary comparison is a within-benchmark evaluation across the 13 tested LLM agents under LPS-Bench's benign and adversarial scenario conditions; a separate comparison table (Table 1) positions LPS-Bench itself against prior agent safety benchmarks (both CUA-specific and general) along dimensions including interaction modality (GUI vs. MCP) and task horizon (short vs. long), rather than evaluating alternative defense systems.</t>
+          <t>The paper does not compare against alternative defense mechanisms or prior long-context safety methods; instead it uses the unmodified, no-padding AgentHarm condition (0 tokens of padding) as the reference baseline against which all padded conditions (varying length, type, and position) are compared for each of the four evaluated models, effectively treating each model's own no-padding performance as its own baseline.</t>
         </is>
       </c>
       <c r="F226" s="5" t="n"/>
@@ -10203,7 +10191,7 @@
       <c r="H226" s="5" t="n"/>
       <c r="I226" s="5" t="inlineStr">
         <is>
-          <t>31e1a7b22ce24c7d1aa5880295c7c2c46abd1ac7</t>
+          <t>febb0d38c39219f39d5325345882b5148a84b79e</t>
         </is>
       </c>
     </row>
@@ -10213,7 +10201,7 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>LPS-Bench: Benchmarking Safety Awareness of Computer-Use Agents in Long-Horizon Planning under Benign and Adversarial Scenarios</t>
+          <t>When Refusals Fail: Unstable Safety Mechanisms in Long-Context LLM Agents</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
@@ -10228,7 +10216,7 @@
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>Formal dual threat model spanning both benign and adversarial settings: for benign users, ambiguous or underspecified instructions (e.g., 'clean up my workspace') combined with the model's tendency to infer missing details can cause action-capable agents to execute unintended harmful actions (e.g., deleting important files) even absent any attacker; for adversarial users, action-enabled agents present a new attack surface where an adversary can manipulate tool selection toward risky operations or compose individually benign tool calls into a harmful sequence, hijacking the agent to exfiltrate data or execute malicious commands. The threat model is specifically scoped to MCP-based CUAs, where atomic, structured tool invocations produce immediate but irreversible side effects (unlike GUI-based CUAs, which allow mid-course correction via incremental, visually observable interactions), making planning-time (anticipatory) safety awareness -- rather than only execution-time error correction -- essential.</t>
+          <t>The threat model centers on AgentHarm's existing harmful-task taxonomy (8 categories including disinformation and fraud, e.g., a task instructing an agent to generate a fabricated video of two named politicians and post it as real on social media), where the 'attacker' is effectively a user issuing an explicitly harmful multi-step agentic task; the paper's contribution is not a new attack but an evaluation of how the model's refusal behavior and task-execution safety degrade as a function of injected context padding (length, semantic type/relevance, and position relative to the task). Two related but distinct failure modes are identified as safety-relevant: refusal-rate volatility (whether models refuse a harmful request at all, which shifts unpredictably and non-monotonically with context length and can move in opposite directions across models) and refusal timing (whether refusal occurs immediately upon reading the harmful task description, versus only after the model has already begun executing tool calls or gathering information for the harmful task -- a 'delayed refusal' pattern the authors identify as concerning because partial harm may already have occurred by the time refusal triggers).</t>
         </is>
       </c>
       <c r="F227" s="5" t="n"/>
@@ -10236,7 +10224,7 @@
       <c r="H227" s="5" t="n"/>
       <c r="I227" s="5" t="inlineStr">
         <is>
-          <t>31e1a7b22ce24c7d1aa5880295c7c2c46abd1ac7</t>
+          <t>febb0d38c39219f39d5325345882b5148a84b79e</t>
         </is>
       </c>
     </row>
@@ -10246,7 +10234,7 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>LPS-Bench: Benchmarking Safety Awareness of Computer-Use Agents in Long-Horizon Planning under Benign and Adversarial Scenarios</t>
+          <t>When Refusals Fail: Unstable Safety Mechanisms in Long-Context LLM Agents</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
@@ -10261,7 +10249,7 @@
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>The paper has an explicit 'Limitations' section (following the Conclusion, before 'Ethical Considerations'), stating two limitations: (1) although the benchmark targets long-horizon planning safety in MCP-style tool-use workflows, it cannot exhaustively cover all real-world domains, tools, and edge cases, and some scenario distributions may differ from actual deployment settings; (2) evaluation is automated for scalability and consistency, and while most cases have been validated by human experts, an exceptionally small subset of borderline trajectories can still be difficult to adjudicate perfectly, leaving room for further calibration and refinement. A separate 'Ethical Considerations' section additionally discusses dual-use risk given that the benchmark contains adversarial, high-risk instructions and an automated red-team-case-generation pipeline.</t>
+          <t>The paper includes an explicit inline limitations discussion (in Section 5, Discussion, not a separately titled 'Limitations' section) stating: due to budget constraints, only a limited set of four models was evaluated; the study used the easiest AgentHarm subset (tasks with both hints and detailed step-by-step instructions), which bypasses planning ability and means the reported results represent an upper bound on model performance rather than typical or worst-case performance; and models were accessed via different API providers (OpenAI API for GPT-4.1-nano, OpenRouter for the others), which may introduce provider-level safety filters that cannot be fully disentangled from base-model behavior, potentially confounding the cross-model refusal-rate comparisons. The Discussion additionally raises a methodological concern rather than a strict limitation: that refusal rate alone may be an unreliable safety metric, since the paper's own results show refusal rate increases in some models (e.g., GPT-4.1-nano) that could plausibly be triggered by something other than genuine safety training (e.g., general confusion or distributional shift from long padding) rather than correct harm recognition, questioning the field's reliance on refusal rate as a primary safety metric without a mechanism to identify what actually triggers a given refusal.</t>
         </is>
       </c>
       <c r="F228" s="5" t="n"/>
@@ -10269,7 +10257,7 @@
       <c r="H228" s="5" t="n"/>
       <c r="I228" s="5" t="inlineStr">
         <is>
-          <t>31e1a7b22ce24c7d1aa5880295c7c2c46abd1ac7</t>
+          <t>febb0d38c39219f39d5325345882b5148a84b79e</t>
         </is>
       </c>
     </row>
@@ -10279,7 +10267,7 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>LPS-Bench: Benchmarking Safety Awareness of Computer-Use Agents in Long-Horizon Planning under Benign and Adversarial Scenarios</t>
+          <t>When Refusals Fail: Unstable Safety Mechanisms in Long-Context LLM Agents</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
@@ -10294,7 +10282,7 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>This paper presents LPS-Bench, a benchmark for evaluating the planning-time safety awareness of MCP (Model Context Protocol)-based computer-use agents (CUAs) under long-horizon tasks, addressing a gap in prior CUA safety benchmarks, which mostly focus on short-horizon or GUI-based tasks and evaluate execution-time errors while overlooking agents' ability to anticipate planning-time risks before taking irreversible actions. The benchmark is motivated by the observation that MCP-based CUAs invoke system tools directly through structured protocol interfaces where tool calls are atomic and can produce immediate but irreversible side effects, substantially amplifying the importance of anticipatory safety reasoning compared to GUI-based agents that allow incremental, correctable interactions. LPS-Bench features five key design elements: (1) MCP-based safety-aware planning evaluation targeting structured tool-connection frameworks; (2) dual-view scenarios covering both benign assistance (testing whether an agent correctly infers ambiguous user intent without incurring unnecessary safety, time, or financial costs) and adversarial manipulation (testing whether an agent recognizes and rejects maliciously steered plans); (3) long-horizon workflows requiring extended planning and repeated replanning across lengthy, state-changing tool interactions; (4) broad coverage spanning 7 CUA domains with roughly 10 scenarios each; and (5) curated, evaluable cases supported by a flexible tool-simulation interface enabling controlled side effects and fully automated evaluation. Test cases are constructed via a multi-agent automated data-generation pipeline that expands high-level scenario templates into executable, tool-simulated cases with case-specific evaluation criteria (e.g., programmatic checker functions like 'is_false_assumption()'), and evaluation uses an LLM-as-a-judge protocol (DeepSeek-R1) that assesses not merely whether the agent's final outcome is safe, but whether the entire generated plan and action trajectory avoided unsafe or risk-amplifying intermediate steps throughout the planning process.</t>
+          <t>This paper investigates how safety alignment (measured via refusal behavior) and task capability of LLM-based agents scale with context length, addressing a gap in prior work that has focused on long-context accuracy/efficiency ('lost in the middle') or on short-prompt agent safety benchmarks (e.g., AgentHarm) separately, but not on how these two dimensions interact when an agent operates with long, padded context. The authors extend the AgentHarm benchmark (176 samples, 44 tasks, 8 harm categories, with manually implemented simulated tools such as Google Search or an X/Twitter posting API) with a controlled context-padding evaluation harness that inserts padding tokens of varying length (1K to 200K, and up to 800K for one model), type (random tokenizer-sampled tokens; non-relevant coherent fiction text spanning five genres; relevant coherent Wikipedia text matched to the task category; or multi-task padding using other validation-set task descriptions), and position (before the task description, simulating accumulated interaction history, versus after, simulating user-added context) relative to the task prompt, restricting evaluation to the simplest task subset (hints plus detailed instructions) to isolate context-length effects from raw capability limitations and establish an upper bound on performance. Scoring combines a rubric-based Harm Score (checking whether all target harmful tools were invoked in the correct order) with an LLM-judge-based binary refusal rate, evaluated across four models spanning different context-window claims and providers: GPT-4.1-nano (1M declared), GPT-5 (400K declared), DeepSeek-V3.1 (128K declared), and Grok 4 Fast (2M declared). The central finding is that agentic capability degrades sharply well before a model's declared maximum context length -- performance drops exceeding 50% for both benign and harmful tasks appear already around 100K tokens even for models claiming multi-million-token windows, suggesting a mismatch between advertised and effectively usable context capacity, possibly because training data distributions concentrate on shorter sequences, making very long agentic tasks effectively out-of-distribution. Critically, the paper shows refusal-rate behavior under increasing context is neither stable nor consistent across models: GPT-4.1-nano's refusal rate rises substantially with padding (from about 5% to about 40% at 200K tokens) while Grok 4 Fast's refusal rate falls dramatically over the same range (from about 80% to about 10%), demonstrating that increased context can push different models' safety mechanisms in opposite directions under identical experimental manipulation, that padding semantic type (coherent versus random versus multi-task-confounding text) and position (before versus after the task) further modulate both capability and refusal behavior in model-specific ways, and that a nontrivial fraction of refusals occur only after an agent has already begun executing part of a harmful task rather than immediately upon reading it. Collectively, these results indicate that longer context windows do not straightforwardly improve or preserve either agentic reliability or safety alignment, and that refusal rate alone -- the field's dominant static safety metric -- may be an unreliable and non-generalizable proxy for agent safety once long, padded, multi-step agentic contexts are considered, motivating calls for more holistic, context-aware agent safety evaluation methodologies.</t>
         </is>
       </c>
       <c r="F229" s="5" t="n"/>
@@ -10302,7 +10290,7 @@
       <c r="H229" s="5" t="n"/>
       <c r="I229" s="5" t="inlineStr">
         <is>
-          <t>31e1a7b22ce24c7d1aa5880295c7c2c46abd1ac7</t>
+          <t>febb0d38c39219f39d5325345882b5148a84b79e</t>
         </is>
       </c>
     </row>
@@ -10312,7 +10300,7 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>WAB: Overcoming Memory, Network, and Security Walls in Native Agentic Browsers with WebAssembly</t>
+          <t>Knowledge Conflicts for LLMs: A Survey</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
@@ -10335,7 +10323,7 @@
       <c r="H230" s="5" t="n"/>
       <c r="I230" s="5" t="inlineStr">
         <is>
-          <t>74aec0665c948c64072682901b7e95e7b71286e4</t>
+          <t>ab8e6df5001dbb9b48445220099425aff536b3e8</t>
         </is>
       </c>
     </row>
@@ -10345,7 +10333,7 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>WAB: Overcoming Memory, Network, and Security Walls in Native Agentic Browsers with WebAssembly</t>
+          <t>Knowledge Conflicts for LLMs: A Survey</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
@@ -10360,7 +10348,7 @@
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>ML/AI</t>
         </is>
       </c>
       <c r="F231" s="5" t="n"/>
@@ -10368,7 +10356,7 @@
       <c r="H231" s="5" t="n"/>
       <c r="I231" s="5" t="inlineStr">
         <is>
-          <t>74aec0665c948c64072682901b7e95e7b71286e4</t>
+          <t>ab8e6df5001dbb9b48445220099425aff536b3e8</t>
         </is>
       </c>
     </row>
@@ -10378,7 +10366,7 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>WAB: Overcoming Memory, Network, and Security Walls in Native Agentic Browsers with WebAssembly</t>
+          <t>Knowledge Conflicts for LLMs: A Survey</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
@@ -10401,7 +10389,7 @@
       <c r="H232" s="5" t="n"/>
       <c r="I232" s="5" t="inlineStr">
         <is>
-          <t>74aec0665c948c64072682901b7e95e7b71286e4</t>
+          <t>ab8e6df5001dbb9b48445220099425aff536b3e8</t>
         </is>
       </c>
     </row>
@@ -10411,7 +10399,7 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>WAB: Overcoming Memory, Network, and Security Walls in Native Agentic Browsers with WebAssembly</t>
+          <t>Knowledge Conflicts for LLMs: A Survey</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
@@ -10426,7 +10414,7 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>defense</t>
+          <t>neither</t>
         </is>
       </c>
       <c r="F233" s="5" t="n"/>
@@ -10434,7 +10422,7 @@
       <c r="H233" s="5" t="n"/>
       <c r="I233" s="5" t="inlineStr">
         <is>
-          <t>74aec0665c948c64072682901b7e95e7b71286e4</t>
+          <t>ab8e6df5001dbb9b48445220099425aff536b3e8</t>
         </is>
       </c>
     </row>
@@ -10444,7 +10432,7 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>WAB: Overcoming Memory, Network, and Security Walls in Native Agentic Browsers with WebAssembly</t>
+          <t>Knowledge Conflicts for LLMs: A Survey</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
@@ -10459,7 +10447,7 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F234" s="5" t="n"/>
@@ -10467,7 +10455,7 @@
       <c r="H234" s="5" t="n"/>
       <c r="I234" s="5" t="inlineStr">
         <is>
-          <t>74aec0665c948c64072682901b7e95e7b71286e4</t>
+          <t>ab8e6df5001dbb9b48445220099425aff536b3e8</t>
         </is>
       </c>
     </row>
@@ -10477,7 +10465,7 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>WAB: Overcoming Memory, Network, and Security Walls in Native Agentic Browsers with WebAssembly</t>
+          <t>Knowledge Conflicts for LLMs: A Survey</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
@@ -10492,7 +10480,7 @@
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="F235" s="5" t="n"/>
@@ -10500,7 +10488,7 @@
       <c r="H235" s="5" t="n"/>
       <c r="I235" s="5" t="inlineStr">
         <is>
-          <t>74aec0665c948c64072682901b7e95e7b71286e4</t>
+          <t>ab8e6df5001dbb9b48445220099425aff536b3e8</t>
         </is>
       </c>
     </row>
@@ -10510,7 +10498,7 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>WAB: Overcoming Memory, Network, and Security Walls in Native Agentic Browsers with WebAssembly</t>
+          <t>Knowledge Conflicts for LLMs: A Survey</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
@@ -10533,7 +10521,7 @@
       <c r="H236" s="5" t="n"/>
       <c r="I236" s="5" t="inlineStr">
         <is>
-          <t>74aec0665c948c64072682901b7e95e7b71286e4</t>
+          <t>ab8e6df5001dbb9b48445220099425aff536b3e8</t>
         </is>
       </c>
     </row>
@@ -10543,7 +10531,7 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>WAB: Overcoming Memory, Network, and Security Walls in Native Agentic Browsers with WebAssembly</t>
+          <t>Knowledge Conflicts for LLMs: A Survey</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
@@ -10566,7 +10554,7 @@
       <c r="H237" s="5" t="n"/>
       <c r="I237" s="5" t="inlineStr">
         <is>
-          <t>74aec0665c948c64072682901b7e95e7b71286e4</t>
+          <t>ab8e6df5001dbb9b48445220099425aff536b3e8</t>
         </is>
       </c>
     </row>
@@ -10576,7 +10564,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>WAB: Overcoming Memory, Network, and Security Walls in Native Agentic Browsers with WebAssembly</t>
+          <t>Knowledge Conflicts for LLMs: A Survey</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -10591,7 +10579,7 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>execution</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F238" s="5" t="n"/>
@@ -10599,7 +10587,7 @@
       <c r="H238" s="5" t="n"/>
       <c r="I238" s="5" t="inlineStr">
         <is>
-          <t>74aec0665c948c64072682901b7e95e7b71286e4</t>
+          <t>ab8e6df5001dbb9b48445220099425aff536b3e8</t>
         </is>
       </c>
     </row>
@@ -10609,7 +10597,7 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>WAB: Overcoming Memory, Network, and Security Walls in Native Agentic Browsers with WebAssembly</t>
+          <t>Knowledge Conflicts for LLMs: A Survey</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
@@ -10632,7 +10620,7 @@
       <c r="H239" s="5" t="n"/>
       <c r="I239" s="5" t="inlineStr">
         <is>
-          <t>74aec0665c948c64072682901b7e95e7b71286e4</t>
+          <t>ab8e6df5001dbb9b48445220099425aff536b3e8</t>
         </is>
       </c>
     </row>
@@ -10642,7 +10630,7 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>WAB: Overcoming Memory, Network, and Security Walls in Native Agentic Browsers with WebAssembly</t>
+          <t>Knowledge Conflicts for LLMs: A Survey</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
@@ -10665,7 +10653,7 @@
       <c r="H240" s="5" t="n"/>
       <c r="I240" s="5" t="inlineStr">
         <is>
-          <t>74aec0665c948c64072682901b7e95e7b71286e4</t>
+          <t>ab8e6df5001dbb9b48445220099425aff536b3e8</t>
         </is>
       </c>
     </row>
@@ -10675,7 +10663,7 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>WAB: Overcoming Memory, Network, and Security Walls in Native Agentic Browsers with WebAssembly</t>
+          <t>Knowledge Conflicts for LLMs: A Survey</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
@@ -10688,13 +10676,17 @@
           <t>secondary</t>
         </is>
       </c>
-      <c r="E241" s="2" t="n"/>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F241" s="5" t="n"/>
       <c r="G241" s="5" t="n"/>
       <c r="H241" s="5" t="n"/>
       <c r="I241" s="5" t="inlineStr">
         <is>
-          <t>74aec0665c948c64072682901b7e95e7b71286e4</t>
+          <t>ab8e6df5001dbb9b48445220099425aff536b3e8</t>
         </is>
       </c>
     </row>
@@ -10704,7 +10696,7 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>WAB: Overcoming Memory, Network, and Security Walls in Native Agentic Browsers with WebAssembly</t>
+          <t>Knowledge Conflicts for LLMs: A Survey</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
@@ -10719,7 +10711,7 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>Not named; the design assumes cloud-hosted LLMs invoked from the browser, with the Wasm runtime handling context retrieval and action execution locally.</t>
+          <t>N/A - this is a survey paper synthesizing findings from prior empirical work rather than conducting its own model evaluation; models discussed across the surveyed literature include GPT-4, ChatGPT, PaLM-2, Llama 2, BERT, RoBERTa, ALBERT, ERNIE, XLM-RoBERTa, Alpaca-30B, and Fusion-in-Decoder, among others</t>
         </is>
       </c>
       <c r="F242" s="5" t="n"/>
@@ -10727,7 +10719,7 @@
       <c r="H242" s="5" t="n"/>
       <c r="I242" s="5" t="inlineStr">
         <is>
-          <t>74aec0665c948c64072682901b7e95e7b71286e4</t>
+          <t>ab8e6df5001dbb9b48445220099425aff536b3e8</t>
         </is>
       </c>
     </row>
@@ -10737,7 +10729,7 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>WAB: Overcoming Memory, Network, and Security Walls in Native Agentic Browsers with WebAssembly</t>
+          <t>Knowledge Conflicts for LLMs: A Survey</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
@@ -10752,7 +10744,7 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>No standard benchmark. A single representative WebQA workflow trace serves as the case study for the proof-of-concept implementation.</t>
+          <t>N/A - survey paper; catalogs and compares 10 existing knowledge-conflict evaluation datasets from the literature (Table 1), organized by conflict type: context-memory conflict datasets (Xie et al. 2023 built on PopQA/StrategyQA, KC, KRE, Farm, Tan et al. 2024 built on NQ/TriviaQA/BoolQ/TruthfulQA), inter-context conflict datasets (WikiContradiction, ClaimDiff, Pan et al. 2023a built on SQuAD, ContraDoc built on CNN-DailyMail/NarrativeQA/WikiText), and intra-memory conflict datasets (ConflictingQA, ParaRel built on T-REx)</t>
         </is>
       </c>
       <c r="F243" s="5" t="n"/>
@@ -10760,7 +10752,7 @@
       <c r="H243" s="5" t="n"/>
       <c r="I243" s="5" t="inlineStr">
         <is>
-          <t>74aec0665c948c64072682901b7e95e7b71286e4</t>
+          <t>ab8e6df5001dbb9b48445220099425aff536b3e8</t>
         </is>
       </c>
     </row>
@@ -10770,7 +10762,7 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>WAB: Overcoming Memory, Network, and Security Walls in Native Agentic Browsers with WebAssembly</t>
+          <t>Knowledge Conflicts for LLMs: A Survey</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
@@ -10785,7 +10777,7 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>Evaluation is a case study rather than a benchmark: a proof-of-concept implementation exercised on a representative WebQA workflow trace, presented to illustrate how a Wasm-centered runtime can mitigate the three walls in one coherent design. The analytic content compares context-retrieval query counts between the stepwise baseline and WAB's action bundles, since batching action steps per LLM call reduces both round trips and the number of retrieval queries issued - so the network and memory mechanisms interact rather than being independent optimizations. No attack success rate, defense effectiveness measurement, or end-to-end latency table is surfaced in the extracted material, so the security claim rests on the architectural property of the Authority mechanism (capabilities are allowlisted, explicitly granted and revocable, blocking unauthorized side effects by default) rather than on measured resistance to injection. For this corpus the transferable point is the placement: least-privilege enforcement at a Wasm sandbox boundary is checkable independently of what the model was persuaded to attempt, which is the same execution-stage argument that RQ6 found is rarely tested in practice.</t>
+          <t>Synthesizing the surveyed literature, the paper's main findings are organized around its three-part taxonomy: (1) for context-memory conflict, LLMs are found to be highly receptive to external evidence when it is semantically coherent, logical, and compelling, but exhibit a competing confirmation bias favoring information consistent with their parametric memory, with no definitive universal rule for which tendency dominates in a given scenario, and LLMs are shown to perform well at detecting that a conflict exists but struggle to pinpoint the specific conflicting segments or produce responses that clearly distinguish between conflicting pieces of information; (2) for inter-context conflict, misinformation and outdated information both degrade LLM performance, average detection accuracy for contradictions across evaluated models (BERT, RoBERTa, ERNIE, GPT-4, PaLM-2, Llama 2) is subpar, models struggle particularly with subjective/emotional or perspective-based contradictions, and models are shown to over-rely on superficial relevance/frequency of a document rather than substantive credibility signals (e.g. presence of scientific references, neutral tone) that humans would use to judge document trustworthiness, with reasoning difficulty increasing as the number of conflicting 'hops' grows; (3) for intra-memory conflict, LLMs (including GPT-4) exhibit substantial self-inconsistency - producing different answers to semantically equivalent but syntactically different prompts, or contradicting a prior correct answer when later asked to re-verify it (Alpaca-30B shows consistency in only 50% of such cases) - attributable to training-corpus bias (conflicting knowledge co-existing in pretraining data, plus a tendency to encode superficial rather than genuine associations), inherent randomness in stochastic decoding strategies, and side effects of post-hoc knowledge-editing techniques that can introduce new inconsistencies while attempting to fix others.</t>
         </is>
       </c>
       <c r="F244" s="5" t="n"/>
@@ -10793,7 +10785,7 @@
       <c r="H244" s="5" t="n"/>
       <c r="I244" s="5" t="inlineStr">
         <is>
-          <t>74aec0665c948c64072682901b7e95e7b71286e4</t>
+          <t>ab8e6df5001dbb9b48445220099425aff536b3e8</t>
         </is>
       </c>
     </row>
@@ -10803,7 +10795,7 @@
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>WAB: Overcoming Memory, Network, and Security Walls in Native Agentic Browsers with WebAssembly</t>
+          <t>Knowledge Conflicts for LLMs: A Survey</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
@@ -10818,7 +10810,7 @@
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>A stepwise (unbatched) execution baseline is compared against WAB's action bundles on context-retrieval query counts and browser-cloud round trips within the WebQA case study. No competing agentic-browser runtime or security mechanism is implemented for comparison, and no defended-versus-undefended attack comparison is reported.</t>
+          <t>N/A - survey paper; compares/contrasts existing solution strategies from the literature rather than running its own baseline experiments, organized by objective: 'faithful to context' strategies (fine-tuning e.g. KAFT, prompting, contrastive decoding e.g. CAD, knowledge plug-in modules e.g. CuQA, extended pre-training e.g. ICLM, fact-validity prediction) vs. 'discriminating misinformation/faithful to memory' strategies (defensive prompting, query augmentation with cross-source confidence checking, training a discriminator) vs. 'disentangling sources' (e.g. DisentQA, giving separate context-based and memory-based answers) vs. 'improving factuality' (e.g. COMBO, CD-squared) for context-memory conflict; specialized contradiction-detection models (e.g. PCNN) vs. general LLM-plus-tool fact-checking frameworks for inter-context conflict; fine-tuning, plug-in modules (e.g. CRM), and output-ensembling (e.g. ConCoRD) for intra-memory conflict</t>
         </is>
       </c>
       <c r="F245" s="5" t="n"/>
@@ -10826,7 +10818,7 @@
       <c r="H245" s="5" t="n"/>
       <c r="I245" s="5" t="inlineStr">
         <is>
-          <t>74aec0665c948c64072682901b7e95e7b71286e4</t>
+          <t>ab8e6df5001dbb9b48445220099425aff536b3e8</t>
         </is>
       </c>
     </row>
@@ -10836,7 +10828,7 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>WAB: Overcoming Memory, Network, and Security Walls in Native Agentic Browsers with WebAssembly</t>
+          <t>Knowledge Conflicts for LLMs: A Survey</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
@@ -10849,13 +10841,17 @@
           <t>freetext</t>
         </is>
       </c>
-      <c r="E246" s="2" t="n"/>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>Partially adversarial for one sub-category (context-memory conflict): the survey explicitly discusses that adversaries can exploit context-memory conflict by introducing false or misleading information into web corpora that retrieval-augmented LLMs draw from, or directly into user conversations via techniques such as prompt injection (citing Liu et al. 2023b, Greshake et al. 2023, Yi et al. 2023), posing a practical threat since LLMs might unknowingly propagate such misinformation if it is incorporated without scrutiny; the other two conflict categories (inter-context and intra-memory) are framed as predominantly non-adversarial, arising incidentally from temporal misalignment between training data and current facts, natural misinformation/noise in retrieved documents, training-corpus bias, stochastic decoding randomness, and side effects of knowledge-editing techniques.</t>
+        </is>
+      </c>
       <c r="F246" s="5" t="n"/>
       <c r="G246" s="5" t="n"/>
       <c r="H246" s="5" t="n"/>
       <c r="I246" s="5" t="inlineStr">
         <is>
-          <t>74aec0665c948c64072682901b7e95e7b71286e4</t>
+          <t>ab8e6df5001dbb9b48445220099425aff536b3e8</t>
         </is>
       </c>
     </row>
@@ -10865,7 +10861,7 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>WAB: Overcoming Memory, Network, and Security Walls in Native Agentic Browsers with WebAssembly</t>
+          <t>Knowledge Conflicts for LLMs: A Survey</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
@@ -10880,7 +10876,7 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>The paper is explicitly a proof of concept presented in a four-page Web Conference companion paper, and the authors frame the WebQA study as highlighting potential rather than establishing results. Consequently the security wall - the motivation most relevant to this corpus - is addressed by design and not evaluated: no prompt-injection attack is executed against WAB, so the claim that the allowlisted capability API prevents high-impact side effects is untested, and the practical question of how capability grants are decided (who authorizes what, and whether a user can be socially engineered into granting) is unaddressed. Performance claims are illustrated on a single representative workflow trace rather than measured across workloads with variance. Whether batching multiple action steps per LLM call harms task success - since the agent commits to a bundle before observing intermediate results - is not quantified, and that trade-off is central to the network-wall mechanism.</t>
+          <t>No explicit numbered Limitations section is present in the pages read, but the survey's own framing repeatedly identifies open gaps in the surveyed literature that it argues remain unresolved: existing mitigation approaches for context-memory conflict are noted to have contradictory goals because they fail to distinguish between the two different causes of conflict (temporal misalignment vs. misinformation pollution), and the authors argue blind faithfulness to either context or parametric memory is undesirable, favoring instead approaches that grant the LLM agency to give distinct, well-reasoned answers - a design principle the surveyed work has not yet converged on; for inter-context conflict, unified and efficient methods capable of handling multiple different conflict types simultaneously are identified as a still-unsolved, formidable challenge, and the use of external tools to help LLMs resolve inter-context conflicts is flagged as a promising but underexplored direction; for intra-memory conflict, existing knowledge-editing methods are noted to generalize poorly (modifications often fail to propagate consistently across all relevant contexts), meaning current solutions can introduce new inconsistencies while attempting to fix others.</t>
         </is>
       </c>
       <c r="F247" s="5" t="n"/>
@@ -10888,7 +10884,7 @@
       <c r="H247" s="5" t="n"/>
       <c r="I247" s="5" t="inlineStr">
         <is>
-          <t>74aec0665c948c64072682901b7e95e7b71286e4</t>
+          <t>ab8e6df5001dbb9b48445220099425aff536b3e8</t>
         </is>
       </c>
     </row>
@@ -10898,7 +10894,7 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>WAB: Overcoming Memory, Network, and Security Walls in Native Agentic Browsers with WebAssembly</t>
+          <t>Knowledge Conflicts for LLMs: A Survey</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
@@ -10913,7 +10909,7 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>Proposes WAB, a WebAssembly-centered runtime for 'native agentic browsers' - browsers that treat agent execution as a first-class workload, running multi-step workflows locally at interactive latency while keeping sensitive user context on-device. The paper frames three runtime 'walls' that in-browser agent execution hits: a memory wall (agents need low-tail-latency access to evolving semantic context, but browser memory and persistent storage are constrained and heterogeneous), a network wall (stepwise tool invocation turns long-horizon workflows into RTT-amplified pipelines whose latency and variance compound per step), and a security wall (untrusted content and prompt injection can steer agents toward high-impact side effects without enforceable least-privilege boundaries). Wasm is proposed as a unifying answer because it supplies a portable execution target, a sandboxed environment, and efficient compute. Three mechanisms follow: Context, doing in-browser semantic retrieval over tiered storage and loading context into Wasm memory on demand; Actions, a Wasm execution module that batches multiple action steps per LLM call to cut browser-cloud round trips; and Authority, an allowlisted capability API for the Wasm sandbox with explicit grants and revocation for external access. The Authority mechanism is the security contribution and it is deny-by-default: unauthorized side effects are blocked unless explicitly and revocably permitted, so a successful injection still cannot reach an ungranted capability. Interesting for this corpus because it derives an execution-stage security boundary from a performance-motivated runtime choice rather than adding a separate guard.</t>
+          <t>Provides the first dedicated, systematic survey of 'knowledge conflicts' in large language models - situations where an LLM must reconcile discrepant knowledge from different sources when generating a response - proposing a three-part taxonomy: context-memory conflict (discrepancy between externally supplied contextual knowledge, e.g. retrieved documents, user prompts, or dialogue history, and the LLM's internal parametric knowledge), inter-context conflict (discrepancy among multiple pieces of contextual knowledge themselves, e.g. conflicting retrieved documents), and intra-memory conflict (discrepancy within the LLM's own parametric knowledge, surfacing as inconsistent responses to semantically equivalent but syntactically different prompts). For each category, the survey systematically reviews (a) root causes - temporal misalignment and misinformation pollution for context-memory conflict; misinformation and outdated information for inter-context conflict; training-corpus bias, decoding-strategy randomness, and knowledge-editing side effects for intra-memory conflict; (b) empirical analyses of how LLMs behave when such conflicts arise, drawing on dozens of surveyed studies to characterize patterns like confirmation bias, popularity-dependent evidence preference, order sensitivity, subpar contradiction-detection accuracy, and self-inconsistency rates; and (c) existing mitigation solutions organized by their intended behavioral objective (faithful-to-context, faithful-to-memory/discriminating-misinformation, disentangling-sources, and improving-overall-factuality strategies, further split into pre-hoc vs. post-hoc timing relative to when the conflict arises). The survey frames knowledge conflict not merely as an isolated phenomenon but as a causal nexus connecting root-cause triggers to downstream LLM behaviors (including hallucination), catalogs 10 existing evaluation datasets across the three conflict categories, and explicitly notes that context-memory conflict in particular has a security-relevant dimension, since adversaries can deliberately introduce misinformation into retrieved web content or user-supplied context (including via prompt injection) to manipulate an LLM's output, while the survey argues current solutions remain incomplete - failing to distinguish conflict causes, lacking unified multi-conflict-type handling, and suffering generalization limitations in knowledge-editing-based fixes - identifying these as open directions for future research toward more robust, trustworthy LLMs.</t>
         </is>
       </c>
       <c r="F248" s="5" t="n"/>
@@ -10921,7 +10917,7 @@
       <c r="H248" s="5" t="n"/>
       <c r="I248" s="5" t="inlineStr">
         <is>
-          <t>74aec0665c948c64072682901b7e95e7b71286e4</t>
+          <t>ab8e6df5001dbb9b48445220099425aff536b3e8</t>
         </is>
       </c>
     </row>
@@ -10931,7 +10927,7 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>Causal Intervention-Based Memory Selection for Long-Horizon LLM Agents</t>
+          <t>Meticulous Thought Defender: Fine-Grained Chain-of-Thought (CoT) for Detecting Prompt Injection Attacks of Large Language Models</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
@@ -10954,7 +10950,7 @@
       <c r="H249" s="5" t="n"/>
       <c r="I249" s="5" t="inlineStr">
         <is>
-          <t>90df5be685de81b6b1acde9031629969b9ce2b49</t>
+          <t>06fa2b9d40f97bd093aa3d21f42828ed82d8f55e</t>
         </is>
       </c>
     </row>
@@ -10964,7 +10960,7 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>Causal Intervention-Based Memory Selection for Long-Horizon LLM Agents</t>
+          <t>Meticulous Thought Defender: Fine-Grained Chain-of-Thought (CoT) for Detecting Prompt Injection Attacks of Large Language Models</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
@@ -10979,7 +10975,7 @@
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>ML/AI</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="F250" s="5" t="n"/>
@@ -10987,7 +10983,7 @@
       <c r="H250" s="5" t="n"/>
       <c r="I250" s="5" t="inlineStr">
         <is>
-          <t>90df5be685de81b6b1acde9031629969b9ce2b49</t>
+          <t>06fa2b9d40f97bd093aa3d21f42828ed82d8f55e</t>
         </is>
       </c>
     </row>
@@ -10997,7 +10993,7 @@
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>Causal Intervention-Based Memory Selection for Long-Horizon LLM Agents</t>
+          <t>Meticulous Thought Defender: Fine-Grained Chain-of-Thought (CoT) for Detecting Prompt Injection Attacks of Large Language Models</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
@@ -11020,7 +11016,7 @@
       <c r="H251" s="5" t="n"/>
       <c r="I251" s="5" t="inlineStr">
         <is>
-          <t>90df5be685de81b6b1acde9031629969b9ce2b49</t>
+          <t>06fa2b9d40f97bd093aa3d21f42828ed82d8f55e</t>
         </is>
       </c>
     </row>
@@ -11030,7 +11026,7 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>Causal Intervention-Based Memory Selection for Long-Horizon LLM Agents</t>
+          <t>Meticulous Thought Defender: Fine-Grained Chain-of-Thought (CoT) for Detecting Prompt Injection Attacks of Large Language Models</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
@@ -11053,7 +11049,7 @@
       <c r="H252" s="5" t="n"/>
       <c r="I252" s="5" t="inlineStr">
         <is>
-          <t>90df5be685de81b6b1acde9031629969b9ce2b49</t>
+          <t>06fa2b9d40f97bd093aa3d21f42828ed82d8f55e</t>
         </is>
       </c>
     </row>
@@ -11063,7 +11059,7 @@
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>Causal Intervention-Based Memory Selection for Long-Horizon LLM Agents</t>
+          <t>Meticulous Thought Defender: Fine-Grained Chain-of-Thought (CoT) for Detecting Prompt Injection Attacks of Large Language Models</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
@@ -11078,7 +11074,7 @@
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F253" s="5" t="n"/>
@@ -11086,7 +11082,7 @@
       <c r="H253" s="5" t="n"/>
       <c r="I253" s="5" t="inlineStr">
         <is>
-          <t>90df5be685de81b6b1acde9031629969b9ce2b49</t>
+          <t>06fa2b9d40f97bd093aa3d21f42828ed82d8f55e</t>
         </is>
       </c>
     </row>
@@ -11096,7 +11092,7 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Causal Intervention-Based Memory Selection for Long-Horizon LLM Agents</t>
+          <t>Meticulous Thought Defender: Fine-Grained Chain-of-Thought (CoT) for Detecting Prompt Injection Attacks of Large Language Models</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
@@ -11111,7 +11107,7 @@
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="F254" s="5" t="n"/>
@@ -11119,7 +11115,7 @@
       <c r="H254" s="5" t="n"/>
       <c r="I254" s="5" t="inlineStr">
         <is>
-          <t>90df5be685de81b6b1acde9031629969b9ce2b49</t>
+          <t>06fa2b9d40f97bd093aa3d21f42828ed82d8f55e</t>
         </is>
       </c>
     </row>
@@ -11129,7 +11125,7 @@
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>Causal Intervention-Based Memory Selection for Long-Horizon LLM Agents</t>
+          <t>Meticulous Thought Defender: Fine-Grained Chain-of-Thought (CoT) for Detecting Prompt Injection Attacks of Large Language Models</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
@@ -11144,7 +11140,7 @@
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F255" s="5" t="n"/>
@@ -11152,7 +11148,7 @@
       <c r="H255" s="5" t="n"/>
       <c r="I255" s="5" t="inlineStr">
         <is>
-          <t>90df5be685de81b6b1acde9031629969b9ce2b49</t>
+          <t>06fa2b9d40f97bd093aa3d21f42828ed82d8f55e</t>
         </is>
       </c>
     </row>
@@ -11162,7 +11158,7 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>Causal Intervention-Based Memory Selection for Long-Horizon LLM Agents</t>
+          <t>Meticulous Thought Defender: Fine-Grained Chain-of-Thought (CoT) for Detecting Prompt Injection Attacks of Large Language Models</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
@@ -11177,7 +11173,7 @@
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F256" s="5" t="n"/>
@@ -11185,7 +11181,7 @@
       <c r="H256" s="5" t="n"/>
       <c r="I256" s="5" t="inlineStr">
         <is>
-          <t>90df5be685de81b6b1acde9031629969b9ce2b49</t>
+          <t>06fa2b9d40f97bd093aa3d21f42828ed82d8f55e</t>
         </is>
       </c>
     </row>
@@ -11195,7 +11191,7 @@
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>Causal Intervention-Based Memory Selection for Long-Horizon LLM Agents</t>
+          <t>Meticulous Thought Defender: Fine-Grained Chain-of-Thought (CoT) for Detecting Prompt Injection Attacks of Large Language Models</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
@@ -11218,7 +11214,7 @@
       <c r="H257" s="5" t="n"/>
       <c r="I257" s="5" t="inlineStr">
         <is>
-          <t>90df5be685de81b6b1acde9031629969b9ce2b49</t>
+          <t>06fa2b9d40f97bd093aa3d21f42828ed82d8f55e</t>
         </is>
       </c>
     </row>
@@ -11228,7 +11224,7 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>Causal Intervention-Based Memory Selection for Long-Horizon LLM Agents</t>
+          <t>Meticulous Thought Defender: Fine-Grained Chain-of-Thought (CoT) for Detecting Prompt Injection Attacks of Large Language Models</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
@@ -11243,7 +11239,7 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>session-persistent</t>
+          <t>one-shot</t>
         </is>
       </c>
       <c r="F258" s="5" t="n"/>
@@ -11251,7 +11247,7 @@
       <c r="H258" s="5" t="n"/>
       <c r="I258" s="5" t="inlineStr">
         <is>
-          <t>90df5be685de81b6b1acde9031629969b9ce2b49</t>
+          <t>06fa2b9d40f97bd093aa3d21f42828ed82d8f55e</t>
         </is>
       </c>
     </row>
@@ -11261,7 +11257,7 @@
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>Causal Intervention-Based Memory Selection for Long-Horizon LLM Agents</t>
+          <t>Meticulous Thought Defender: Fine-Grained Chain-of-Thought (CoT) for Detecting Prompt Injection Attacks of Large Language Models</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
@@ -11284,7 +11280,7 @@
       <c r="H259" s="5" t="n"/>
       <c r="I259" s="5" t="inlineStr">
         <is>
-          <t>90df5be685de81b6b1acde9031629969b9ce2b49</t>
+          <t>06fa2b9d40f97bd093aa3d21f42828ed82d8f55e</t>
         </is>
       </c>
     </row>
@@ -11294,7 +11290,7 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>Causal Intervention-Based Memory Selection for Long-Horizon LLM Agents</t>
+          <t>Meticulous Thought Defender: Fine-Grained Chain-of-Thought (CoT) for Detecting Prompt Injection Attacks of Large Language Models</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
@@ -11307,17 +11303,13 @@
           <t>secondary</t>
         </is>
       </c>
-      <c r="E260" s="2" t="inlineStr">
-        <is>
-          <t>Full framework, benchmark construction code, and experimental pipeline publicly released at https://github.com/Saksham4796/causal-memory-intervention (stated explicitly in the abstract and confirmed on the title page).</t>
-        </is>
-      </c>
+      <c r="E260" s="2" t="n"/>
       <c r="F260" s="5" t="n"/>
       <c r="G260" s="5" t="n"/>
       <c r="H260" s="5" t="n"/>
       <c r="I260" s="5" t="inlineStr">
         <is>
-          <t>90df5be685de81b6b1acde9031629969b9ce2b49</t>
+          <t>06fa2b9d40f97bd093aa3d21f42828ed82d8f55e</t>
         </is>
       </c>
     </row>
@@ -11327,7 +11319,7 @@
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>Causal Intervention-Based Memory Selection for Long-Horizon LLM Agents</t>
+          <t>Meticulous Thought Defender: Fine-Grained Chain-of-Thought (CoT) for Detecting Prompt Injection Attacks of Large Language Models</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
@@ -11342,7 +11334,7 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>GPT-4.1 is used as the shared final response model across all compared memory methods; GPT-5 serves as both the dataset-construction model (generating 100 candidate benchmark examples) and the LLM judge for the hybrid task score; text-embedding-3-large is used for the vector-memory baseline's semantic retrieval. All methods share the same response model and scoring pipeline so that differences are attributable only to memory selection.</t>
+          <t>Qwen2.5 family at several scales (0.5B, 1.5B, 3B-Instruct, 7B-Instruct, 14B-Instruct) with DeepSeek-R1 and GPT-4 as comparators.</t>
         </is>
       </c>
       <c r="F261" s="5" t="n"/>
@@ -11350,7 +11342,7 @@
       <c r="H261" s="5" t="n"/>
       <c r="I261" s="5" t="inlineStr">
         <is>
-          <t>90df5be685de81b6b1acde9031629969b9ce2b49</t>
+          <t>06fa2b9d40f97bd093aa3d21f42828ed82d8f55e</t>
         </is>
       </c>
     </row>
@@ -11360,7 +11352,7 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>Causal Intervention-Based Memory Selection for Long-Horizon LLM Agents</t>
+          <t>Meticulous Thought Defender: Fine-Grained Chain-of-Thought (CoT) for Detecting Prompt Injection Attacks of Large Language Models</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
@@ -11375,7 +11367,7 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>CAUSAL-LOCOMO, a causally annotated memory-selection benchmark constructed by the authors from LoCoMo (Maharana et al., 2024) long-conversation QA data. Each example is converted into a structured memory bank containing useful memories (rewritten supporting evidence), irrelevant distractors (sampled from the same conversation), and synthetic harmful/poisoned memories (plausible but misleading, contradicting the gold answer or swapping entities/temporal facts). After LLM-assisted generation (GPT-5) and deterministic filtering/schema validation, the final benchmark contains 87 evaluation examples with 432 past sessions and 491 memory entries (89 useful, 348 irrelevant, 54 harmful), spanning 46 temporal, 25 multi-evidence, 14 inferential, and 2 factual memory QA examples.</t>
+          <t>Two public prompt-injection test sets, used test-split-only so the baseline detector's training data is not reused: Deepset (116 rows, 51.7% injected) and Safe-guard-prompt-injection (2.06k rows, 31.6% injected). Combined 2,176 rows, 710 positive (injected) and 1,466 negative.</t>
         </is>
       </c>
       <c r="F262" s="5" t="n"/>
@@ -11383,7 +11375,7 @@
       <c r="H262" s="5" t="n"/>
       <c r="I262" s="5" t="inlineStr">
         <is>
-          <t>90df5be685de81b6b1acde9031629969b9ce2b49</t>
+          <t>06fa2b9d40f97bd093aa3d21f42828ed82d8f55e</t>
         </is>
       </c>
     </row>
@@ -11393,7 +11385,7 @@
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>Causal Intervention-Based Memory Selection for Long-Horizon LLM Agents</t>
+          <t>Meticulous Thought Defender: Fine-Grained Chain-of-Thought (CoT) for Detecting Prompt Injection Attacks of Large Language Models</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
@@ -11408,7 +11400,7 @@
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>On the 87-example CAUSAL-LOCOMO benchmark, CMI achieves the best overall task score (0.846), success rate (0.816), useful-memory F1 (0.875), and near-perfect bad-memory rejection (0.990) with zero poisoned-memory adoption (0.000), while selecting fewer than one memory on average (0.943) -- indicating its gains come from selective filtering rather than larger context. The strongest non-CMI baselines, reflection memory (0.845 task score) and vector memory (0.839), achieve comparable task scores but adopt poisoned memories far more often (0.540 and 0.609 poison-adoption rates respectively, vs. CMI's 0.000) while selecting 3 memories on average. Full-history and summary-memory baselines underperform despite exposing far more context (5.644 memories on average): full history scores only 0.515 task score / 0.218 success rate, and summary memory scores 0.723 / 0.586, both with 0.000 bad-memory rejection. The no-memory baseline scores lowest (0.429 task score, 0.034 success rate). CMI's causal utility diagnostics show useful memories have positive average utility (+0.307), irrelevant memories near-zero (-0.009), and harmful memories negative (-0.033), directly evidencing the intervention mechanism. By task family, CMI leads on multi-evidence QA (0.754) and ties for best on factual QA (0.985, only 2 examples), while vector memory leads temporal QA (0.925) and reflection memory leads inferential QA (0.823, vs. CMI's 0.808).</t>
+          <t>A fine-grained chain-of-thought detection framework that dissects the model's step-by-step reasoning improves prompt-injection detection over static-rule and surface-level detectors, with improved interpretability of why an input is flagged.</t>
         </is>
       </c>
       <c r="F263" s="5" t="n"/>
@@ -11416,7 +11408,7 @@
       <c r="H263" s="5" t="n"/>
       <c r="I263" s="5" t="inlineStr">
         <is>
-          <t>90df5be685de81b6b1acde9031629969b9ce2b49</t>
+          <t>06fa2b9d40f97bd093aa3d21f42828ed82d8f55e</t>
         </is>
       </c>
     </row>
@@ -11426,7 +11418,7 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>Causal Intervention-Based Memory Selection for Long-Horizon LLM Agents</t>
+          <t>Meticulous Thought Defender: Fine-Grained Chain-of-Thought (CoT) for Detecting Prompt Injection Attacks of Large Language Models</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
@@ -11441,7 +11433,7 @@
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>Six baseline memory-access strategies compared against CMI, all sharing the same GPT-4.1 response model and scoring pipeline: No Memory (task request only, no external memory), Full History (raw past LoCoMo sessions provided, no explicit selection), Summary Memory (single synthesized summary of the structured memory bank), Vector Memory (embedding-similarity top-k retrieval via text-embedding-3-large), Graph Memory (lightweight lexical/scope-based graph retrieval over memory nodes), and Reflection Memory (deterministic label-aware reflections retrieved via keyword matching, inspired by Shinn et al. 2023's Reflexion).</t>
+          <t>LLM Guard (a dedicated prompt-injection detector tool) and other detection approaches, evaluated on the same 2,176-row combined test set.</t>
         </is>
       </c>
       <c r="F264" s="5" t="n"/>
@@ -11449,7 +11441,7 @@
       <c r="H264" s="5" t="n"/>
       <c r="I264" s="5" t="inlineStr">
         <is>
-          <t>90df5be685de81b6b1acde9031629969b9ce2b49</t>
+          <t>06fa2b9d40f97bd093aa3d21f42828ed82d8f55e</t>
         </is>
       </c>
     </row>
@@ -11459,7 +11451,7 @@
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>Causal Intervention-Based Memory Selection for Long-Horizon LLM Agents</t>
+          <t>Meticulous Thought Defender: Fine-Grained Chain-of-Thought (CoT) for Detecting Prompt Injection Attacks of Large Language Models</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
@@ -11474,7 +11466,7 @@
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>N/A - non-adversarial in the classic red-team/defender sense (this is a memory-selection methodology paper, not a security paper), but the benchmark explicitly incorporates synthetic harmful/poisoned memories -- plausible but misleading entries that contradict the gold answer, swap entities, or introduce incorrect temporal information -- to test robustness against misleading retrieval, and the paper's own Limitations section explicitly notes that similar poisoned-memory constructions 'could be misused to attack memory-augmented agents,' citing prior prompt-injection and RAG-poisoning work.</t>
+          <t>Prompt injection against LLMs, detected at the input stage. The defender sees the candidate input and must classify it; the attacker varies injection type across the categories catalogued in the paper's type table.</t>
         </is>
       </c>
       <c r="F265" s="5" t="n"/>
@@ -11482,7 +11474,7 @@
       <c r="H265" s="5" t="n"/>
       <c r="I265" s="5" t="inlineStr">
         <is>
-          <t>90df5be685de81b6b1acde9031629969b9ce2b49</t>
+          <t>06fa2b9d40f97bd093aa3d21f42828ed82d8f55e</t>
         </is>
       </c>
     </row>
@@ -11492,7 +11484,7 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>Causal Intervention-Based Memory Selection for Long-Horizon LLM Agents</t>
+          <t>Meticulous Thought Defender: Fine-Grained Chain-of-Thought (CoT) for Detecting Prompt Injection Attacks of Large Language Models</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
@@ -11507,7 +11499,7 @@
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>The paper has an explicit Section 8, 'Limitations and Ethical Considerations.' Key points: (1) the current CMI implementation relies on gold memory role-labels (useful/irrelevant/harmful) during selection, so experiments evaluate the value of explicit causal-memory structure rather than proving agents can infer causal roles from raw memories alone -- a fully deployable version would need predicted causal-role estimates evaluated under distribution shift and adversarial conditions; (2) CAUSAL-LOCOMO is relatively small (87 filtered examples derived from LoCoMo), concentrated mainly in temporal, multi-evidence, and inferential QA, and does not cover the full range of deployed-agent memory failures (stale preferences, incorrect summaries, entity-linking errors, conflicting updates, long-term drift), and its harmful memories are synthetic adversarial insertions that may not fully capture naturally occurring or human-crafted corruptions; (3) the hybrid task score combines a deterministic scorer with a GPT-5 judge, introducing dependence on judge calibration, prompt sensitivity, and possible bias -- future work should include larger benchmarks, label-free settings, human-authored corruptions, independent human evaluation, and judge-model ablations; (4) CMI incurs additional inference cost/latency from its pre-answer intervention calls (no-memory, with-memory, perturbed-memory) relative to simple retrieval, which practical deployments may need to mitigate via caching, restricting scoring to high-risk queries, or smaller verifier models. A separate Ethical Considerations discussion also notes privacy risks (memories may contain sensitive personal/health/relationship information) and the dual-use risk of harmful-memory construction techniques.</t>
+          <t>Not explicitly stated in a limitations section. Evaluation is confined to two public English-language test sets and to classification accuracy rather than end-to-end agent impact.</t>
         </is>
       </c>
       <c r="F266" s="5" t="n"/>
@@ -11515,7 +11507,7 @@
       <c r="H266" s="5" t="n"/>
       <c r="I266" s="5" t="inlineStr">
         <is>
-          <t>90df5be685de81b6b1acde9031629969b9ce2b49</t>
+          <t>06fa2b9d40f97bd093aa3d21f42828ed82d8f55e</t>
         </is>
       </c>
     </row>
@@ -11525,7 +11517,7 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>Causal Intervention-Based Memory Selection for Long-Horizon LLM Agents</t>
+          <t>Meticulous Thought Defender: Fine-Grained Chain-of-Thought (CoT) for Detecting Prompt Injection Attacks of Large Language Models</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
@@ -11540,7 +11532,7 @@
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>Causal Memory Intervention (CMI) reframes long-horizon LLM agent memory selection as a causal decision problem rather than a similarity-based retrieval problem. Given a user request and a persistent memory bank, CMI first proposes a small candidate set via a broad hybrid retriever, then scores each candidate through three controlled interventions using the response model: answering with no memory, answering with only the candidate memory, and answering with a perturbed version of that memory. From these, CMI computes Utility(m) as the task-score improvement of with-memory over no-memory, and Stability(m) as the score difference between with-memory and perturbed-memory conditions. A memory is selected into the final context only if Utility(m) &gt; 0 and Stability(m) &gt;= 0, subject to a memory budget and risk-filtering constraints (in the annotated benchmark setting, harmful-labeled memories are additionally suppressed as a risk signal, standing in for a learned/prompted causal-role predictor in a label-free deployment). The final answer is generated by the shared response model conditioned only on the selected subset. This intervention-based selection is evaluated on CAUSAL-LOCOMO against six baselines using a hybrid task score (0.7 x deterministic scorer + 0.3 x GPT-5 judge score), success rate, useful-memory F1, bad-memory rejection, poisoned-memory adoption rate, and average memories selected/exposed, isolating whether performance gains come from selective, causally-grounded memory use versus simply exposing more context.</t>
+          <t>A chain-of-thought based prompt-injection detector: rather than matching static rules or surface features, it decomposes the model's reasoning into fine-grained steps and uses multidimensional signals from that trace to classify an input, aiming at both robustness and interpretability of the decision.</t>
         </is>
       </c>
       <c r="F267" s="5" t="n"/>
@@ -11548,7 +11540,7 @@
       <c r="H267" s="5" t="n"/>
       <c r="I267" s="5" t="inlineStr">
         <is>
-          <t>90df5be685de81b6b1acde9031629969b9ce2b49</t>
+          <t>06fa2b9d40f97bd093aa3d21f42828ed82d8f55e</t>
         </is>
       </c>
     </row>
@@ -11558,7 +11550,7 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>Embedding-Based Detection of Indirect Prompt Injection Attacks in Large Language Models Using Semantic Context Analysis</t>
+          <t>Towards trustworthy agentic AI: a comprehensive survey of safety, robustness, privacy, and system security</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
@@ -11581,7 +11573,7 @@
       <c r="H268" s="5" t="n"/>
       <c r="I268" s="5" t="inlineStr">
         <is>
-          <t>dfc9d7ad54c197d239cb473f3ae7a64ab50d0e90</t>
+          <t>e7ce3289d680295e57dc66ad0563924e2006cd3a</t>
         </is>
       </c>
     </row>
@@ -11591,7 +11583,7 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>Embedding-Based Detection of Indirect Prompt Injection Attacks in Large Language Models Using Semantic Context Analysis</t>
+          <t>Towards trustworthy agentic AI: a comprehensive survey of safety, robustness, privacy, and system security</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
@@ -11614,7 +11606,7 @@
       <c r="H269" s="5" t="n"/>
       <c r="I269" s="5" t="inlineStr">
         <is>
-          <t>dfc9d7ad54c197d239cb473f3ae7a64ab50d0e90</t>
+          <t>e7ce3289d680295e57dc66ad0563924e2006cd3a</t>
         </is>
       </c>
     </row>
@@ -11624,7 +11616,7 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>Embedding-Based Detection of Indirect Prompt Injection Attacks in Large Language Models Using Semantic Context Analysis</t>
+          <t>Towards trustworthy agentic AI: a comprehensive survey of safety, robustness, privacy, and system security</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
@@ -11647,7 +11639,7 @@
       <c r="H270" s="5" t="n"/>
       <c r="I270" s="5" t="inlineStr">
         <is>
-          <t>dfc9d7ad54c197d239cb473f3ae7a64ab50d0e90</t>
+          <t>e7ce3289d680295e57dc66ad0563924e2006cd3a</t>
         </is>
       </c>
     </row>
@@ -11657,7 +11649,7 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>Embedding-Based Detection of Indirect Prompt Injection Attacks in Large Language Models Using Semantic Context Analysis</t>
+          <t>Towards trustworthy agentic AI: a comprehensive survey of safety, robustness, privacy, and system security</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
@@ -11672,7 +11664,7 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>defense</t>
+          <t>neither</t>
         </is>
       </c>
       <c r="F271" s="5" t="n"/>
@@ -11680,7 +11672,7 @@
       <c r="H271" s="5" t="n"/>
       <c r="I271" s="5" t="inlineStr">
         <is>
-          <t>dfc9d7ad54c197d239cb473f3ae7a64ab50d0e90</t>
+          <t>e7ce3289d680295e57dc66ad0563924e2006cd3a</t>
         </is>
       </c>
     </row>
@@ -11690,7 +11682,7 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>Embedding-Based Detection of Indirect Prompt Injection Attacks in Large Language Models Using Semantic Context Analysis</t>
+          <t>Towards trustworthy agentic AI: a comprehensive survey of safety, robustness, privacy, and system security</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
@@ -11705,7 +11697,7 @@
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F272" s="5" t="n"/>
@@ -11713,7 +11705,7 @@
       <c r="H272" s="5" t="n"/>
       <c r="I272" s="5" t="inlineStr">
         <is>
-          <t>dfc9d7ad54c197d239cb473f3ae7a64ab50d0e90</t>
+          <t>e7ce3289d680295e57dc66ad0563924e2006cd3a</t>
         </is>
       </c>
     </row>
@@ -11723,7 +11715,7 @@
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>Embedding-Based Detection of Indirect Prompt Injection Attacks in Large Language Models Using Semantic Context Analysis</t>
+          <t>Towards trustworthy agentic AI: a comprehensive survey of safety, robustness, privacy, and system security</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
@@ -11746,7 +11738,7 @@
       <c r="H273" s="5" t="n"/>
       <c r="I273" s="5" t="inlineStr">
         <is>
-          <t>dfc9d7ad54c197d239cb473f3ae7a64ab50d0e90</t>
+          <t>e7ce3289d680295e57dc66ad0563924e2006cd3a</t>
         </is>
       </c>
     </row>
@@ -11756,7 +11748,7 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>Embedding-Based Detection of Indirect Prompt Injection Attacks in Large Language Models Using Semantic Context Analysis</t>
+          <t>Towards trustworthy agentic AI: a comprehensive survey of safety, robustness, privacy, and system security</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
@@ -11779,7 +11771,7 @@
       <c r="H274" s="5" t="n"/>
       <c r="I274" s="5" t="inlineStr">
         <is>
-          <t>dfc9d7ad54c197d239cb473f3ae7a64ab50d0e90</t>
+          <t>e7ce3289d680295e57dc66ad0563924e2006cd3a</t>
         </is>
       </c>
     </row>
@@ -11789,7 +11781,7 @@
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>Embedding-Based Detection of Indirect Prompt Injection Attacks in Large Language Models Using Semantic Context Analysis</t>
+          <t>Towards trustworthy agentic AI: a comprehensive survey of safety, robustness, privacy, and system security</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
@@ -11804,7 +11796,7 @@
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F275" s="5" t="n"/>
@@ -11812,7 +11804,7 @@
       <c r="H275" s="5" t="n"/>
       <c r="I275" s="5" t="inlineStr">
         <is>
-          <t>dfc9d7ad54c197d239cb473f3ae7a64ab50d0e90</t>
+          <t>e7ce3289d680295e57dc66ad0563924e2006cd3a</t>
         </is>
       </c>
     </row>
@@ -11822,7 +11814,7 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>Embedding-Based Detection of Indirect Prompt Injection Attacks in Large Language Models Using Semantic Context Analysis</t>
+          <t>Towards trustworthy agentic AI: a comprehensive survey of safety, robustness, privacy, and system security</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
@@ -11837,7 +11829,7 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>ingestion</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F276" s="5" t="n"/>
@@ -11845,7 +11837,7 @@
       <c r="H276" s="5" t="n"/>
       <c r="I276" s="5" t="inlineStr">
         <is>
-          <t>dfc9d7ad54c197d239cb473f3ae7a64ab50d0e90</t>
+          <t>e7ce3289d680295e57dc66ad0563924e2006cd3a</t>
         </is>
       </c>
     </row>
@@ -11855,7 +11847,7 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>Embedding-Based Detection of Indirect Prompt Injection Attacks in Large Language Models Using Semantic Context Analysis</t>
+          <t>Towards trustworthy agentic AI: a comprehensive survey of safety, robustness, privacy, and system security</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
@@ -11878,7 +11870,7 @@
       <c r="H277" s="5" t="n"/>
       <c r="I277" s="5" t="inlineStr">
         <is>
-          <t>dfc9d7ad54c197d239cb473f3ae7a64ab50d0e90</t>
+          <t>e7ce3289d680295e57dc66ad0563924e2006cd3a</t>
         </is>
       </c>
     </row>
@@ -11888,7 +11880,7 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>Embedding-Based Detection of Indirect Prompt Injection Attacks in Large Language Models Using Semantic Context Analysis</t>
+          <t>Towards trustworthy agentic AI: a comprehensive survey of safety, robustness, privacy, and system security</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
@@ -11911,7 +11903,7 @@
       <c r="H278" s="5" t="n"/>
       <c r="I278" s="5" t="inlineStr">
         <is>
-          <t>dfc9d7ad54c197d239cb473f3ae7a64ab50d0e90</t>
+          <t>e7ce3289d680295e57dc66ad0563924e2006cd3a</t>
         </is>
       </c>
     </row>
@@ -11921,7 +11913,7 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>Embedding-Based Detection of Indirect Prompt Injection Attacks in Large Language Models Using Semantic Context Analysis</t>
+          <t>Towards trustworthy agentic AI: a comprehensive survey of safety, robustness, privacy, and system security</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
@@ -11934,13 +11926,17 @@
           <t>secondary</t>
         </is>
       </c>
-      <c r="E279" s="2" t="n"/>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>No code or dataset artifact is released; this is a review/survey article rather than an empirical systems paper. The 'Data availability statement' explicitly confirms: 'No new data were created or analyzed in this study. Data sharing is not applicable to this article.'</t>
+        </is>
+      </c>
       <c r="F279" s="5" t="n"/>
       <c r="G279" s="5" t="n"/>
       <c r="H279" s="5" t="n"/>
       <c r="I279" s="5" t="inlineStr">
         <is>
-          <t>dfc9d7ad54c197d239cb473f3ae7a64ab50d0e90</t>
+          <t>e7ce3289d680295e57dc66ad0563924e2006cd3a</t>
         </is>
       </c>
     </row>
@@ -11950,7 +11946,7 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>Embedding-Based Detection of Indirect Prompt Injection Attacks in Large Language Models Using Semantic Context Analysis</t>
+          <t>Towards trustworthy agentic AI: a comprehensive survey of safety, robustness, privacy, and system security</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
@@ -11965,7 +11961,7 @@
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>Three embedding models as feature extractors: OpenAI text-embedding-3-small, GTE-large, and MiniLM-L6-v2, each paired with XGBoost, LightGBM and Random Forest classifiers. ChatGPT-4o-mini is used to generate the benign half of the dataset rather than as a detector. No target LLM is instrumented - detection is evaluated on prompts, not end-to-end agent behaviour.</t>
+          <t>N/A - this is a survey paper synthesizing the literature on trustworthy agentic AI rather than conducting its own model evaluations. It references numerous representative agentic systems and real-world incidents throughout (e.g., Microsoft 365 Copilot's 'EchoLeak' zero-click prompt injection vulnerability, CVE-2025-32711) and presents a detailed case study of security failures in open-source agentic systems (OpenClaw/Moltbook) rather than running its own benchmark evaluations.</t>
         </is>
       </c>
       <c r="F280" s="5" t="n"/>
@@ -11973,7 +11969,7 @@
       <c r="H280" s="5" t="n"/>
       <c r="I280" s="5" t="inlineStr">
         <is>
-          <t>dfc9d7ad54c197d239cb473f3ae7a64ab50d0e90</t>
+          <t>e7ce3289d680295e57dc66ad0563924e2006cd3a</t>
         </is>
       </c>
     </row>
@@ -11983,7 +11979,7 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>Embedding-Based Detection of Indirect Prompt Injection Attacks in Large Language Models Using Semantic Context Analysis</t>
+          <t>Towards trustworthy agentic AI: a comprehensive survey of safety, robustness, privacy, and system security</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
@@ -11998,7 +11994,7 @@
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>A purpose-built 70,000-sample dataset: 35,000 malicious instances taken from BIPIA (Benchmark for Indirect Prompt Injection Attacks) and 35,000 benign instances generated with ChatGPT-4o-mini. Metrics are accuracy, F1, and per-sample inference time (0.001 ms average). No agentic benchmark is used.</t>
+          <t>N/A as a primary contribution -- rather than introducing a new benchmark, the survey consolidates fragmented existing evaluation metrics and benchmark suites from the literature into what it calls a unified 'evaluation hub' (Section 4), covering both outcome signals (e.g., adversarial success rates) and process signals (e.g., constraint violations, trace completeness, compliance verifiability), along with scenario-to-metric mapping guidance intended to support release-gating decisions for real-world deployment.</t>
         </is>
       </c>
       <c r="F281" s="5" t="n"/>
@@ -12006,7 +12002,7 @@
       <c r="H281" s="5" t="n"/>
       <c r="I281" s="5" t="inlineStr">
         <is>
-          <t>dfc9d7ad54c197d239cb473f3ae7a64ab50d0e90</t>
+          <t>e7ce3289d680295e57dc66ad0563924e2006cd3a</t>
         </is>
       </c>
     </row>
@@ -12016,7 +12012,7 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>Embedding-Based Detection of Indirect Prompt Injection Attacks in Large Language Models Using Semantic Context Analysis</t>
+          <t>Towards trustworthy agentic AI: a comprehensive survey of safety, robustness, privacy, and system security</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
@@ -12031,7 +12027,7 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>The best configuration - OpenAI text-embedding-3-small embeddings with an XGBoost classifier - achieves 97.7% accuracy and an F1 of 0.977, which the authors report as matching or exceeding existing IPIA detection methods. The more practically consequential figure is inference cost: an average of 0.001 ms per sample, several orders of magnitude cheaper than LLM-based detection, which is what makes an always-on inline detection layer feasible rather than a design aspiration. Combined with model-agnosticism, this positions the method as a complement to prevention mechanisms rather than a replacement - it can be dropped into an existing pipeline without architectural change. The comparative design across three embedding models and three classifiers means the result identifies which component carries the performance rather than reporting a single tuned pipeline, though the strongest configuration depends on a proprietary API embedding model, which reintroduces an external dependency the rest of the design avoids.</t>
+          <t>As a survey, the paper's 'key result' is its synthesis and case study rather than a benchmarked numerical finding. Its central case study traces a real-world compromise of an open-source agentic system (OpenClaw/Moltbook) through the survey's own Perceive-Plan-Act-Reflect-Learn workflow lens, showing the failure was systemic across every stage: Perceive -- injected instructions were processed without validation (no input sanitization); Plan -- injected instructions altered the agent's plan to include data-exfiltration steps, with no constraint checker detecting the deviation; Act -- unrestricted tool access (file I/O, shell, network) allowed the agent to execute attacker-controlled commands without least-privilege enforcement; Reflect -- no anomaly detection flagged unusual credential-access patterns or data-transmission volumes; Learn -- malicious skills propagated through the agent's update/install mechanism without provenance checks or regression gating. The survey's explicit conclusion from this mapping is that 'the chain of failure is systemic; no single-stage mitigation would have been sufficient,' reinforcing a defense-in-depth principle as the paper's core practical recommendation, and that agentic AI security must be treated as privileged infrastructure (mandatory authentication, least-privilege scoping, cryptographically signed plugin governance, continuous runtime monitoring, and explicit human approval for sensitive actions) rather than optional hardening.</t>
         </is>
       </c>
       <c r="F282" s="5" t="n"/>
@@ -12039,7 +12035,7 @@
       <c r="H282" s="5" t="n"/>
       <c r="I282" s="5" t="inlineStr">
         <is>
-          <t>dfc9d7ad54c197d239cb473f3ae7a64ab50d0e90</t>
+          <t>e7ce3289d680295e57dc66ad0563924e2006cd3a</t>
         </is>
       </c>
     </row>
@@ -12049,7 +12045,7 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>Embedding-Based Detection of Indirect Prompt Injection Attacks in Large Language Models Using Semantic Context Analysis</t>
+          <t>Towards trustworthy agentic AI: a comprehensive survey of safety, robustness, privacy, and system security</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
@@ -12064,7 +12060,7 @@
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>A nine-way internal comparison: three embedding models (OpenAI text-embedding-3-small, GTE-large, MiniLM-L6-v2) crossed with three classifiers (XGBoost, LightGBM, Random Forest), with the OpenAI+XGBoost configuration best at 97.7% accuracy / 0.977 F1. Performance is described as matching or exceeding existing IPIA detection methods, but those methods are characterized from the literature rather than reimplemented and run on this dataset, so the cross-method comparison is indirect.</t>
+          <t>N/A - as a survey/review paper, there is no direct method-vs-baseline empirical comparison; the paper instead organizes and compares the trustworthy-AI research landscape itself, explicitly positioning its own contribution against prior surveys (which it characterizes as either covering general AI trustworthiness principles, LLM-specific trustworthiness evaluation, or narrower trust/safety issues for LLM-based agents and multi-agent systems, or providing architecture/application-centered overviews of agentic AI) by integrating a multi-dimensional trust taxonomy with an explicit workflow lens (Perceive-Plan-Act-Reflect-Learn) and consolidating process-aware evaluation with scenario-based release gating (summarized comparatively in the paper's Table 1).</t>
         </is>
       </c>
       <c r="F283" s="5" t="n"/>
@@ -12072,7 +12068,7 @@
       <c r="H283" s="5" t="n"/>
       <c r="I283" s="5" t="inlineStr">
         <is>
-          <t>dfc9d7ad54c197d239cb473f3ae7a64ab50d0e90</t>
+          <t>e7ce3289d680295e57dc66ad0563924e2006cd3a</t>
         </is>
       </c>
     </row>
@@ -12082,7 +12078,7 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>Embedding-Based Detection of Indirect Prompt Injection Attacks in Large Language Models Using Semantic Context Analysis</t>
+          <t>Towards trustworthy agentic AI: a comprehensive survey of safety, robustness, privacy, and system security</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
@@ -12095,13 +12091,17 @@
           <t>freetext</t>
         </is>
       </c>
-      <c r="E284" s="2" t="n"/>
+      <c r="E284" s="2" t="inlineStr">
+        <is>
+          <t>This survey covers a broad, multi-faceted threat landscape rather than a single formal threat model, organized around two core trustworthiness dimensions: Safety and Robustness, and Privacy and System Security. Representative threats discussed include indirect/zero-click prompt injection (e.g., the Microsoft 365 Copilot EchoLeak vulnerability, where specially crafted untrusted inputs such as emails trigger unintended agent behavior and sensitive data exposure without explicit user interaction), tool misuse and unrestricted/excessive tool access enabling attacker-controlled command execution, data exfiltration, memory/personalization privacy risks, and cascading multi-step trajectory failures where a minor early error propagates into high-impact downstream actions -- collectively framed as risks that must be assessed at the system level across an agent's full Perceive-Plan-Act-Reflect-Learn lifecycle, rather than via conventional single-turn LLM safety evaluations.</t>
+        </is>
+      </c>
       <c r="F284" s="5" t="n"/>
       <c r="G284" s="5" t="n"/>
       <c r="H284" s="5" t="n"/>
       <c r="I284" s="5" t="inlineStr">
         <is>
-          <t>dfc9d7ad54c197d239cb473f3ae7a64ab50d0e90</t>
+          <t>e7ce3289d680295e57dc66ad0563924e2006cd3a</t>
         </is>
       </c>
     </row>
@@ -12111,7 +12111,7 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>Embedding-Based Detection of Indirect Prompt Injection Attacks in Large Language Models Using Semantic Context Analysis</t>
+          <t>Towards trustworthy agentic AI: a comprehensive survey of safety, robustness, privacy, and system security</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
@@ -12126,7 +12126,7 @@
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>The authors are unusually forthcoming. The dataset combines BIPIA with synthetically generated benign examples and may therefore not match real-world user-content distributions - notably, benign instances generated by ChatGPT-4o-mini may be more homogeneous and more easily separable than organic content, which would inflate accuracy. As a single-shot embedding detector, the method may be defeated by adaptive attackers who iteratively rewrite injected instructions, particularly in interactive agent settings, and no such adversary is evaluated. They explicitly flag needed future work that is absent here: validation on external organic datasets, robustness testing under basic evasion transformations such as paraphrasing and formatting changes, cluster-quality analysis of the embedding space, ablations isolating the contribution of user-intent versus external-content embeddings, and - significantly for interpreting the headline - reporting standard deviations across multiple runs, since no variance is currently reported for the 97.7% figure.</t>
+          <t>The paper contains an explicit 'Summary of open problems' subsection (7.1) within the Conclusions: 'Despite rapid progress, important limitations remain before trustworthy agentic AI can be deployed at scale. First, today's agents are still far from reliable lifelong learners: they struggle with long-horizon generalization, are vulnerable to reward/specification gaming, and can accumulate errors across extended tool-mediated trajectories. Second, verification and evaluation remain bottlenecked by long-tail and interactive risks; simulations and testbeds rarely cover rare events, adaptive attacks, and sim-to-real gaps, while many evaluations depend on imperfect judges and incomplete trace standards. Third, deployment introduces persistent trade-offs and system risks, including privacy-utility tension in memory-based personalization and security vulnerabilities from tool access and credential management. Finally, frequent re-verification, monitoring, and safeguarding can impose substantial compute and operational costs.' The paper translates these limitations into five concrete future research/engineering challenges: (i) self-evolving agents with safe update rules and regression-gated releases; (ii) continuous runtime monitoring and verification able to detect rare-event and adversarial failures early; (iii) privacy-preserving personalization and memory governance that bounds leakage while preserving utility; (iv) efficiency-aware trust mechanisms delivering guarantees under realistic latency/energy budgets; (v) principled resolution of the trust-utility trade-off via risk-bounded, scenario-driven evaluation and deployment practices.</t>
         </is>
       </c>
       <c r="F285" s="5" t="n"/>
@@ -12134,7 +12134,7 @@
       <c r="H285" s="5" t="n"/>
       <c r="I285" s="5" t="inlineStr">
         <is>
-          <t>dfc9d7ad54c197d239cb473f3ae7a64ab50d0e90</t>
+          <t>e7ce3289d680295e57dc66ad0563924e2006cd3a</t>
         </is>
       </c>
     </row>
@@ -12144,7 +12144,7 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>Embedding-Based Detection of Indirect Prompt Injection Attacks in Large Language Models Using Semantic Context Analysis</t>
+          <t>Towards trustworthy agentic AI: a comprehensive survey of safety, robustness, privacy, and system security</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
@@ -12159,7 +12159,7 @@
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>Proposes an embedding-based detector for Indirect Prompt Injection Attacks that works by analysing the semantic relationship between the user's stated intent and the external content retrieved into context, rather than by inspecting the external content in isolation. That relational framing is the paper's core idea: an injected instruction is anomalous not because of its own surface features but because it is semantically unrelated to what the user asked for, which is a signal a content-only filter cannot see. The method is deliberately architecture-agnostic - it sits outside the LLM as an external detection layer requiring no modification to the model, in contrast to prevention-focused approaches that alter the underlying architecture. The study contributes a 70,000-sample dataset combining 35,000 malicious instances drawn from BIPIA (the Benchmark for Indirect Prompt Injection Attacks) with 35,000 benign instances generated using ChatGPT-4o-mini, and conducts a full factorial comparison of three embedding models (OpenAI text-embedding-3-small, GTE-large, MiniLM-L6-v2) against three classifiers (XGBoost, LightGBM, Random Forest). An ingestion-stage Track A defense; notable in this corpus for using an established external benchmark (BIPIA) for its attack half rather than a wholly self-generated attack set, which makes its malicious-class results more comparable than most defense papers in this batch.</t>
+          <t>This is a comprehensive survey of trustworthy agentic AI -- LLM-based systems augmented with planning, tool use, memory, and long-horizon multi-step interaction -- organized around two core trustworthiness dimensions the authors identify as most critical for high-risk deployments: Safety and Robustness, and Privacy and System Security (with other trustworthiness aspects such as value alignment, transparency, fairness, and accountability discussed as contextual rather than as parallel chapters). The survey's central organizing device is a Perceive-Plan-Act-Reflect-Learn workflow lens, used systematically to localize where specific risks emerge along an agent's operational lifecycle (e.g., unvalidated perception of untrusted inputs, unconstrained plan deviation from injected instructions, unrestricted tool execution without least-privilege enforcement, absent anomaly detection during reflection, and unguarded skill/capability propagation during learning/updating) and to map stage-targeted mitigation strategies onto each stage rather than treating trustworthiness as a single, undifferentiated property assessed only from final task outputs. For each of the two core dimensions, the survey clarifies key concepts, systematically identifies where risks emerge along this workflow, and summarizes corresponding stage-targeted mitigation strategies drawn from the literature. To make cross-paper evaluation practically comparable, the survey consolidates the field's fragmented evaluation metrics and benchmark suites into a unified 'evaluation hub,' explicitly emphasizing that trustworthy agents must be judged not only by final task success (outcome signals) but also by process signals such as constraint violations, trace completeness, compliance verifiability, and adversarial success rates, and provides scenario-to-metric mapping guidance intended to support real-world release-gating decisions. The survey culminates in a detailed case study applying its Perceive-Plan-Act-Reflect-Learn lens to a real-world security compromise of an open-source agentic system (OpenClaw/Moltbook), using it to concretely demonstrate that agentic-system failures are typically systemic chains spanning multiple lifecycle stages rather than single-point failures, and that no single-stage mitigation would have been sufficient to prevent the incident -- reinforcing the survey's core practical recommendation of defense-in-depth and treating agentic AI security as privileged infrastructure requiring mandatory authentication, least-privilege scoping, cryptographically signed plugin governance, continuous runtime monitoring, and explicit human approval for sensitive actions as baseline (non-optional) requirements.</t>
         </is>
       </c>
       <c r="F286" s="5" t="n"/>
@@ -12167,7 +12167,7 @@
       <c r="H286" s="5" t="n"/>
       <c r="I286" s="5" t="inlineStr">
         <is>
-          <t>dfc9d7ad54c197d239cb473f3ae7a64ab50d0e90</t>
+          <t>e7ce3289d680295e57dc66ad0563924e2006cd3a</t>
         </is>
       </c>
     </row>
@@ -12177,7 +12177,7 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>How Easily do Irrelevant Inputs Skew the Responses of Large Language Models?</t>
+          <t>Agentic Memory: Learning Unified Long-Term and Short-Term Memory Management for Large Language Model Agents</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
@@ -12200,7 +12200,7 @@
       <c r="H287" s="5" t="n"/>
       <c r="I287" s="5" t="inlineStr">
         <is>
-          <t>5168d3595acaf7528039ee542eb57d0dc3ad2fd8</t>
+          <t>fddca50008a46c925b288bae079e43ead0bbeb6e</t>
         </is>
       </c>
     </row>
@@ -12210,7 +12210,7 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>How Easily do Irrelevant Inputs Skew the Responses of Large Language Models?</t>
+          <t>Agentic Memory: Learning Unified Long-Term and Short-Term Memory Management for Large Language Model Agents</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
@@ -12233,7 +12233,7 @@
       <c r="H288" s="5" t="n"/>
       <c r="I288" s="5" t="inlineStr">
         <is>
-          <t>5168d3595acaf7528039ee542eb57d0dc3ad2fd8</t>
+          <t>fddca50008a46c925b288bae079e43ead0bbeb6e</t>
         </is>
       </c>
     </row>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>How Easily do Irrelevant Inputs Skew the Responses of Large Language Models?</t>
+          <t>Agentic Memory: Learning Unified Long-Term and Short-Term Memory Management for Large Language Model Agents</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
@@ -12266,7 +12266,7 @@
       <c r="H289" s="5" t="n"/>
       <c r="I289" s="5" t="inlineStr">
         <is>
-          <t>5168d3595acaf7528039ee542eb57d0dc3ad2fd8</t>
+          <t>fddca50008a46c925b288bae079e43ead0bbeb6e</t>
         </is>
       </c>
     </row>
@@ -12276,7 +12276,7 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>How Easily do Irrelevant Inputs Skew the Responses of Large Language Models?</t>
+          <t>Agentic Memory: Learning Unified Long-Term and Short-Term Memory Management for Large Language Model Agents</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>attack</t>
+          <t>defense</t>
         </is>
       </c>
       <c r="F290" s="5" t="n"/>
@@ -12299,7 +12299,7 @@
       <c r="H290" s="5" t="n"/>
       <c r="I290" s="5" t="inlineStr">
         <is>
-          <t>5168d3595acaf7528039ee542eb57d0dc3ad2fd8</t>
+          <t>fddca50008a46c925b288bae079e43ead0bbeb6e</t>
         </is>
       </c>
     </row>
@@ -12309,7 +12309,7 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>How Easily do Irrelevant Inputs Skew the Responses of Large Language Models?</t>
+          <t>Agentic Memory: Learning Unified Long-Term and Short-Term Memory Management for Large Language Model Agents</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
@@ -12324,7 +12324,7 @@
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>RAG</t>
+          <t>memory</t>
         </is>
       </c>
       <c r="F291" s="5" t="n"/>
@@ -12332,7 +12332,7 @@
       <c r="H291" s="5" t="n"/>
       <c r="I291" s="5" t="inlineStr">
         <is>
-          <t>5168d3595acaf7528039ee542eb57d0dc3ad2fd8</t>
+          <t>fddca50008a46c925b288bae079e43ead0bbeb6e</t>
         </is>
       </c>
     </row>
@@ -12342,7 +12342,7 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>How Easily do Irrelevant Inputs Skew the Responses of Large Language Models?</t>
+          <t>Agentic Memory: Learning Unified Long-Term and Short-Term Memory Management for Large Language Model Agents</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
@@ -12365,7 +12365,7 @@
       <c r="H292" s="5" t="n"/>
       <c r="I292" s="5" t="inlineStr">
         <is>
-          <t>5168d3595acaf7528039ee542eb57d0dc3ad2fd8</t>
+          <t>fddca50008a46c925b288bae079e43ead0bbeb6e</t>
         </is>
       </c>
     </row>
@@ -12375,7 +12375,7 @@
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>How Easily do Irrelevant Inputs Skew the Responses of Large Language Models?</t>
+          <t>Agentic Memory: Learning Unified Long-Term and Short-Term Memory Management for Large Language Model Agents</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
@@ -12398,7 +12398,7 @@
       <c r="H293" s="5" t="n"/>
       <c r="I293" s="5" t="inlineStr">
         <is>
-          <t>5168d3595acaf7528039ee542eb57d0dc3ad2fd8</t>
+          <t>fddca50008a46c925b288bae079e43ead0bbeb6e</t>
         </is>
       </c>
     </row>
@@ -12408,7 +12408,7 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>How Easily do Irrelevant Inputs Skew the Responses of Large Language Models?</t>
+          <t>Agentic Memory: Learning Unified Long-Term and Short-Term Memory Management for Large Language Model Agents</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
@@ -12423,7 +12423,7 @@
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F294" s="5" t="n"/>
@@ -12431,7 +12431,7 @@
       <c r="H294" s="5" t="n"/>
       <c r="I294" s="5" t="inlineStr">
         <is>
-          <t>5168d3595acaf7528039ee542eb57d0dc3ad2fd8</t>
+          <t>fddca50008a46c925b288bae079e43ead0bbeb6e</t>
         </is>
       </c>
     </row>
@@ -12441,7 +12441,7 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>How Easily do Irrelevant Inputs Skew the Responses of Large Language Models?</t>
+          <t>Agentic Memory: Learning Unified Long-Term and Short-Term Memory Management for Large Language Model Agents</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
@@ -12456,7 +12456,7 @@
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>reasoning</t>
         </is>
       </c>
       <c r="F295" s="5" t="n"/>
@@ -12464,7 +12464,7 @@
       <c r="H295" s="5" t="n"/>
       <c r="I295" s="5" t="inlineStr">
         <is>
-          <t>5168d3595acaf7528039ee542eb57d0dc3ad2fd8</t>
+          <t>fddca50008a46c925b288bae079e43ead0bbeb6e</t>
         </is>
       </c>
     </row>
@@ -12474,7 +12474,7 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>How Easily do Irrelevant Inputs Skew the Responses of Large Language Models?</t>
+          <t>Agentic Memory: Learning Unified Long-Term and Short-Term Memory Management for Large Language Model Agents</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
@@ -12489,7 +12489,7 @@
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>one-shot</t>
+          <t>session-persistent</t>
         </is>
       </c>
       <c r="F296" s="5" t="n"/>
@@ -12497,7 +12497,7 @@
       <c r="H296" s="5" t="n"/>
       <c r="I296" s="5" t="inlineStr">
         <is>
-          <t>5168d3595acaf7528039ee542eb57d0dc3ad2fd8</t>
+          <t>fddca50008a46c925b288bae079e43ead0bbeb6e</t>
         </is>
       </c>
     </row>
@@ -12507,7 +12507,7 @@
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>How Easily do Irrelevant Inputs Skew the Responses of Large Language Models?</t>
+          <t>Agentic Memory: Learning Unified Long-Term and Short-Term Memory Management for Large Language Model Agents</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
@@ -12522,7 +12522,7 @@
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F297" s="5" t="n"/>
@@ -12530,7 +12530,7 @@
       <c r="H297" s="5" t="n"/>
       <c r="I297" s="5" t="inlineStr">
         <is>
-          <t>5168d3595acaf7528039ee542eb57d0dc3ad2fd8</t>
+          <t>fddca50008a46c925b288bae079e43ead0bbeb6e</t>
         </is>
       </c>
     </row>
@@ -12540,7 +12540,7 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>How Easily do Irrelevant Inputs Skew the Responses of Large Language Models?</t>
+          <t>Agentic Memory: Learning Unified Long-Term and Short-Term Memory Management for Large Language Model Agents</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
@@ -12555,7 +12555,7 @@
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>All resources (the irrelevant-information construction framework, constructed datasets, and evaluation code) are stated to be available on GitHub, though the specific repository URL is not given in the main text.</t>
+          <t>The paper does not state an explicit public code/checkpoint release URL in the excerpted text. It uses the Agentscope framework for agent construction and the Trinity framework for RL fine-tuning, both cited as prior third-party tools rather than releases of this paper.</t>
         </is>
       </c>
       <c r="F298" s="5" t="n"/>
@@ -12563,7 +12563,7 @@
       <c r="H298" s="5" t="n"/>
       <c r="I298" s="5" t="inlineStr">
         <is>
-          <t>5168d3595acaf7528039ee542eb57d0dc3ad2fd8</t>
+          <t>fddca50008a46c925b288bae079e43ead0bbeb6e</t>
         </is>
       </c>
     </row>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>How Easily do Irrelevant Inputs Skew the Responses of Large Language Models?</t>
+          <t>Agentic Memory: Learning Unified Long-Term and Short-Term Memory Management for Large Language Model Agents</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
@@ -12588,7 +12588,7 @@
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>Four LLMs: three closed-source (GPT-3.5 Turbo, GPT-4 Turbo, Gemini Pro) and one open-source (Llama2-7B). GPT-3.5 Turbo is additionally used as an automatic answer-alignment judge for free-form responses (validated against human evaluation on 300 cases, 97% agreement), and GPT-4 Turbo is used to generate the natural-language 'Related Information' passages for the irrelevant-information construction pipeline.</t>
+          <t>Two base LLM backbones fine-tuned with AgeMem: Qwen2.5-7B-Instruct and Qwen3-4B-Instruct. Four representative agent long-term-memory (LTM) baseline systems: LangMem, A-Mem (Zettelkasten-inspired), Mem0, and Mem0g (graph-based Mem0 variant). An ablation baseline AgeMem-noRL (same tool interface, no RL fine-tuning) isolates the RL contribution. Qwen-Max is used as an LLM-based evaluator for memory-quality scoring.</t>
         </is>
       </c>
       <c r="F299" s="5" t="n"/>
@@ -12596,7 +12596,7 @@
       <c r="H299" s="5" t="n"/>
       <c r="I299" s="5" t="inlineStr">
         <is>
-          <t>5168d3595acaf7528039ee542eb57d0dc3ad2fd8</t>
+          <t>fddca50008a46c925b288bae079e43ead0bbeb6e</t>
         </is>
       </c>
     </row>
@@ -12606,7 +12606,7 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>How Easily do Irrelevant Inputs Skew the Responses of Large Language Models?</t>
+          <t>Agentic Memory: Learning Unified Long-Term and Short-Term Memory Management for Large Language Model Agents</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
@@ -12621,7 +12621,7 @@
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>Two entity-centric open-domain QA datasets: PopQA (Mallen et al. 2023, 14,000 questions from Wikidata (subj, relationship, obj) triples across 16 relationship types) and EntityQuestions (Sciavolino et al. 2021, 17 additional relationship types not covered by PopQA, 1,500 randomly sampled entries per relationship). The Contriever dense retriever is used to source Top-10 Wikipedia passages for constructing irrelevant information. Evaluation uses a custom Misrepresentation Ratio (MR, how often the LLM's answer changes to an irrelevant option) and Uncertainty Ratio (UR, how often the LLM expresses uncertainty) across multiple-choice, boolean, and free-form QA formats.</t>
+          <t>Five long-horizon, reasoning-intensive benchmarks: ALFWorld and BabyAI (embodied instruction-following/navigation), SciWorld (a science-themed embodied benchmark), PDDL-based planning benchmarks, and HotpotQA (multi-hop QA, whose annotated supporting facts are also used to construct an LLM-based Memory Quality metric). Metrics include task success/accuracy per benchmark, an LLM-evaluated Memory Quality (MQ) score assessing relevance between stored LTM entries and ground-truth facts, and average prompt token count as an efficiency metric for STM management.</t>
         </is>
       </c>
       <c r="F300" s="5" t="n"/>
@@ -12629,7 +12629,7 @@
       <c r="H300" s="5" t="n"/>
       <c r="I300" s="5" t="inlineStr">
         <is>
-          <t>5168d3595acaf7528039ee542eb57d0dc3ad2fd8</t>
+          <t>fddca50008a46c925b288bae079e43ead0bbeb6e</t>
         </is>
       </c>
     </row>
@@ -12639,7 +12639,7 @@
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>How Easily do Irrelevant Inputs Skew the Responses of Large Language Models?</t>
+          <t>Agentic Memory: Learning Unified Long-Term and Short-Term Memory Management for Large Language Model Agents</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>LLMs are far more distracted by semantically related irrelevant information than by unrelated information: for GPT-3.5 Turbo on PopQA, MR rises from 5.5% (Unrelated) to 10.0% (Partially Related) to 22.5% (Related), with a similar pattern for GPT-4 Turbo (8.2% to 8.5% to 15.0%) and Gemini Pro (5.3% to 5.9% to 10.3%); Llama2-7B is most severely affected, reaching MR of 83.5% under Related Information on PopQA. Increasing the quantity of irrelevant information worsens distraction (e.g., GPT-3.5 Turbo MR rises from 22.5% at a 1:0 irrelevant:relevant ratio to 27.4% at 3:0, and even with one piece of relevant information present, MR only drops to 1.7%/5.5% at 1:1/3:1 ratios) and question format matters, with free-form QA proving most robust (GPT-3.5 Turbo MR of 2.7% under free-form vs. 5.5% under multiple-choice at a 3:1 ratio). Mitigation strategies largely fail or backfire: adding Chain-of-Thought prompting increases GPT-3.5 Turbo's misrepresentation ratio (from 6.1% to 10.1% on PopQA) due to 'over-reasoning' on misleading content, an explicit 'ignore irrelevant information' instruction yields only marginal improvement, and providing in-context examples of relevant/irrelevant labeling can even increase the misrepresentation ratio.</t>
+          <t>AgeMem achieves the highest average performance on both backbones: 41.96% on Qwen2.5-7B-Instruct and 54.31% on Qwen3-4B-Instruct, representing relative gains of 49.59% and 23.52% over a No-Memory baseline, and improvements of 4.82 and 8.57 percentage points over the best prior baselines (Mem0 and A-Mem respectively). RL training itself contributes 8.53 and 8.72 percentage points of improvement over the non-RL ablation (AgeMem-noRL), validating the three-stage progressive RL strategy. On HotpotQA specifically, AgeMem's LLM-evaluated Memory Quality (MQ) score is highest among all baselines at 0.533 (Qwen2.5) and 0.605 (Qwen3), indicating it stores more relevant, reusable knowledge, not just achieving higher task accuracy. For STM efficiency, AgeMem reduces average prompt token usage versus an AgeMem-RAG ablation (STM tools replaced by standard RAG) by 3.1% on Qwen2.5 (2,117 vs. 2,186 tokens) and 5.1% on Qwen3 (2,191 vs. 2,310 tokens). Tool-usage analysis shows RL training shifts behavior toward more selective, efficient memory operations -- e.g., RETRIEVE call frequency decreases post-RL (Qwen2.5: 2.31 to 1.95 calls/episode) while FILTER usage increases substantially (e.g., 0.02 to 0.31 on Qwen2.5), indicating the agent learns proactive context control rather than indiscriminate retrieval.</t>
         </is>
       </c>
       <c r="F301" s="5" t="n"/>
@@ -12662,7 +12662,7 @@
       <c r="H301" s="5" t="n"/>
       <c r="I301" s="5" t="inlineStr">
         <is>
-          <t>5168d3595acaf7528039ee542eb57d0dc3ad2fd8</t>
+          <t>fddca50008a46c925b288bae079e43ead0bbeb6e</t>
         </is>
       </c>
     </row>
@@ -12672,7 +12672,7 @@
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>How Easily do Irrelevant Inputs Skew the Responses of Large Language Models?</t>
+          <t>Agentic Memory: Learning Unified Long-Term and Short-Term Memory Management for Large Language Model Agents</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
@@ -12687,7 +12687,7 @@
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>The paper is primarily a diagnostic/benchmarking study rather than a method paper defending against a baseline; its 'baselines' are the three graded categories of irrelevant information (Unrelated, Partially Related, Related) compared against each other as conditions, plus a relevant-information-only control (parametric memory / gold passage). For the mitigation-strategies analysis (Sec. 4.4), a Vanilla (no mitigation) condition is compared against three existing mitigation techniques: Chain-of-Thought prompting (+CoT), an explicit ignore-irrelevant-information instruction (+instr.), and in-context learning examples of relevant/irrelevant labeling (+instr.+ICL).</t>
+          <t>Four external LTM baseline systems (LangMem, A-Mem, Mem0, Mem0g) representing trigger-based and agent-based long-term memory paradigms with static short-term memory; a No-Memory baseline; and an internal ablation, AgeMem-noRL, which uses the same unified tool interface but without the proposed three-stage RL training, isolating the contribution of reinforcement learning. A further internal ablation compares AgeMem's learned STM tools (RETRIEVE/SUMMARY/FILTER) against a standard RAG-based STM approach (AgeMem-RAG) to isolate STM management's efficiency contribution.</t>
         </is>
       </c>
       <c r="F302" s="5" t="n"/>
@@ -12695,7 +12695,7 @@
       <c r="H302" s="5" t="n"/>
       <c r="I302" s="5" t="inlineStr">
         <is>
-          <t>5168d3595acaf7528039ee542eb57d0dc3ad2fd8</t>
+          <t>fddca50008a46c925b288bae079e43ead0bbeb6e</t>
         </is>
       </c>
     </row>
@@ -12705,7 +12705,7 @@
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>How Easily do Irrelevant Inputs Skew the Responses of Large Language Models?</t>
+          <t>Agentic Memory: Learning Unified Long-Term and Short-Term Memory Management for Large Language Model Agents</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
@@ -12720,7 +12720,7 @@
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>N/A - non-adversarial. This is a robustness/diagnostic study of RAG systems under naturally occurring irrelevant retrieved content, not an adversarial attack paper -- the 'irrelevant information' is constructed from real Wikipedia passages retrieved by a standard dense retriever (Contriever) rather than adversarially crafted to manipulate the model. The incidental failure mode is that LLMs are systematically distracted (misrepresent their answer) by topically/semantically related but factually irrelevant retrieved passages, with the effect worsening as such content's semantic similarity and quantity increase, and existing mitigation prompting strategies (CoT, ignore-instructions, ICL examples) provide little or even negative protection.</t>
+          <t>N/A - non-adversarial. This is an agent memory-management/reinforcement-learning paper, not a security paper; there is no adversary. The incidental failure mode addressed is architectural/systemic: existing LLM agents treat long-term memory (LTM) and short-term memory (STM) as separate, loosely-coupled, heuristic-driven components (fixed triggers, predefined schedules, or auxiliary expert-model controllers), leading to fragmented memory construction, redundant storage, context explosion, and loss of rare-but-crucial details in long-horizon reasoning tasks -- AgeMem addresses this by unifying LTM and STM control into a single learnable agent policy.</t>
         </is>
       </c>
       <c r="F303" s="5" t="n"/>
@@ -12728,7 +12728,7 @@
       <c r="H303" s="5" t="n"/>
       <c r="I303" s="5" t="inlineStr">
         <is>
-          <t>5168d3595acaf7528039ee542eb57d0dc3ad2fd8</t>
+          <t>fddca50008a46c925b288bae079e43ead0bbeb6e</t>
         </is>
       </c>
     </row>
@@ -12738,7 +12738,7 @@
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>How Easily do Irrelevant Inputs Skew the Responses of Large Language Models?</t>
+          <t>Agentic Memory: Learning Unified Long-Term and Short-Term Memory Management for Large Language Model Agents</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>The paper has no explicit standalone 'Limitations' section (this is a COLM 2024 paper without a distinct end-of-paper Limitations heading). The closest analog is Section 4.4, 'Limitations of Current Solutions,' which is itself a set of findings (not a limitations statement about the paper's own study) showing that CoT prompting, ignore-instructions, and ICL examples all fail to reliably improve LLM robustness to related irrelevant information, and can even worsen performance (CoT causing 'over-reasoning,' ICL examples sometimes raising the misrepresentation ratio). The Conclusion reiterates this finding as the paper's key takeaway and calls for focused future research on mitigating irrelevant-information interference, rather than framing it as a limitation of the current study's methodology.</t>
+          <t>The paper has an explicit 'Limitations' section with two points: (1) the current implementation adopts a fixed set of memory management tools (ADD/UPDATE/DELETE for LTM; RETRIEVE/SUMMARY/FILTER for STM), which provides a clear and effective abstraction but could be extended to support more fine-grained memory control in future work; (2) although the approach is evaluated on five representative long-horizon benchmarks and demonstrates zero-shot cross-domain transfer, these settings remain relatively controlled compared to open-ended real-world deployments -- evaluation in persistent, long-term dialogue or real-user interaction scenarios is identified as an important next step, with the current study framed as establishing cross-domain transfer under controlled conditions as a foundation for that future work.</t>
         </is>
       </c>
       <c r="F304" s="5" t="n"/>
@@ -12761,7 +12761,7 @@
       <c r="H304" s="5" t="n"/>
       <c r="I304" s="5" t="inlineStr">
         <is>
-          <t>5168d3595acaf7528039ee542eb57d0dc3ad2fd8</t>
+          <t>fddca50008a46c925b288bae079e43ead0bbeb6e</t>
         </is>
       </c>
     </row>
@@ -12771,7 +12771,7 @@
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>How Easily do Irrelevant Inputs Skew the Responses of Large Language Models?</t>
+          <t>Agentic Memory: Learning Unified Long-Term and Short-Term Memory Management for Large Language Model Agents</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
@@ -12786,7 +12786,7 @@
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>This paper systematically studies how robust LLMs are to irrelevant information encountered in Retrieval-Augmented Generation (RAG), motivated by the observation that real retrieval systems surface top-ranked passages that are topically similar but factually irrelevant to the query. The authors construct a graded framework for irrelevant information using Wikipedia and the Contriever dense retriever: Unrelated Information (high similarity score but topically unconnected, built from a different subject/object pair within the same relationship type), Partially Related Information (topically connected but not entailing the answer), and Related Information (highest similarity, generated via GPT-4 Turbo to bear strong semantic connection to the question while still not answering it) -- validated to have similarity scores comparable to genuinely retrieved Wikipedia passages. Using entity-centric QA from PopQA and EntityQuestions, and eliciting each LLM's parametric memory answer via closed-book QA as a relevant-information control, the authors evaluate four LLMs (GPT-3.5 Turbo, GPT-4 Turbo, Gemini Pro, Llama2-7B) with a Misrepresentation Ratio and Uncertainty Ratio across multiple-choice, boolean, and free-form question formats, and under varying quantities/ratios of irrelevant-to-relevant information. They find LLMs are substantially more prone to being misled as semantic relatedness and quantity of irrelevant content increase, that free-form question format is most robust while multiple-choice is least robust, and that common mitigation techniques (Chain-of-Thought prompting, explicit ignore-instructions, in-context relevant/irrelevant examples) provide only marginal or sometimes counterproductive protection, with CoT specifically inducing 'over-reasoning' failures where the model's reasoning chain incorporates the misleading irrelevant content into its final answer.</t>
+          <t>Agentic Memory (AgeMem) is a unified reinforcement-learning framework that integrates long-term memory (LTM) and short-term memory (STM) management directly into an LLM agent's own policy, rather than treating them as separate heuristic-driven or externally-controlled components. The agent's state at each timestep combines the current context (STM), the persistent memory store (LTM), and the task specification; the agent selects actions from a hybrid action space spanning ordinary language generation and six explicit memory-management tools exposed via a tool-calling interface: ADD, UPDATE, and DELETE for manipulating LTM entries, and RETRIEVE (top-k semantic retrieval from LTM into active context), SUMMARY (compress a context span), and FILTER (remove irrelevant context segments) for STM. To train this unified policy despite the sparse, discontinuous rewards induced by memory operations (since most memory actions only receive credit at trajectory completion) and the training-paradigm mismatch between typical LTM-focused and STM-focused RL setups, the authors design a three-stage progressive RL curriculum: Stage 1 trains casual-interaction LTM storage behavior; Stage 2 resets the context and injects distracting content to train selective STM retention/compression, forcing genuine reliance on LTM rather than residual context; Stage 3 presents tasks requiring coordinated use of both persistent LTM (which carries over across all stages) and STM management. To propagate terminal task rewards back to earlier memory decisions across this staged, fragmented trajectory structure, the authors design a step-wise Group Relative Policy Optimization (GRPO) variant that performs credit assignment over the full multi-stage trajectory. Evaluated on five long-horizon, reasoning-intensive benchmarks (ALFWorld, SciWorld, PDDL planning, BabyAI, HotpotQA) across two LLM backbones (Qwen2.5-7B-Instruct, Qwen3-4B-Instruct), AgeMem consistently outperforms four representative external LTM systems (LangMem, A-Mem, Mem0, Mem0g) as well as a non-RL ablation of itself, while also producing higher-quality stored memories (per an LLM-based Memory Quality metric) and more token-efficient context management than a RAG-based STM alternative.</t>
         </is>
       </c>
       <c r="F305" s="5" t="n"/>
@@ -12794,7 +12794,7 @@
       <c r="H305" s="5" t="n"/>
       <c r="I305" s="5" t="inlineStr">
         <is>
-          <t>5168d3595acaf7528039ee542eb57d0dc3ad2fd8</t>
+          <t>fddca50008a46c925b288bae079e43ead0bbeb6e</t>
         </is>
       </c>
     </row>
@@ -12814,7 +12814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -12893,27 +12893,27 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Lost in the Middle: An Emergent Property from Information Retrieval Demands in LLMs</t>
+          <t>A Layered Security Framework Against Prompt Injection in RAG-Based Chatbots</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>attack / failure mechanism</t>
+          <t>defense / fix</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>mechanistic explanation of lost-in-the-middle (training-induced primacy/recency from retrieval-demand adaptation)</t>
+          <t>UNNAMED: Three-layer middleware defense for RAG chatbots (Input Screening + Privilege-Constrained Context Assembly + Output Auditing)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>RAG</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="G2" s="5" t="n"/>
@@ -12922,7 +12922,7 @@
       <c r="J2" s="5" t="n"/>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>47878fc606ace61368776bf9407466cc19ea7a9b</t>
+          <t>1a062f96584a9f5c14177ae49fe9bb3ae30b67c1</t>
         </is>
       </c>
     </row>
@@ -12932,22 +12932,22 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>A Study on Prompt Injection Attack Against LLM-Integrated Mobile Robotic Systems</t>
+          <t>Protecting Context and Prompts: Deterministic Security for Non-Deterministic AI</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>attack / failure mechanism</t>
+          <t>defense / fix</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>UNNAMED: multi-modal prompt injection against robot navigation</t>
+          <t>Authenticated Prompts / Authenticated Context (cryptographic provenance + policy algebra)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>cross-modal</t>
+          <t>tool-output</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -12961,7 +12961,7 @@
       <c r="J3" s="5" t="n"/>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>bb5cd74e28059073b0f50ba42b1dcec41d29af82</t>
+          <t>94981b50dd04908681311e4a3ff3a833b297ea3d</t>
         </is>
       </c>
     </row>
@@ -12971,7 +12971,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>A Study on Prompt Injection Attack Against LLM-Integrated Mobile Robotic Systems</t>
+          <t>RADIANT: Retrieval AugmenteD entIty-context AligNmenT - Introducing RAG-ability and Entity-Context Divergence</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>UNNAMED: secure prompt strategies for robotic navigation</t>
+          <t>RADIANT (DPO-ECD, Entity-Context Divergence alignment)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>RAG</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="G4" s="5" t="n"/>
@@ -13000,7 +13000,7 @@
       <c r="J4" s="5" t="n"/>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>bb5cd74e28059073b0f50ba42b1dcec41d29af82</t>
+          <t>719089f4a546d74b4b8ec6bcdac5dfd8dd4391da</t>
         </is>
       </c>
     </row>
@@ -13010,7 +13010,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Unified Security Orchestration Framework for Protecting AI/ML Systems Against Input-Based and Model Supply Chain Attacks</t>
+          <t>AgentSecBench: Measuring Prompt Injection, Privacy Leakage, and Tool-Use Integrity in LLM Agents</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -13020,17 +13020,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Unified Security Orchestration Framework (USOF)</t>
+          <t>AgentSecBench Combined defense stack (filtering + projection + redaction + delimiter annotation)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>supply-chain</t>
+          <t>RAG</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>data-exfiltration</t>
         </is>
       </c>
       <c r="G5" s="5" t="n"/>
@@ -13039,7 +13039,7 @@
       <c r="J5" s="5" t="n"/>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>cce1b13eebe88e5051d329a95616c9df646fb08c</t>
+          <t>7761142d2760d74f0870cabe24176356e32198e0</t>
         </is>
       </c>
     </row>
@@ -13049,27 +13049,27 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Failure-Gated Hierarchical Memory: Preventing Memory Pollution in Long-Horizon LLM Agents via Critic-Guided Write Control</t>
+          <t>Addressing Prompt Injection in Large Language Models via In-Context Learning</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>attack / failure mechanism</t>
+          <t>defense / fix</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>memory pollution (agent long-term memory)</t>
+          <t>UNNAMED: ICL-based multi-LLM agent harmfulness-detection framework</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>silent-corruption</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="G6" s="5" t="n"/>
@@ -13078,7 +13078,7 @@
       <c r="J6" s="5" t="n"/>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>341883c91dabb788b32dae7d1bd6c6146d266b95</t>
+          <t>c30673d667b2875f2a7563c4755520d6961783f8</t>
         </is>
       </c>
     </row>
@@ -13088,7 +13088,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Failure-Gated Hierarchical Memory: Preventing Memory Pollution in Long-Horizon LLM Agents via Critic-Guided Write Control</t>
+          <t>Agentic Permissions Policy Algebra for Taint Confinement in LLM Agents</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -13098,17 +13098,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>FGHM (Failure-Gated Hierarchical Memory) with Failure Critic and LTM Pollution Rate (LPR) metric</t>
+          <t>APPA (Agentic Permissions Policy Algebra)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>tool-output</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>silent-corruption</t>
+          <t>data-exfiltration</t>
         </is>
       </c>
       <c r="G7" s="5" t="n"/>
@@ -13117,7 +13117,7 @@
       <c r="J7" s="5" t="n"/>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>341883c91dabb788b32dae7d1bd6c6146d266b95</t>
+          <t>a627218ebc531a61b3f43df433c8034165e32ba9</t>
         </is>
       </c>
     </row>
@@ -13127,7 +13127,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Fact-Augmented Lookahead Planning for LLM Agents</t>
+          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -13137,12 +13137,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>LWM-Planner (Fact Extraction and Compression / FEC)</t>
+          <t>UNNAMED: DPO-based faithfulness-improvement training for GUI agents against environmental distraction</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>cross-modal</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -13156,7 +13156,7 @@
       <c r="J8" s="5" t="n"/>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>93f50fbd4ed8303e86ebb5946339bb103a234ab5</t>
+          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
         </is>
       </c>
     </row>
@@ -13166,7 +13166,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>ReAcTree: Hierarchical LLM Agent Trees with Control Flow for Long-Horizon Task Planning</t>
+          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -13176,17 +13176,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>ReAcTree</t>
+          <t>Pattern D: Inference-boundary redaction proxy (PII extraction/tokenization before model inference)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>tool-output</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="G9" s="5" t="n"/>
@@ -13195,7 +13195,7 @@
       <c r="J9" s="5" t="n"/>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>adfb2a3dd1d4913fb68f057a0b92c4aa224adcea</t>
+          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
         </is>
       </c>
     </row>
@@ -13205,22 +13205,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Oblivion: Self-Adaptive Agentic Memory Control through Decay-Driven Activation</t>
+          <t>When Refusals Fail: Unstable Safety Mechanisms in Long-Context LLM Agents</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>defense / fix</t>
+          <t>attack / failure mechanism</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Oblivion (decay-driven memory control)</t>
+          <t>UNNAMED: long-context safety/refusal degradation in agents</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -13234,7 +13234,7 @@
       <c r="J10" s="5" t="n"/>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>454069505d79f8b20538c78591702ac4dae921df</t>
+          <t>febb0d38c39219f39d5325345882b5148a84b79e</t>
         </is>
       </c>
     </row>
@@ -13244,7 +13244,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>WAB: Overcoming Memory, Network, and Security Walls in Native Agentic Browsers with WebAssembly</t>
+          <t>Meticulous Thought Defender: Fine-Grained Chain-of-Thought (CoT) for Detecting Prompt Injection Attacks of Large Language Models</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>UNNAMED: WAB Wasm-sandboxed capability-based authority mechanism (allowlisted API with explicit grant/revocation)</t>
+          <t>Meticulous Thought Defender</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -13273,7 +13273,7 @@
       <c r="J11" s="5" t="n"/>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>74aec0665c948c64072682901b7e95e7b71286e4</t>
+          <t>06fa2b9d40f97bd093aa3d21f42828ed82d8f55e</t>
         </is>
       </c>
     </row>
@@ -13283,7 +13283,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Causal Intervention-Based Memory Selection for Long-Horizon LLM Agents</t>
+          <t>Agentic Memory: Learning Unified Long-Term and Short-Term Memory Management for Large Language Model Agents</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -13293,7 +13293,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>CMI (Causal Memory Intervention)</t>
+          <t>AgeMem (Agentic Memory)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -13312,97 +13312,19 @@
       <c r="J12" s="5" t="n"/>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>90df5be685de81b6b1acde9031629969b9ce2b49</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Embedding-Based Detection of Indirect Prompt Injection Attacks in Large Language Models Using Semantic Context Analysis</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>defense / fix</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>UNNAMED: Embedding-based semantic context analysis detector for IPI</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>tool-output</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>goal-hijack</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>dfc9d7ad54c197d239cb473f3ae7a64ab50d0e90</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>How Easily do Irrelevant Inputs Skew the Responses of Large Language Models?</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>attack / failure mechanism</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>distraction by irrelevant context (graded by semantic relatedness)</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>RAG</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>reasoning-corruption</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>5168d3595acaf7528039ee542eb57d0dc3ad2fd8</t>
+          <t>fddca50008a46c925b288bae079e43ead0bbeb6e</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation sqref="G2:G14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"yes,no,unclear"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"yes,no,unclear"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"yes,no,unclear"</formula1>
     </dataValidation>
   </dataValidations>
